--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D51A35-FE7F-AF40-BF25-9B1774A55AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209D92CF-B366-CB46-8259-0512C8FAEC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -458,10 +458,10 @@
     <t>Ismail Mediouna</t>
   </si>
   <si>
-    <t xml:space="preserve">Fares </t>
-  </si>
-  <si>
     <t>Donald Onana</t>
+  </si>
+  <si>
+    <t>Fares Farhi</t>
   </si>
 </sst>
 </file>
@@ -519,75 +519,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2332,11 +2264,11 @@
         <v>0</v>
       </c>
       <c r="W2" s="3">
-        <f>SUM(AK2,AO2,AS2,AW2,BA2,BE2,BI2,BM2,BQ2,BU2,BY2,CC2,CG2,CK2,CO2,CS2,CW2,DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <f t="shared" ref="W2:W32" si="1">SUM(AK2,AO2,AS2,AW2,BA2,BE2,BI2,BM2,BQ2,BU2,BY2,CC2,CG2,CK2,CO2,CS2,CW2,DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
         <v>0</v>
       </c>
       <c r="X2" s="4">
-        <f>SUM(DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <f t="shared" ref="X2:X32" si="2">SUM(DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
         <v>0</v>
       </c>
       <c r="Y2" s="4" t="e">
@@ -2372,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <f>SUM(IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <f t="shared" ref="AG2:AG32" si="3">SUM(IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
         <v>0</v>
       </c>
       <c r="AH2" t="e">
@@ -2392,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="PV2">
-        <f t="shared" ref="PV2:PV29" si="1">COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" ref="PV2:PV29" si="4">COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW2">
@@ -2409,79 +2341,79 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C29" si="2">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
+        <f t="shared" ref="C3:C29" si="5">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D29" si="3">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
+        <f t="shared" ref="D3:D29" si="6">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E29" si="4">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
+        <f t="shared" ref="E3:E29" si="7">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F30" si="5">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
+        <f t="shared" ref="F3:F30" si="8">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G29" si="6">SUM(H3:I3)</f>
+        <f t="shared" ref="G3:G29" si="9">SUM(H3:I3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H29" si="7">COUNTIF(AI3:PR3,"T")</f>
+        <f t="shared" ref="H3:H29" si="10">COUNTIF(AI3:PR3,"T")</f>
         <v>0</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I29" si="8">COUNTIF(AI3:PR3,"R")</f>
+        <f t="shared" ref="I3:I29" si="11">COUNTIF(AI3:PR3,"R")</f>
         <v>0</v>
       </c>
       <c r="J3" s="3">
-        <f t="shared" ref="J3:J29" si="9">COUNTIF(AI3:PR3,"NR")</f>
+        <f t="shared" ref="J3:J29" si="12">COUNTIF(AI3:PR3,"NR")</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K29" si="10">SUM(L3:M3)</f>
+        <f t="shared" ref="K3:K29" si="13">SUM(L3:M3)</f>
         <v>0</v>
       </c>
       <c r="L3" s="3">
-        <f t="shared" ref="L3:L29" si="11">COUNTIF(CY3:GX3,"T")</f>
+        <f t="shared" ref="L3:L29" si="14">COUNTIF(CY3:GX3,"T")</f>
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <f t="shared" ref="M3:M29" si="12">COUNTIF(CY3:GX3,"R")</f>
+        <f t="shared" ref="M3:M29" si="15">COUNTIF(CY3:GX3,"R")</f>
         <v>0</v>
       </c>
       <c r="N3" s="3">
-        <f t="shared" ref="N3:N29" si="13">COUNTIF(CY3:GX3,"NR")</f>
+        <f t="shared" ref="N3:N29" si="16">COUNTIF(CY3:GX3,"NR")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O29" si="14">SUM(P3:Q3)</f>
+        <f t="shared" ref="O3:O29" si="17">SUM(P3:Q3)</f>
         <v>0</v>
       </c>
       <c r="P3" s="3">
-        <f t="shared" ref="P3:P29" si="15">COUNTIF(GY3:IT3,"T")</f>
+        <f t="shared" ref="P3:P29" si="18">COUNTIF(GY3:IT3,"T")</f>
         <v>0</v>
       </c>
       <c r="Q3" s="3">
-        <f t="shared" ref="Q3:Q29" si="16">COUNTIF(GY3:IT3,"R")</f>
+        <f t="shared" ref="Q3:Q29" si="19">COUNTIF(GY3:IT3,"R")</f>
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <f t="shared" ref="R3:R29" si="17">COUNTIF(GY3:IT3,"NR")</f>
+        <f t="shared" ref="R3:R29" si="20">COUNTIF(GY3:IT3,"NR")</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S29" si="18">SUM(T3:U3)</f>
+        <f t="shared" ref="S3:S29" si="21">SUM(T3:U3)</f>
         <v>0</v>
       </c>
       <c r="T3" s="3">
-        <f t="shared" ref="T3:T29" si="19">COUNTIF(IU3:PR3,"T")</f>
+        <f t="shared" ref="T3:T29" si="22">COUNTIF(IU3:PR3,"T")</f>
         <v>0</v>
       </c>
       <c r="U3" s="3">
-        <f t="shared" ref="U3:U29" si="20">COUNTIF(IU3:PR3,"R")</f>
+        <f t="shared" ref="U3:U29" si="23">COUNTIF(IU3:PR3,"R")</f>
         <v>0</v>
       </c>
       <c r="V3" s="3">
@@ -2489,11 +2421,11 @@
         <v>0</v>
       </c>
       <c r="W3" s="3">
-        <f>SUM(AK3,AO3,AS3,AW3,BA3,BE3,BI3,BM3,BQ3,BU3,BY3,CC3,CG3,CK3,CO3,CS3,CW3,DA3,DE3,DI3,DM3,DQ3,DU3,DY3,EC3,EG3,EK3,EO3,ES3,EW3,FA3,FE3,FI3,FM3,FQ3,FU3,FY3,GC3,GG3,GK3,GO3,GS3,GW3,HA3,HE3,HI3,HM3,HQ3,HU3,HY3,IC3,IG3,IK3,IO3,IS3,IW3,JA3,JE3,JI3,JM3,JQ3,JU3,JY3,KC3,KG3,KK3,KO3,KS3,KW3,LA3,LE3,LI3,LM3,LQ3,LU3,LY3,MC3,MH3,MK3,MO3,MS3,MW3,NA3,NE3,NI3,NM3,NQ3,NU3,NY3,OC3,OG3,OK3,OO3,OS3,OW3,PA3,PE3,PI3,PM3,PQ3)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X3" s="4">
-        <f>SUM(DA3,DE3,DI3,DM3,DQ3,DU3,DY3,EC3,EG3,EK3,EO3,ES3,EW3,FA3,FE3,FI3,FM3,FQ3,FU3,FY3,GC3,GG3,GK3,GO3,GS3,GW3,HA3,HE3,HI3,HM3,HQ3,HU3,HY3,IC3,IG3,IK3,IO3,IS3,IW3,JA3,JE3,JI3,JM3,JQ3,JU3,JY3,KC3,KG3,KK3,KO3,KS3,KW3,LA3,LE3,LI3,LM3,LQ3,LU3,LY3,MC3,MH3,MK3,MO3,MS3,MW3,NA3,NE3,NI3,NM3,NQ3,NU3,NY3,OC3,OG3,OK3,OO3,OS3,OW3,PA3,PE3,PI3,PM3,PQ3)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y3" s="4" t="e">
@@ -2505,31 +2437,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA3">
-        <f t="shared" ref="AA3:AA29" si="21">SUM(DA3,DE3,DI3,DM3,DQ3,DU3,DY3,EC3,EG3,EK3,EO3,ES3,EW3,FA3,FE3,FI3,FM3,FQ3,FU3,FY3,GC3,GG3,GK3,GO3,GS3,GW3)</f>
+        <f t="shared" ref="AA3:AA29" si="24">SUM(DA3,DE3,DI3,DM3,DQ3,DU3,DY3,EC3,EG3,EK3,EO3,ES3,EW3,FA3,FE3,FI3,FM3,FQ3,FU3,FY3,GC3,GG3,GK3,GO3,GS3,GW3)</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f t="shared" ref="AB3:AB29" si="22">SUM(DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3)</f>
+        <f t="shared" ref="AB3:AB29" si="25">SUM(DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3)</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" ref="AC3:AC29" si="23">SUM(HA3,HE3,HI3,HM3,HQ3,HU3,HY3,IC3,IG3,IK3,IO3,IS3)</f>
+        <f t="shared" ref="AC3:AC29" si="26">SUM(HA3,HE3,HI3,HM3,HQ3,HU3,HY3,IC3,IG3,IK3,IO3,IS3)</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD29" si="24">SUM(HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3)</f>
+        <f t="shared" ref="AD3:AD29" si="27">SUM(HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3)</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" ref="AE3:AE29" si="25">SUM(AK3,AO3,AS3,AW3,BA3,BE3,BI3,BM3,BQ3,BU3,BY3,CC3,CG3,CK3,CO3,CS3,CW3)</f>
+        <f t="shared" ref="AE3:AE29" si="28">SUM(AK3,AO3,AS3,AW3,BA3,BE3,BI3,BM3,BQ3,BU3,BY3,CC3,CG3,CK3,CO3,CS3,CW3)</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" ref="AF3:AF29" si="26">SUM(AL3,AP3,AT3,AX3,BB3,BF3,BJ3,BN3,BR3,BV3,BZ3,CD3,CH3,CL3,CP3,CT3,CX3)</f>
+        <f t="shared" ref="AF3:AF29" si="29">SUM(AL3,AP3,AT3,AX3,BB3,BF3,BJ3,BN3,BR3,BV3,BZ3,CD3,CH3,CL3,CP3,CT3,CX3)</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>SUM(IW3,JA3,JE3,JI3,JM3,JQ3,JU3,JY3,KC3,KG3,KK3,KO3,KS3,KW3,LA3,LE3,LI3,LM3,LQ3,LU3,LY3,MC3,MH3,MK3,MO3,MS3,MW3,NA3,NE3,NI3,NM3,NQ3,NU3,NY3,OC3,OG3,OK3,OO3,OS3,OW3,PA3,PE3,PI3,PM3,PQ3)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH3" t="e">
@@ -2537,23 +2469,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS3" s="3">
-        <f t="shared" ref="PS3:PS29" si="27">COUNTIF(AI3:PR3,"HG")</f>
+        <f t="shared" ref="PS3:PS29" si="30">COUNTIF(AI3:PR3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT3" s="3">
-        <f t="shared" ref="PT3:PT29" si="28">COUNTIF(CY3:GX3,"HG")</f>
+        <f t="shared" ref="PT3:PT29" si="31">COUNTIF(CY3:GX3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU3" s="3">
-        <f t="shared" ref="PU3:PU29" si="29">COUNTIF(GY3:IT3,"HG")</f>
+        <f t="shared" ref="PU3:PU29" si="32">COUNTIF(GY3:IT3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW3">
-        <f t="shared" ref="PW3:PW29" si="30">G3-(K3+O3+S3)</f>
+        <f t="shared" ref="PW3:PW29" si="33">G3-(K3+O3+S3)</f>
         <v>0</v>
       </c>
     </row>
@@ -2562,83 +2494,83 @@
         <v>128</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B29" si="31">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
+        <f t="shared" ref="B4:B29" si="34">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4" si="32">SUM(H4:I4)</f>
+        <f t="shared" ref="G4" si="35">SUM(H4:I4)</f>
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H4" si="33">COUNTIF(AI4:PR4,"T")</f>
+        <f t="shared" ref="H4" si="36">COUNTIF(AI4:PR4,"T")</f>
         <v>0</v>
       </c>
       <c r="I4" s="3">
-        <f t="shared" ref="I4" si="34">COUNTIF(AI4:PR4,"R")</f>
+        <f t="shared" ref="I4" si="37">COUNTIF(AI4:PR4,"R")</f>
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <f t="shared" ref="J4" si="35">COUNTIF(AI4:PR4,"NR")</f>
+        <f t="shared" ref="J4" si="38">COUNTIF(AI4:PR4,"NR")</f>
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4" si="36">SUM(L4:M4)</f>
+        <f t="shared" ref="K4" si="39">SUM(L4:M4)</f>
         <v>0</v>
       </c>
       <c r="L4" s="3">
-        <f t="shared" ref="L4" si="37">COUNTIF(CY4:GX4,"T")</f>
+        <f t="shared" ref="L4" si="40">COUNTIF(CY4:GX4,"T")</f>
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <f t="shared" ref="M4" si="38">COUNTIF(CY4:GX4,"R")</f>
+        <f t="shared" ref="M4" si="41">COUNTIF(CY4:GX4,"R")</f>
         <v>0</v>
       </c>
       <c r="N4" s="3">
-        <f t="shared" ref="N4" si="39">COUNTIF(CY4:GX4,"NR")</f>
+        <f t="shared" ref="N4" si="42">COUNTIF(CY4:GX4,"NR")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f t="shared" ref="O4" si="40">SUM(P4:Q4)</f>
+        <f t="shared" ref="O4" si="43">SUM(P4:Q4)</f>
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <f t="shared" ref="P4" si="41">COUNTIF(GY4:IT4,"T")</f>
+        <f t="shared" ref="P4" si="44">COUNTIF(GY4:IT4,"T")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="3">
-        <f t="shared" ref="Q4" si="42">COUNTIF(GY4:IT4,"R")</f>
+        <f t="shared" ref="Q4" si="45">COUNTIF(GY4:IT4,"R")</f>
         <v>0</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" ref="R4" si="43">COUNTIF(GY4:IT4,"NR")</f>
+        <f t="shared" ref="R4" si="46">COUNTIF(GY4:IT4,"NR")</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" ref="S4" si="44">SUM(T4:U4)</f>
+        <f t="shared" ref="S4" si="47">SUM(T4:U4)</f>
         <v>0</v>
       </c>
       <c r="T4" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U4" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V4" s="3">
@@ -2646,11 +2578,11 @@
         <v>0</v>
       </c>
       <c r="W4" s="3">
-        <f>SUM(AK4,AO4,AS4,AW4,BA4,BE4,BI4,BM4,BQ4,BU4,BY4,CC4,CG4,CK4,CO4,CS4,CW4,DA4,DE4,DI4,DM4,DQ4,DU4,DY4,EC4,EG4,EK4,EO4,ES4,EW4,FA4,FE4,FI4,FM4,FQ4,FU4,FY4,GC4,GG4,GK4,GO4,GS4,GW4,HA4,HE4,HI4,HM4,HQ4,HU4,HY4,IC4,IG4,IK4,IO4,IS4,IW4,JA4,JE4,JI4,JM4,JQ4,JU4,JY4,KC4,KG4,KK4,KO4,KS4,KW4,LA4,LE4,LI4,LM4,LQ4,LU4,LY4,MC4,MH4,MK4,MO4,MS4,MW4,NA4,NE4,NI4,NM4,NQ4,NU4,NY4,OC4,OG4,OK4,OO4,OS4,OW4,PA4,PE4,PI4,PM4,PQ4)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X4" s="4">
-        <f>SUM(DA4,DE4,DI4,DM4,DQ4,DU4,DY4,EC4,EG4,EK4,EO4,ES4,EW4,FA4,FE4,FI4,FM4,FQ4,FU4,FY4,GC4,GG4,GK4,GO4,GS4,GW4,HA4,HE4,HI4,HM4,HQ4,HU4,HY4,IC4,IG4,IK4,IO4,IS4,IW4,JA4,JE4,JI4,JM4,JQ4,JU4,JY4,KC4,KG4,KK4,KO4,KS4,KW4,LA4,LE4,LI4,LM4,LQ4,LU4,LY4,MC4,MH4,MK4,MO4,MS4,MW4,NA4,NE4,NI4,NM4,NQ4,NU4,NY4,OC4,OG4,OK4,OO4,OS4,OW4,PA4,PE4,PI4,PM4,PQ4)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y4" s="4" t="e">
@@ -2662,31 +2594,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA4">
-        <f t="shared" ref="AA4" si="45">SUM(DA4,DE4,DI4,DM4,DQ4,DU4,DY4,EC4,EG4,EK4,EO4,ES4,EW4,FA4,FE4,FI4,FM4,FQ4,FU4,FY4,GC4,GG4,GK4,GO4,GS4,GW4)</f>
+        <f t="shared" ref="AA4" si="48">SUM(DA4,DE4,DI4,DM4,DQ4,DU4,DY4,EC4,EG4,EK4,EO4,ES4,EW4,FA4,FE4,FI4,FM4,FQ4,FU4,FY4,GC4,GG4,GK4,GO4,GS4,GW4)</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f t="shared" ref="AB4" si="46">SUM(DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4)</f>
+        <f t="shared" ref="AB4" si="49">SUM(DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4)</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" ref="AC4" si="47">SUM(HA4,HE4,HI4,HM4,HQ4,HU4,HY4,IC4,IG4,IK4,IO4,IS4)</f>
+        <f t="shared" ref="AC4" si="50">SUM(HA4,HE4,HI4,HM4,HQ4,HU4,HY4,IC4,IG4,IK4,IO4,IS4)</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" ref="AD4" si="48">SUM(HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4)</f>
+        <f t="shared" ref="AD4" si="51">SUM(HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4)</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f t="shared" ref="AE4" si="49">SUM(AK4,AO4,AS4,AW4,BA4,BE4,BI4,BM4,BQ4,BU4,BY4,CC4,CG4,CK4,CO4,CS4,CW4)</f>
+        <f t="shared" ref="AE4" si="52">SUM(AK4,AO4,AS4,AW4,BA4,BE4,BI4,BM4,BQ4,BU4,BY4,CC4,CG4,CK4,CO4,CS4,CW4)</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" ref="AF4" si="50">SUM(AL4,AP4,AT4,AX4,BB4,BF4,BJ4,BN4,BR4,BV4,BZ4,CD4,CH4,CL4,CP4,CT4,CX4)</f>
+        <f t="shared" ref="AF4" si="53">SUM(AL4,AP4,AT4,AX4,BB4,BF4,BJ4,BN4,BR4,BV4,BZ4,CD4,CH4,CL4,CP4,CT4,CX4)</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>SUM(IW4,JA4,JE4,JI4,JM4,JQ4,JU4,JY4,KC4,KG4,KK4,KO4,KS4,KW4,LA4,LE4,LI4,LM4,LQ4,LU4,LY4,MC4,MH4,MK4,MO4,MS4,MW4,NA4,NE4,NI4,NM4,NQ4,NU4,NY4,OC4,OG4,OK4,OO4,OS4,OW4,PA4,PE4,PI4,PM4,PQ4)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH4" t="e">
@@ -2694,23 +2626,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS4" s="3">
-        <f t="shared" ref="PS4" si="51">COUNTIF(AI4:PR4,"HG")</f>
+        <f t="shared" ref="PS4" si="54">COUNTIF(AI4:PR4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT4" s="3">
-        <f t="shared" ref="PT4" si="52">COUNTIF(CY4:GX4,"HG")</f>
+        <f t="shared" ref="PT4" si="55">COUNTIF(CY4:GX4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU4" s="3">
-        <f t="shared" ref="PU4" si="53">COUNTIF(GY4:IT4,"HG")</f>
+        <f t="shared" ref="PU4" si="56">COUNTIF(GY4:IT4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW4">
-        <f t="shared" ref="PW4" si="54">G4-(K4+O4+S4)</f>
+        <f t="shared" ref="PW4" si="57">G4-(K4+O4+S4)</f>
         <v>0</v>
       </c>
     </row>
@@ -2719,83 +2651,83 @@
         <v>112</v>
       </c>
       <c r="B5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N5" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P5" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q5" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T5" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U5" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V5" s="3">
@@ -2803,11 +2735,11 @@
         <v>0</v>
       </c>
       <c r="W5" s="3">
-        <f>SUM(AK5,AO5,AS5,AW5,BA5,BE5,BI5,BM5,BQ5,BU5,BY5,CC5,CG5,CK5,CO5,CS5,CW5,DA5,DE5,DI5,DM5,DQ5,DU5,DY5,EC5,EG5,EK5,EO5,ES5,EW5,FA5,FE5,FI5,FM5,FQ5,FU5,FY5,GC5,GG5,GK5,GO5,GS5,GW5,HA5,HE5,HI5,HM5,HQ5,HU5,HY5,IC5,IG5,IK5,IO5,IS5,IW5,JA5,JE5,JI5,JM5,JQ5,JU5,JY5,KC5,KG5,KK5,KO5,KS5,KW5,LA5,LE5,LI5,LM5,LQ5,LU5,LY5,MC5,MH5,MK5,MO5,MS5,MW5,NA5,NE5,NI5,NM5,NQ5,NU5,NY5,OC5,OG5,OK5,OO5,OS5,OW5,PA5,PE5,PI5,PM5,PQ5)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X5" s="4">
-        <f>SUM(DA5,DE5,DI5,DM5,DQ5,DU5,DY5,EC5,EG5,EK5,EO5,ES5,EW5,FA5,FE5,FI5,FM5,FQ5,FU5,FY5,GC5,GG5,GK5,GO5,GS5,GW5,HA5,HE5,HI5,HM5,HQ5,HU5,HY5,IC5,IG5,IK5,IO5,IS5,IW5,JA5,JE5,JI5,JM5,JQ5,JU5,JY5,KC5,KG5,KK5,KO5,KS5,KW5,LA5,LE5,LI5,LM5,LQ5,LU5,LY5,MC5,MH5,MK5,MO5,MS5,MW5,NA5,NE5,NI5,NM5,NQ5,NU5,NY5,OC5,OG5,OK5,OO5,OS5,OW5,PA5,PE5,PI5,PM5,PQ5)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y5" s="4" t="e">
@@ -2819,31 +2751,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>SUM(IW5,JA5,JE5,JI5,JM5,JQ5,JU5,JY5,KC5,KG5,KK5,KO5,KS5,KW5,LA5,LE5,LI5,LM5,LQ5,LU5,LY5,MC5,MH5,MK5,MO5,MS5,MW5,NA5,NE5,NI5,NM5,NQ5,NU5,NY5,OC5,OG5,OK5,OO5,OS5,OW5,PA5,PE5,PI5,PM5,PQ5)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH5" t="e">
@@ -2851,23 +2783,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS5" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT5" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU5" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -2876,83 +2808,83 @@
         <v>129</v>
       </c>
       <c r="B6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R6" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V6" s="3">
@@ -2960,11 +2892,11 @@
         <v>0</v>
       </c>
       <c r="W6" s="3">
-        <f>SUM(AK6,AO6,AS6,AW6,BA6,BE6,BI6,BM6,BQ6,BU6,BY6,CC6,CG6,CK6,CO6,CS6,CW6,DA6,DE6,DI6,DM6,DQ6,DU6,DY6,EC6,EG6,EK6,EO6,ES6,EW6,FA6,FE6,FI6,FM6,FQ6,FU6,FY6,GC6,GG6,GK6,GO6,GS6,GW6,HA6,HE6,HI6,HM6,HQ6,HU6,HY6,IC6,IG6,IK6,IO6,IS6,IW6,JA6,JE6,JI6,JM6,JQ6,JU6,JY6,KC6,KG6,KK6,KO6,KS6,KW6,LA6,LE6,LI6,LM6,LQ6,LU6,LY6,MC6,MH6,MK6,MO6,MS6,MW6,NA6,NE6,NI6,NM6,NQ6,NU6,NY6,OC6,OG6,OK6,OO6,OS6,OW6,PA6,PE6,PI6,PM6,PQ6)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X6" s="4">
-        <f>SUM(DA6,DE6,DI6,DM6,DQ6,DU6,DY6,EC6,EG6,EK6,EO6,ES6,EW6,FA6,FE6,FI6,FM6,FQ6,FU6,FY6,GC6,GG6,GK6,GO6,GS6,GW6,HA6,HE6,HI6,HM6,HQ6,HU6,HY6,IC6,IG6,IK6,IO6,IS6,IW6,JA6,JE6,JI6,JM6,JQ6,JU6,JY6,KC6,KG6,KK6,KO6,KS6,KW6,LA6,LE6,LI6,LM6,LQ6,LU6,LY6,MC6,MH6,MK6,MO6,MS6,MW6,NA6,NE6,NI6,NM6,NQ6,NU6,NY6,OC6,OG6,OK6,OO6,OS6,OW6,PA6,PE6,PI6,PM6,PQ6)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y6" s="4" t="e">
@@ -2976,31 +2908,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>SUM(IW6,JA6,JE6,JI6,JM6,JQ6,JU6,JY6,KC6,KG6,KK6,KO6,KS6,KW6,LA6,LE6,LI6,LM6,LQ6,LU6,LY6,MC6,MH6,MK6,MO6,MS6,MW6,NA6,NE6,NI6,NM6,NQ6,NU6,NY6,OC6,OG6,OK6,OO6,OS6,OW6,PA6,PE6,PI6,PM6,PQ6)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH6" t="e">
@@ -3008,23 +2940,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS6" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT6" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU6" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -3033,83 +2965,83 @@
         <v>130</v>
       </c>
       <c r="B7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L7" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M7" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N7" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P7" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q7" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U7" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V7" s="3">
@@ -3117,11 +3049,11 @@
         <v>0</v>
       </c>
       <c r="W7" s="3">
-        <f>SUM(AK7,AO7,AS7,AW7,BA7,BE7,BI7,BM7,BQ7,BU7,BY7,CC7,CG7,CK7,CO7,CS7,CW7,DA7,DE7,DI7,DM7,DQ7,DU7,DY7,EC7,EG7,EK7,EO7,ES7,EW7,FA7,FE7,FI7,FM7,FQ7,FU7,FY7,GC7,GG7,GK7,GO7,GS7,GW7,HA7,HE7,HI7,HM7,HQ7,HU7,HY7,IC7,IG7,IK7,IO7,IS7,IW7,JA7,JE7,JI7,JM7,JQ7,JU7,JY7,KC7,KG7,KK7,KO7,KS7,KW7,LA7,LE7,LI7,LM7,LQ7,LU7,LY7,MC7,MH7,MK7,MO7,MS7,MW7,NA7,NE7,NI7,NM7,NQ7,NU7,NY7,OC7,OG7,OK7,OO7,OS7,OW7,PA7,PE7,PI7,PM7,PQ7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X7" s="4">
-        <f>SUM(DA7,DE7,DI7,DM7,DQ7,DU7,DY7,EC7,EG7,EK7,EO7,ES7,EW7,FA7,FE7,FI7,FM7,FQ7,FU7,FY7,GC7,GG7,GK7,GO7,GS7,GW7,HA7,HE7,HI7,HM7,HQ7,HU7,HY7,IC7,IG7,IK7,IO7,IS7,IW7,JA7,JE7,JI7,JM7,JQ7,JU7,JY7,KC7,KG7,KK7,KO7,KS7,KW7,LA7,LE7,LI7,LM7,LQ7,LU7,LY7,MC7,MH7,MK7,MO7,MS7,MW7,NA7,NE7,NI7,NM7,NQ7,NU7,NY7,OC7,OG7,OK7,OO7,OS7,OW7,PA7,PE7,PI7,PM7,PQ7)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y7" s="4" t="e">
@@ -3133,31 +3065,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>SUM(IW7,JA7,JE7,JI7,JM7,JQ7,JU7,JY7,KC7,KG7,KK7,KO7,KS7,KW7,LA7,LE7,LI7,LM7,LQ7,LU7,LY7,MC7,MH7,MK7,MO7,MS7,MW7,NA7,NE7,NI7,NM7,NQ7,NU7,NY7,OC7,OG7,OK7,OO7,OS7,OW7,PA7,PE7,PI7,PM7,PQ7)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH7" t="e">
@@ -3165,23 +3097,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS7" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT7" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU7" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -3190,71 +3122,71 @@
         <v>131</v>
       </c>
       <c r="B8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M8" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N8" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S8">
@@ -3262,11 +3194,11 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V8" s="3">
@@ -3274,11 +3206,11 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
-        <f>SUM(AK8,AO8,AS8,AW8,BA8,BE8,BI8,BM8,BQ8,BU8,BY8,CC8,CG8,CK8,CO8,CS8,CW8,DA8,DE8,DI8,DM8,DQ8,DU8,DY8,EC8,EG8,EK8,EO8,ES8,EW8,FA8,FE8,FI8,FM8,FQ8,FU8,FY8,GC8,GG8,GK8,GO8,GS8,GW8,HA8,HE8,HI8,HM8,HQ8,HU8,HY8,IC8,IG8,IK8,IO8,IS8,IW8,JA8,JE8,JI8,JM8,JQ8,JU8,JY8,KC8,KG8,KK8,KO8,KS8,KW8,LA8,LE8,LI8,LM8,LQ8,LU8,LY8,MC8,MH8,MK8,MO8,MS8,MW8,NA8,NE8,NI8,NM8,NQ8,NU8,NY8,OC8,OG8,OK8,OO8,OS8,OW8,PA8,PE8,PI8,PM8,PQ8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X8" s="4">
-        <f>SUM(DA8,DE8,DI8,DM8,DQ8,DU8,DY8,EC8,EG8,EK8,EO8,ES8,EW8,FA8,FE8,FI8,FM8,FQ8,FU8,FY8,GC8,GG8,GK8,GO8,GS8,GW8,HA8,HE8,HI8,HM8,HQ8,HU8,HY8,IC8,IG8,IK8,IO8,IS8,IW8,JA8,JE8,JI8,JM8,JQ8,JU8,JY8,KC8,KG8,KK8,KO8,KS8,KW8,LA8,LE8,LI8,LM8,LQ8,LU8,LY8,MC8,MH8,MK8,MO8,MS8,MW8,NA8,NE8,NI8,NM8,NQ8,NU8,NY8,OC8,OG8,OK8,OO8,OS8,OW8,PA8,PE8,PI8,PM8,PQ8)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y8" s="4" t="e">
@@ -3290,31 +3222,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>SUM(IW8,JA8,JE8,JI8,JM8,JQ8,JU8,JY8,KC8,KG8,KK8,KO8,KS8,KW8,LA8,LE8,LI8,LM8,LQ8,LU8,LY8,MC8,MH8,MK8,MO8,MS8,MW8,NA8,NE8,NI8,NM8,NQ8,NU8,NY8,OC8,OG8,OK8,OO8,OS8,OW8,PA8,PE8,PI8,PM8,PQ8)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH8" t="e">
@@ -3322,23 +3254,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS8" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT8" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU8" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -3347,83 +3279,83 @@
         <v>118</v>
       </c>
       <c r="B9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J9" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M9" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N9" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U9" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V9" s="3">
@@ -3431,11 +3363,11 @@
         <v>0</v>
       </c>
       <c r="W9" s="3">
-        <f>SUM(AK9,AO9,AS9,AW9,BA9,BE9,BI9,BM9,BQ9,BU9,BY9,CC9,CG9,CK9,CO9,CS9,CW9,DA9,DE9,DI9,DM9,DQ9,DU9,DY9,EC9,EG9,EK9,EO9,ES9,EW9,FA9,FE9,FI9,FM9,FQ9,FU9,FY9,GC9,GG9,GK9,GO9,GS9,GW9,HA9,HE9,HI9,HM9,HQ9,HU9,HY9,IC9,IG9,IK9,IO9,IS9,IW9,JA9,JE9,JI9,JM9,JQ9,JU9,JY9,KC9,KG9,KK9,KO9,KS9,KW9,LA9,LE9,LI9,LM9,LQ9,LU9,LY9,MC9,MH9,MK9,MO9,MS9,MW9,NA9,NE9,NI9,NM9,NQ9,NU9,NY9,OC9,OG9,OK9,OO9,OS9,OW9,PA9,PE9,PI9,PM9,PQ9)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X9" s="4">
-        <f>SUM(DA9,DE9,DI9,DM9,DQ9,DU9,DY9,EC9,EG9,EK9,EO9,ES9,EW9,FA9,FE9,FI9,FM9,FQ9,FU9,FY9,GC9,GG9,GK9,GO9,GS9,GW9,HA9,HE9,HI9,HM9,HQ9,HU9,HY9,IC9,IG9,IK9,IO9,IS9,IW9,JA9,JE9,JI9,JM9,JQ9,JU9,JY9,KC9,KG9,KK9,KO9,KS9,KW9,LA9,LE9,LI9,LM9,LQ9,LU9,LY9,MC9,MH9,MK9,MO9,MS9,MW9,NA9,NE9,NI9,NM9,NQ9,NU9,NY9,OC9,OG9,OK9,OO9,OS9,OW9,PA9,PE9,PI9,PM9,PQ9)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y9" s="4" t="e">
@@ -3447,31 +3379,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>SUM(IW9,JA9,JE9,JI9,JM9,JQ9,JU9,JY9,KC9,KG9,KK9,KO9,KS9,KW9,LA9,LE9,LI9,LM9,LQ9,LU9,LY9,MC9,MH9,MK9,MO9,MS9,MW9,NA9,NE9,NI9,NM9,NQ9,NU9,NY9,OC9,OG9,OK9,OO9,OS9,OW9,PA9,PE9,PI9,PM9,PQ9)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH9" t="e">
@@ -3479,23 +3411,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS9" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT9" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU9" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -3504,83 +3436,83 @@
         <v>132</v>
       </c>
       <c r="B10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L10" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N10" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q10" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T10" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U10" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V10" s="3">
@@ -3588,11 +3520,11 @@
         <v>0</v>
       </c>
       <c r="W10" s="3">
-        <f>SUM(AK10,AO10,AS10,AW10,BA10,BE10,BI10,BM10,BQ10,BU10,BY10,CC10,CG10,CK10,CO10,CS10,CW10,DA10,DE10,DI10,DM10,DQ10,DU10,DY10,EC10,EG10,EK10,EO10,ES10,EW10,FA10,FE10,FI10,FM10,FQ10,FU10,FY10,GC10,GG10,GK10,GO10,GS10,GW10,HA10,HE10,HI10,HM10,HQ10,HU10,HY10,IC10,IG10,IK10,IO10,IS10,IW10,JA10,JE10,JI10,JM10,JQ10,JU10,JY10,KC10,KG10,KK10,KO10,KS10,KW10,LA10,LE10,LI10,LM10,LQ10,LU10,LY10,MC10,MH10,MK10,MO10,MS10,MW10,NA10,NE10,NI10,NM10,NQ10,NU10,NY10,OC10,OG10,OK10,OO10,OS10,OW10,PA10,PE10,PI10,PM10,PQ10)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X10" s="4">
-        <f>SUM(DA10,DE10,DI10,DM10,DQ10,DU10,DY10,EC10,EG10,EK10,EO10,ES10,EW10,FA10,FE10,FI10,FM10,FQ10,FU10,FY10,GC10,GG10,GK10,GO10,GS10,GW10,HA10,HE10,HI10,HM10,HQ10,HU10,HY10,IC10,IG10,IK10,IO10,IS10,IW10,JA10,JE10,JI10,JM10,JQ10,JU10,JY10,KC10,KG10,KK10,KO10,KS10,KW10,LA10,LE10,LI10,LM10,LQ10,LU10,LY10,MC10,MH10,MK10,MO10,MS10,MW10,NA10,NE10,NI10,NM10,NQ10,NU10,NY10,OC10,OG10,OK10,OO10,OS10,OW10,PA10,PE10,PI10,PM10,PQ10)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y10" s="4" t="e">
@@ -3604,31 +3536,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>SUM(IW10,JA10,JE10,JI10,JM10,JQ10,JU10,JY10,KC10,KG10,KK10,KO10,KS10,KW10,LA10,LE10,LI10,LM10,LQ10,LU10,LY10,MC10,MH10,MK10,MO10,MS10,MW10,NA10,NE10,NI10,NM10,NQ10,NU10,NY10,OC10,OG10,OK10,OO10,OS10,OW10,PA10,PE10,PI10,PM10,PQ10)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH10" t="e">
@@ -3636,23 +3568,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS10" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT10" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU10" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -3661,83 +3593,83 @@
         <v>113</v>
       </c>
       <c r="B11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L11" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P11" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q11" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R11" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T11" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U11" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V11" s="3">
@@ -3745,11 +3677,11 @@
         <v>0</v>
       </c>
       <c r="W11" s="3">
-        <f>SUM(AK11,AO11,AS11,AW11,BA11,BE11,BI11,BM11,BQ11,BU11,BY11,CC11,CG11,CK11,CO11,CS11,CW11,DA11,DE11,DI11,DM11,DQ11,DU11,DY11,EC11,EG11,EK11,EO11,ES11,EW11,FA11,FE11,FI11,FM11,FQ11,FU11,FY11,GC11,GG11,GK11,GO11,GS11,GW11,HA11,HE11,HI11,HM11,HQ11,HU11,HY11,IC11,IG11,IK11,IO11,IS11,IW11,JA11,JE11,JI11,JM11,JQ11,JU11,JY11,KC11,KG11,KK11,KO11,KS11,KW11,LA11,LE11,LI11,LM11,LQ11,LU11,LY11,MC11,MH11,MK11,MO11,MS11,MW11,NA11,NE11,NI11,NM11,NQ11,NU11,NY11,OC11,OG11,OK11,OO11,OS11,OW11,PA11,PE11,PI11,PM11,PQ11)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X11" s="4">
-        <f>SUM(DA11,DE11,DI11,DM11,DQ11,DU11,DY11,EC11,EG11,EK11,EO11,ES11,EW11,FA11,FE11,FI11,FM11,FQ11,FU11,FY11,GC11,GG11,GK11,GO11,GS11,GW11,HA11,HE11,HI11,HM11,HQ11,HU11,HY11,IC11,IG11,IK11,IO11,IS11,IW11,JA11,JE11,JI11,JM11,JQ11,JU11,JY11,KC11,KG11,KK11,KO11,KS11,KW11,LA11,LE11,LI11,LM11,LQ11,LU11,LY11,MC11,MH11,MK11,MO11,MS11,MW11,NA11,NE11,NI11,NM11,NQ11,NU11,NY11,OC11,OG11,OK11,OO11,OS11,OW11,PA11,PE11,PI11,PM11,PQ11)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y11" s="4" t="e">
@@ -3761,31 +3693,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>SUM(IW11,JA11,JE11,JI11,JM11,JQ11,JU11,JY11,KC11,KG11,KK11,KO11,KS11,KW11,LA11,LE11,LI11,LM11,LQ11,LU11,LY11,MC11,MH11,MK11,MO11,MS11,MW11,NA11,NE11,NI11,NM11,NQ11,NU11,NY11,OC11,OG11,OK11,OO11,OS11,OW11,PA11,PE11,PI11,PM11,PQ11)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH11" t="e">
@@ -3793,23 +3725,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS11" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT11" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU11" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -3818,83 +3750,83 @@
         <v>114</v>
       </c>
       <c r="B12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V12" s="3">
@@ -3902,11 +3834,11 @@
         <v>0</v>
       </c>
       <c r="W12" s="3">
-        <f>SUM(AK12,AO12,AS12,AW12,BA12,BE12,BI12,BM12,BQ12,BU12,BY12,CC12,CG12,CK12,CO12,CS12,CW12,DA12,DE12,DI12,DM12,DQ12,DU12,DY12,EC12,EG12,EK12,EO12,ES12,EW12,FA12,FE12,FI12,FM12,FQ12,FU12,FY12,GC12,GG12,GK12,GO12,GS12,GW12,HA12,HE12,HI12,HM12,HQ12,HU12,HY12,IC12,IG12,IK12,IO12,IS12,IW12,JA12,JE12,JI12,JM12,JQ12,JU12,JY12,KC12,KG12,KK12,KO12,KS12,KW12,LA12,LE12,LI12,LM12,LQ12,LU12,LY12,MC12,MH12,MK12,MO12,MS12,MW12,NA12,NE12,NI12,NM12,NQ12,NU12,NY12,OC12,OG12,OK12,OO12,OS12,OW12,PA12,PE12,PI12,PM12,PQ12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X12" s="4">
-        <f>SUM(DA12,DE12,DI12,DM12,DQ12,DU12,DY12,EC12,EG12,EK12,EO12,ES12,EW12,FA12,FE12,FI12,FM12,FQ12,FU12,FY12,GC12,GG12,GK12,GO12,GS12,GW12,HA12,HE12,HI12,HM12,HQ12,HU12,HY12,IC12,IG12,IK12,IO12,IS12,IW12,JA12,JE12,JI12,JM12,JQ12,JU12,JY12,KC12,KG12,KK12,KO12,KS12,KW12,LA12,LE12,LI12,LM12,LQ12,LU12,LY12,MC12,MH12,MK12,MO12,MS12,MW12,NA12,NE12,NI12,NM12,NQ12,NU12,NY12,OC12,OG12,OK12,OO12,OS12,OW12,PA12,PE12,PI12,PM12,PQ12)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y12" s="4" t="e">
@@ -3918,31 +3850,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>SUM(IW12,JA12,JE12,JI12,JM12,JQ12,JU12,JY12,KC12,KG12,KK12,KO12,KS12,KW12,LA12,LE12,LI12,LM12,LQ12,LU12,LY12,MC12,MH12,MK12,MO12,MS12,MW12,NA12,NE12,NI12,NM12,NQ12,NU12,NY12,OC12,OG12,OK12,OO12,OS12,OW12,PA12,PE12,PI12,PM12,PQ12)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH12" t="e">
@@ -3950,23 +3882,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS12" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU12" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -3975,83 +3907,83 @@
         <v>127</v>
       </c>
       <c r="B13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I13" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L13" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M13" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N13" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P13" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q13" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T13" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U13" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V13" s="3">
@@ -4059,11 +3991,11 @@
         <v>0</v>
       </c>
       <c r="W13" s="3">
-        <f>SUM(AK13,AO13,AS13,AW13,BA13,BE13,BI13,BM13,BQ13,BU13,BY13,CC13,CG13,CK13,CO13,CS13,CW13,DA13,DE13,DI13,DM13,DQ13,DU13,DY13,EC13,EG13,EK13,EO13,ES13,EW13,FA13,FE13,FI13,FM13,FQ13,FU13,FY13,GC13,GG13,GK13,GO13,GS13,GW13,HA13,HE13,HI13,HM13,HQ13,HU13,HY13,IC13,IG13,IK13,IO13,IS13,IW13,JA13,JE13,JI13,JM13,JQ13,JU13,JY13,KC13,KG13,KK13,KO13,KS13,KW13,LA13,LE13,LI13,LM13,LQ13,LU13,LY13,MC13,MH13,MK13,MO13,MS13,MW13,NA13,NE13,NI13,NM13,NQ13,NU13,NY13,OC13,OG13,OK13,OO13,OS13,OW13,PA13,PE13,PI13,PM13,PQ13)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X13" s="4">
-        <f>SUM(DA13,DE13,DI13,DM13,DQ13,DU13,DY13,EC13,EG13,EK13,EO13,ES13,EW13,FA13,FE13,FI13,FM13,FQ13,FU13,FY13,GC13,GG13,GK13,GO13,GS13,GW13,HA13,HE13,HI13,HM13,HQ13,HU13,HY13,IC13,IG13,IK13,IO13,IS13,IW13,JA13,JE13,JI13,JM13,JQ13,JU13,JY13,KC13,KG13,KK13,KO13,KS13,KW13,LA13,LE13,LI13,LM13,LQ13,LU13,LY13,MC13,MH13,MK13,MO13,MS13,MW13,NA13,NE13,NI13,NM13,NQ13,NU13,NY13,OC13,OG13,OK13,OO13,OS13,OW13,PA13,PE13,PI13,PM13,PQ13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y13" s="4" t="e">
@@ -4075,31 +4007,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>SUM(IW13,JA13,JE13,JI13,JM13,JQ13,JU13,JY13,KC13,KG13,KK13,KO13,KS13,KW13,LA13,LE13,LI13,LM13,LQ13,LU13,LY13,MC13,MH13,MK13,MO13,MS13,MW13,NA13,NE13,NI13,NM13,NQ13,NU13,NY13,OC13,OG13,OK13,OO13,OS13,OW13,PA13,PE13,PI13,PM13,PQ13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH13" t="e">
@@ -4107,23 +4039,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS13" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT13" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU13" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -4132,83 +4064,83 @@
         <v>115</v>
       </c>
       <c r="B14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M14" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N14" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q14" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R14" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T14" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U14" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V14" s="3">
@@ -4216,11 +4148,11 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
-        <f>SUM(AK14,AO14,AS14,AW14,BA14,BE14,BI14,BM14,BQ14,BU14,BY14,CC14,CG14,CK14,CO14,CS14,CW14,DA14,DE14,DI14,DM14,DQ14,DU14,DY14,EC14,EG14,EK14,EO14,ES14,EW14,FA14,FE14,FI14,FM14,FQ14,FU14,FY14,GC14,GG14,GK14,GO14,GS14,GW14,HA14,HE14,HI14,HM14,HQ14,HU14,HY14,IC14,IG14,IK14,IO14,IS14,IW14,JA14,JE14,JI14,JM14,JQ14,JU14,JY14,KC14,KG14,KK14,KO14,KS14,KW14,LA14,LE14,LI14,LM14,LQ14,LU14,LY14,MC14,MH14,MK14,MO14,MS14,MW14,NA14,NE14,NI14,NM14,NQ14,NU14,NY14,OC14,OG14,OK14,OO14,OS14,OW14,PA14,PE14,PI14,PM14,PQ14)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X14" s="4">
-        <f>SUM(DA14,DE14,DI14,DM14,DQ14,DU14,DY14,EC14,EG14,EK14,EO14,ES14,EW14,FA14,FE14,FI14,FM14,FQ14,FU14,FY14,GC14,GG14,GK14,GO14,GS14,GW14,HA14,HE14,HI14,HM14,HQ14,HU14,HY14,IC14,IG14,IK14,IO14,IS14,IW14,JA14,JE14,JI14,JM14,JQ14,JU14,JY14,KC14,KG14,KK14,KO14,KS14,KW14,LA14,LE14,LI14,LM14,LQ14,LU14,LY14,MC14,MH14,MK14,MO14,MS14,MW14,NA14,NE14,NI14,NM14,NQ14,NU14,NY14,OC14,OG14,OK14,OO14,OS14,OW14,PA14,PE14,PI14,PM14,PQ14)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y14" s="4" t="e">
@@ -4232,31 +4164,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f>SUM(IW14,JA14,JE14,JI14,JM14,JQ14,JU14,JY14,KC14,KG14,KK14,KO14,KS14,KW14,LA14,LE14,LI14,LM14,LQ14,LU14,LY14,MC14,MH14,MK14,MO14,MS14,MW14,NA14,NE14,NI14,NM14,NQ14,NU14,NY14,OC14,OG14,OK14,OO14,OS14,OW14,PA14,PE14,PI14,PM14,PQ14)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH14" t="e">
@@ -4264,23 +4196,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS14" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT14" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU14" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -4289,83 +4221,83 @@
         <v>133</v>
       </c>
       <c r="B15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N15" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q15" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R15" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T15" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U15" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V15" s="3">
@@ -4373,11 +4305,11 @@
         <v>0</v>
       </c>
       <c r="W15" s="3">
-        <f>SUM(AK15,AO15,AS15,AW15,BA15,BE15,BI15,BM15,BQ15,BU15,BY15,CC15,CG15,CK15,CO15,CS15,CW15,DA15,DE15,DI15,DM15,DQ15,DU15,DY15,EC15,EG15,EK15,EO15,ES15,EW15,FA15,FE15,FI15,FM15,FQ15,FU15,FY15,GC15,GG15,GK15,GO15,GS15,GW15,HA15,HE15,HI15,HM15,HQ15,HU15,HY15,IC15,IG15,IK15,IO15,IS15,IW15,JA15,JE15,JI15,JM15,JQ15,JU15,JY15,KC15,KG15,KK15,KO15,KS15,KW15,LA15,LE15,LI15,LM15,LQ15,LU15,LY15,MC15,MH15,MK15,MO15,MS15,MW15,NA15,NE15,NI15,NM15,NQ15,NU15,NY15,OC15,OG15,OK15,OO15,OS15,OW15,PA15,PE15,PI15,PM15,PQ15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X15" s="4">
-        <f>SUM(DA15,DE15,DI15,DM15,DQ15,DU15,DY15,EC15,EG15,EK15,EO15,ES15,EW15,FA15,FE15,FI15,FM15,FQ15,FU15,FY15,GC15,GG15,GK15,GO15,GS15,GW15,HA15,HE15,HI15,HM15,HQ15,HU15,HY15,IC15,IG15,IK15,IO15,IS15,IW15,JA15,JE15,JI15,JM15,JQ15,JU15,JY15,KC15,KG15,KK15,KO15,KS15,KW15,LA15,LE15,LI15,LM15,LQ15,LU15,LY15,MC15,MH15,MK15,MO15,MS15,MW15,NA15,NE15,NI15,NM15,NQ15,NU15,NY15,OC15,OG15,OK15,OO15,OS15,OW15,PA15,PE15,PI15,PM15,PQ15)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y15" s="4" t="e">
@@ -4389,31 +4321,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f>SUM(IW15,JA15,JE15,JI15,JM15,JQ15,JU15,JY15,KC15,KG15,KK15,KO15,KS15,KW15,LA15,LE15,LI15,LM15,LQ15,LU15,LY15,MC15,MH15,MK15,MO15,MS15,MW15,NA15,NE15,NI15,NM15,NQ15,NU15,NY15,OC15,OG15,OK15,OO15,OS15,OW15,PA15,PE15,PI15,PM15,PQ15)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH15" t="e">
@@ -4421,23 +4353,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS15" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT15" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU15" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -4446,83 +4378,83 @@
         <v>134</v>
       </c>
       <c r="B16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I16" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N16" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P16" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q16" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T16" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U16" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V16" s="3">
@@ -4530,11 +4462,11 @@
         <v>0</v>
       </c>
       <c r="W16" s="3">
-        <f>SUM(AK16,AO16,AS16,AW16,BA16,BE16,BI16,BM16,BQ16,BU16,BY16,CC16,CG16,CK16,CO16,CS16,CW16,DA16,DE16,DI16,DM16,DQ16,DU16,DY16,EC16,EG16,EK16,EO16,ES16,EW16,FA16,FE16,FI16,FM16,FQ16,FU16,FY16,GC16,GG16,GK16,GO16,GS16,GW16,HA16,HE16,HI16,HM16,HQ16,HU16,HY16,IC16,IG16,IK16,IO16,IS16,IW16,JA16,JE16,JI16,JM16,JQ16,JU16,JY16,KC16,KG16,KK16,KO16,KS16,KW16,LA16,LE16,LI16,LM16,LQ16,LU16,LY16,MC16,MH16,MK16,MO16,MS16,MW16,NA16,NE16,NI16,NM16,NQ16,NU16,NY16,OC16,OG16,OK16,OO16,OS16,OW16,PA16,PE16,PI16,PM16,PQ16)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X16" s="4">
-        <f>SUM(DA16,DE16,DI16,DM16,DQ16,DU16,DY16,EC16,EG16,EK16,EO16,ES16,EW16,FA16,FE16,FI16,FM16,FQ16,FU16,FY16,GC16,GG16,GK16,GO16,GS16,GW16,HA16,HE16,HI16,HM16,HQ16,HU16,HY16,IC16,IG16,IK16,IO16,IS16,IW16,JA16,JE16,JI16,JM16,JQ16,JU16,JY16,KC16,KG16,KK16,KO16,KS16,KW16,LA16,LE16,LI16,LM16,LQ16,LU16,LY16,MC16,MH16,MK16,MO16,MS16,MW16,NA16,NE16,NI16,NM16,NQ16,NU16,NY16,OC16,OG16,OK16,OO16,OS16,OW16,PA16,PE16,PI16,PM16,PQ16)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y16" s="4" t="e">
@@ -4546,31 +4478,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f>SUM(IW16,JA16,JE16,JI16,JM16,JQ16,JU16,JY16,KC16,KG16,KK16,KO16,KS16,KW16,LA16,LE16,LI16,LM16,LQ16,LU16,LY16,MC16,MH16,MK16,MO16,MS16,MW16,NA16,NE16,NI16,NM16,NQ16,NU16,NY16,OC16,OG16,OK16,OO16,OS16,OW16,PA16,PE16,PI16,PM16,PQ16)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH16" t="e">
@@ -4578,23 +4510,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS16" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT16" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU16" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW16">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -4603,83 +4535,83 @@
         <v>135</v>
       </c>
       <c r="B17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M17" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P17" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q17" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R17" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T17" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U17" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V17" s="3">
@@ -4687,11 +4619,11 @@
         <v>0</v>
       </c>
       <c r="W17" s="3">
-        <f>SUM(AK17,AO17,AS17,AW17,BA17,BE17,BI17,BM17,BQ17,BU17,BY17,CC17,CG17,CK17,CO17,CS17,CW17,DA17,DE17,DI17,DM17,DQ17,DU17,DY17,EC17,EG17,EK17,EO17,ES17,EW17,FA17,FE17,FI17,FM17,FQ17,FU17,FY17,GC17,GG17,GK17,GO17,GS17,GW17,HA17,HE17,HI17,HM17,HQ17,HU17,HY17,IC17,IG17,IK17,IO17,IS17,IW17,JA17,JE17,JI17,JM17,JQ17,JU17,JY17,KC17,KG17,KK17,KO17,KS17,KW17,LA17,LE17,LI17,LM17,LQ17,LU17,LY17,MC17,MH17,MK17,MO17,MS17,MW17,NA17,NE17,NI17,NM17,NQ17,NU17,NY17,OC17,OG17,OK17,OO17,OS17,OW17,PA17,PE17,PI17,PM17,PQ17)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X17" s="4">
-        <f>SUM(DA17,DE17,DI17,DM17,DQ17,DU17,DY17,EC17,EG17,EK17,EO17,ES17,EW17,FA17,FE17,FI17,FM17,FQ17,FU17,FY17,GC17,GG17,GK17,GO17,GS17,GW17,HA17,HE17,HI17,HM17,HQ17,HU17,HY17,IC17,IG17,IK17,IO17,IS17,IW17,JA17,JE17,JI17,JM17,JQ17,JU17,JY17,KC17,KG17,KK17,KO17,KS17,KW17,LA17,LE17,LI17,LM17,LQ17,LU17,LY17,MC17,MH17,MK17,MO17,MS17,MW17,NA17,NE17,NI17,NM17,NQ17,NU17,NY17,OC17,OG17,OK17,OO17,OS17,OW17,PA17,PE17,PI17,PM17,PQ17)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y17" s="4" t="e">
@@ -4703,31 +4635,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f>SUM(IW17,JA17,JE17,JI17,JM17,JQ17,JU17,JY17,KC17,KG17,KK17,KO17,KS17,KW17,LA17,LE17,LI17,LM17,LQ17,LU17,LY17,MC17,MH17,MK17,MO17,MS17,MW17,NA17,NE17,NI17,NM17,NQ17,NU17,NY17,OC17,OG17,OK17,OO17,OS17,OW17,PA17,PE17,PI17,PM17,PQ17)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH17" t="e">
@@ -4735,23 +4667,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS17" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT17" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU17" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -4760,83 +4692,83 @@
         <v>119</v>
       </c>
       <c r="B18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L18" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M18" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N18" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O18">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P18" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q18" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R18" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T18" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U18" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V18" s="3">
@@ -4844,11 +4776,11 @@
         <v>0</v>
       </c>
       <c r="W18" s="3">
-        <f>SUM(AK18,AO18,AS18,AW18,BA18,BE18,BI18,BM18,BQ18,BU18,BY18,CC18,CG18,CK18,CO18,CS18,CW18,DA18,DE18,DI18,DM18,DQ18,DU18,DY18,EC18,EG18,EK18,EO18,ES18,EW18,FA18,FE18,FI18,FM18,FQ18,FU18,FY18,GC18,GG18,GK18,GO18,GS18,GW18,HA18,HE18,HI18,HM18,HQ18,HU18,HY18,IC18,IG18,IK18,IO18,IS18,IW18,JA18,JE18,JI18,JM18,JQ18,JU18,JY18,KC18,KG18,KK18,KO18,KS18,KW18,LA18,LE18,LI18,LM18,LQ18,LU18,LY18,MC18,MH18,MK18,MO18,MS18,MW18,NA18,NE18,NI18,NM18,NQ18,NU18,NY18,OC18,OG18,OK18,OO18,OS18,OW18,PA18,PE18,PI18,PM18,PQ18)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X18" s="4">
-        <f>SUM(DA18,DE18,DI18,DM18,DQ18,DU18,DY18,EC18,EG18,EK18,EO18,ES18,EW18,FA18,FE18,FI18,FM18,FQ18,FU18,FY18,GC18,GG18,GK18,GO18,GS18,GW18,HA18,HE18,HI18,HM18,HQ18,HU18,HY18,IC18,IG18,IK18,IO18,IS18,IW18,JA18,JE18,JI18,JM18,JQ18,JU18,JY18,KC18,KG18,KK18,KO18,KS18,KW18,LA18,LE18,LI18,LM18,LQ18,LU18,LY18,MC18,MH18,MK18,MO18,MS18,MW18,NA18,NE18,NI18,NM18,NQ18,NU18,NY18,OC18,OG18,OK18,OO18,OS18,OW18,PA18,PE18,PI18,PM18,PQ18)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y18" s="4" t="e">
@@ -4860,31 +4792,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG18">
-        <f>SUM(IW18,JA18,JE18,JI18,JM18,JQ18,JU18,JY18,KC18,KG18,KK18,KO18,KS18,KW18,LA18,LE18,LI18,LM18,LQ18,LU18,LY18,MC18,MH18,MK18,MO18,MS18,MW18,NA18,NE18,NI18,NM18,NQ18,NU18,NY18,OC18,OG18,OK18,OO18,OS18,OW18,PA18,PE18,PI18,PM18,PQ18)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH18" t="e">
@@ -4892,23 +4824,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS18" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT18" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU18" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -4917,71 +4849,71 @@
         <v>117</v>
       </c>
       <c r="B19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L19" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M19" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q19" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S19">
@@ -4989,11 +4921,11 @@
         <v>0</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U19" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V19" s="3">
@@ -5001,11 +4933,11 @@
         <v>0</v>
       </c>
       <c r="W19" s="3">
-        <f>SUM(AK19,AO19,AS19,AW19,BA19,BE19,BI19,BM19,BQ19,BU19,BY19,CC19,CG19,CK19,CO19,CS19,CW19,DA19,DE19,DI19,DM19,DQ19,DU19,DY19,EC19,EG19,EK19,EO19,ES19,EW19,FA19,FE19,FI19,FM19,FQ19,FU19,FY19,GC19,GG19,GK19,GO19,GS19,GW19,HA19,HE19,HI19,HM19,HQ19,HU19,HY19,IC19,IG19,IK19,IO19,IS19,IW19,JA19,JE19,JI19,JM19,JQ19,JU19,JY19,KC19,KG19,KK19,KO19,KS19,KW19,LA19,LE19,LI19,LM19,LQ19,LU19,LY19,MC19,MH19,MK19,MO19,MS19,MW19,NA19,NE19,NI19,NM19,NQ19,NU19,NY19,OC19,OG19,OK19,OO19,OS19,OW19,PA19,PE19,PI19,PM19,PQ19)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X19" s="4">
-        <f>SUM(DA19,DE19,DI19,DM19,DQ19,DU19,DY19,EC19,EG19,EK19,EO19,ES19,EW19,FA19,FE19,FI19,FM19,FQ19,FU19,FY19,GC19,GG19,GK19,GO19,GS19,GW19,HA19,HE19,HI19,HM19,HQ19,HU19,HY19,IC19,IG19,IK19,IO19,IS19,IW19,JA19,JE19,JI19,JM19,JQ19,JU19,JY19,KC19,KG19,KK19,KO19,KS19,KW19,LA19,LE19,LI19,LM19,LQ19,LU19,LY19,MC19,MH19,MK19,MO19,MS19,MW19,NA19,NE19,NI19,NM19,NQ19,NU19,NY19,OC19,OG19,OK19,OO19,OS19,OW19,PA19,PE19,PI19,PM19,PQ19)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y19" s="4" t="e">
@@ -5017,31 +4949,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG19">
-        <f>SUM(IW19,JA19,JE19,JI19,JM19,JQ19,JU19,JY19,KC19,KG19,KK19,KO19,KS19,KW19,LA19,LE19,LI19,LM19,LQ19,LU19,LY19,MC19,MH19,MK19,MO19,MS19,MW19,NA19,NE19,NI19,NM19,NQ19,NU19,NY19,OC19,OG19,OK19,OO19,OS19,OW19,PA19,PE19,PI19,PM19,PQ19)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH19" t="e">
@@ -5049,23 +4981,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS19" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT19" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -5074,83 +5006,83 @@
         <v>136</v>
       </c>
       <c r="B20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V20" s="3">
@@ -5158,11 +5090,11 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <f>SUM(AK20,AO20,AS20,AW20,BA20,BE20,BI20,BM20,BQ20,BU20,BY20,CC20,CG20,CK20,CO20,CS20,CW20,DA20,DE20,DI20,DM20,DQ20,DU20,DY20,EC20,EG20,EK20,EO20,ES20,EW20,FA20,FE20,FI20,FM20,FQ20,FU20,FY20,GC20,GG20,GK20,GO20,GS20,GW20,HA20,HE20,HI20,HM20,HQ20,HU20,HY20,IC20,IG20,IK20,IO20,IS20,IW20,JA20,JE20,JI20,JM20,JQ20,JU20,JY20,KC20,KG20,KK20,KO20,KS20,KW20,LA20,LE20,LI20,LM20,LQ20,LU20,LY20,MC20,MH20,MK20,MO20,MS20,MW20,NA20,NE20,NI20,NM20,NQ20,NU20,NY20,OC20,OG20,OK20,OO20,OS20,OW20,PA20,PE20,PI20,PM20,PQ20)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X20" s="4">
-        <f>SUM(DA20,DE20,DI20,DM20,DQ20,DU20,DY20,EC20,EG20,EK20,EO20,ES20,EW20,FA20,FE20,FI20,FM20,FQ20,FU20,FY20,GC20,GG20,GK20,GO20,GS20,GW20,HA20,HE20,HI20,HM20,HQ20,HU20,HY20,IC20,IG20,IK20,IO20,IS20,IW20,JA20,JE20,JI20,JM20,JQ20,JU20,JY20,KC20,KG20,KK20,KO20,KS20,KW20,LA20,LE20,LI20,LM20,LQ20,LU20,LY20,MC20,MH20,MK20,MO20,MS20,MW20,NA20,NE20,NI20,NM20,NQ20,NU20,NY20,OC20,OG20,OK20,OO20,OS20,OW20,PA20,PE20,PI20,PM20,PQ20)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y20" s="4" t="e">
@@ -5174,31 +5106,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD20">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG20">
-        <f>SUM(IW20,JA20,JE20,JI20,JM20,JQ20,JU20,JY20,KC20,KG20,KK20,KO20,KS20,KW20,LA20,LE20,LI20,LM20,LQ20,LU20,LY20,MC20,MH20,MK20,MO20,MS20,MW20,NA20,NE20,NI20,NM20,NQ20,NU20,NY20,OC20,OG20,OK20,OO20,OS20,OW20,PA20,PE20,PI20,PM20,PQ20)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH20" t="e">
@@ -5206,23 +5138,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS20" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT20" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU20" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -5231,83 +5163,83 @@
         <v>137</v>
       </c>
       <c r="B21">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L21" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N21" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P21" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T21" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U21" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V21" s="3">
@@ -5315,11 +5247,11 @@
         <v>0</v>
       </c>
       <c r="W21" s="3">
-        <f>SUM(AK21,AO21,AS21,AW21,BA21,BE21,BI21,BM21,BQ21,BU21,BY21,CC21,CG21,CK21,CO21,CS21,CW21,DA21,DE21,DI21,DM21,DQ21,DU21,DY21,EC21,EG21,EK21,EO21,ES21,EW21,FA21,FE21,FI21,FM21,FQ21,FU21,FY21,GC21,GG21,GK21,GO21,GS21,GW21,HA21,HE21,HI21,HM21,HQ21,HU21,HY21,IC21,IG21,IK21,IO21,IS21,IW21,JA21,JE21,JI21,JM21,JQ21,JU21,JY21,KC21,KG21,KK21,KO21,KS21,KW21,LA21,LE21,LI21,LM21,LQ21,LU21,LY21,MC21,MH21,MK21,MO21,MS21,MW21,NA21,NE21,NI21,NM21,NQ21,NU21,NY21,OC21,OG21,OK21,OO21,OS21,OW21,PA21,PE21,PI21,PM21,PQ21)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X21" s="4">
-        <f>SUM(DA21,DE21,DI21,DM21,DQ21,DU21,DY21,EC21,EG21,EK21,EO21,ES21,EW21,FA21,FE21,FI21,FM21,FQ21,FU21,FY21,GC21,GG21,GK21,GO21,GS21,GW21,HA21,HE21,HI21,HM21,HQ21,HU21,HY21,IC21,IG21,IK21,IO21,IS21,IW21,JA21,JE21,JI21,JM21,JQ21,JU21,JY21,KC21,KG21,KK21,KO21,KS21,KW21,LA21,LE21,LI21,LM21,LQ21,LU21,LY21,MC21,MH21,MK21,MO21,MS21,MW21,NA21,NE21,NI21,NM21,NQ21,NU21,NY21,OC21,OG21,OK21,OO21,OS21,OW21,PA21,PE21,PI21,PM21,PQ21)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y21" s="4" t="e">
@@ -5331,31 +5263,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF21">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG21">
-        <f>SUM(IW21,JA21,JE21,JI21,JM21,JQ21,JU21,JY21,KC21,KG21,KK21,KO21,KS21,KW21,LA21,LE21,LI21,LM21,LQ21,LU21,LY21,MC21,MH21,MK21,MO21,MS21,MW21,NA21,NE21,NI21,NM21,NQ21,NU21,NY21,OC21,OG21,OK21,OO21,OS21,OW21,PA21,PE21,PI21,PM21,PQ21)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH21" t="e">
@@ -5363,23 +5295,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS21" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT21" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU21" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW21">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -5388,83 +5320,83 @@
         <v>138</v>
       </c>
       <c r="B22">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T22" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U22" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V22" s="3">
@@ -5472,11 +5404,11 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
-        <f>SUM(AK22,AO22,AS22,AW22,BA22,BE22,BI22,BM22,BQ22,BU22,BY22,CC22,CG22,CK22,CO22,CS22,CW22,DA22,DE22,DI22,DM22,DQ22,DU22,DY22,EC22,EG22,EK22,EO22,ES22,EW22,FA22,FE22,FI22,FM22,FQ22,FU22,FY22,GC22,GG22,GK22,GO22,GS22,GW22,HA22,HE22,HI22,HM22,HQ22,HU22,HY22,IC22,IG22,IK22,IO22,IS22,IW22,JA22,JE22,JI22,JM22,JQ22,JU22,JY22,KC22,KG22,KK22,KO22,KS22,KW22,LA22,LE22,LI22,LM22,LQ22,LU22,LY22,MC22,MH22,MK22,MO22,MS22,MW22,NA22,NE22,NI22,NM22,NQ22,NU22,NY22,OC22,OG22,OK22,OO22,OS22,OW22,PA22,PE22,PI22,PM22,PQ22)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X22" s="4">
-        <f>SUM(DA22,DE22,DI22,DM22,DQ22,DU22,DY22,EC22,EG22,EK22,EO22,ES22,EW22,FA22,FE22,FI22,FM22,FQ22,FU22,FY22,GC22,GG22,GK22,GO22,GS22,GW22,HA22,HE22,HI22,HM22,HQ22,HU22,HY22,IC22,IG22,IK22,IO22,IS22,IW22,JA22,JE22,JI22,JM22,JQ22,JU22,JY22,KC22,KG22,KK22,KO22,KS22,KW22,LA22,LE22,LI22,LM22,LQ22,LU22,LY22,MC22,MH22,MK22,MO22,MS22,MW22,NA22,NE22,NI22,NM22,NQ22,NU22,NY22,OC22,OG22,OK22,OO22,OS22,OW22,PA22,PE22,PI22,PM22,PQ22)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y22" s="4" t="e">
@@ -5488,31 +5420,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE22">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF22">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG22">
-        <f>SUM(IW22,JA22,JE22,JI22,JM22,JQ22,JU22,JY22,KC22,KG22,KK22,KO22,KS22,KW22,LA22,LE22,LI22,LM22,LQ22,LU22,LY22,MC22,MH22,MK22,MO22,MS22,MW22,NA22,NE22,NI22,NM22,NQ22,NU22,NY22,OC22,OG22,OK22,OO22,OS22,OW22,PA22,PE22,PI22,PM22,PQ22)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH22" t="e">
@@ -5520,23 +5452,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS22" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT22" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU22" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW22">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -5545,83 +5477,83 @@
         <v>139</v>
       </c>
       <c r="B23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M23" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N23" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P23" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R23" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U23" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V23" s="3">
@@ -5629,11 +5561,11 @@
         <v>0</v>
       </c>
       <c r="W23" s="3">
-        <f>SUM(AK23,AO23,AS23,AW23,BA23,BE23,BI23,BM23,BQ23,BU23,BY23,CC23,CG23,CK23,CO23,CS23,CW23,DA23,DE23,DI23,DM23,DQ23,DU23,DY23,EC23,EG23,EK23,EO23,ES23,EW23,FA23,FE23,FI23,FM23,FQ23,FU23,FY23,GC23,GG23,GK23,GO23,GS23,GW23,HA23,HE23,HI23,HM23,HQ23,HU23,HY23,IC23,IG23,IK23,IO23,IS23,IW23,JA23,JE23,JI23,JM23,JQ23,JU23,JY23,KC23,KG23,KK23,KO23,KS23,KW23,LA23,LE23,LI23,LM23,LQ23,LU23,LY23,MC23,MH23,MK23,MO23,MS23,MW23,NA23,NE23,NI23,NM23,NQ23,NU23,NY23,OC23,OG23,OK23,OO23,OS23,OW23,PA23,PE23,PI23,PM23,PQ23)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X23" s="4">
-        <f>SUM(DA23,DE23,DI23,DM23,DQ23,DU23,DY23,EC23,EG23,EK23,EO23,ES23,EW23,FA23,FE23,FI23,FM23,FQ23,FU23,FY23,GC23,GG23,GK23,GO23,GS23,GW23,HA23,HE23,HI23,HM23,HQ23,HU23,HY23,IC23,IG23,IK23,IO23,IS23,IW23,JA23,JE23,JI23,JM23,JQ23,JU23,JY23,KC23,KG23,KK23,KO23,KS23,KW23,LA23,LE23,LI23,LM23,LQ23,LU23,LY23,MC23,MH23,MK23,MO23,MS23,MW23,NA23,NE23,NI23,NM23,NQ23,NU23,NY23,OC23,OG23,OK23,OO23,OS23,OW23,PA23,PE23,PI23,PM23,PQ23)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y23" s="4" t="e">
@@ -5645,31 +5577,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG23">
-        <f>SUM(IW23,JA23,JE23,JI23,JM23,JQ23,JU23,JY23,KC23,KG23,KK23,KO23,KS23,KW23,LA23,LE23,LI23,LM23,LQ23,LU23,LY23,MC23,MH23,MK23,MO23,MS23,MW23,NA23,NE23,NI23,NM23,NQ23,NU23,NY23,OC23,OG23,OK23,OO23,OS23,OW23,PA23,PE23,PI23,PM23,PQ23)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH23" t="e">
@@ -5677,108 +5609,108 @@
         <v>#REF!</v>
       </c>
       <c r="PS23" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT23" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU23" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW23">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N24" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P24" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R24" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T24" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U24" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V24" s="3">
@@ -5786,11 +5718,11 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
-        <f>SUM(AK24,AO24,AS24,AW24,BA24,BE24,BI24,BM24,BQ24,BU24,BY24,CC24,CG24,CK24,CO24,CS24,CW24,DA24,DE24,DI24,DM24,DQ24,DU24,DY24,EC24,EG24,EK24,EO24,ES24,EW24,FA24,FE24,FI24,FM24,FQ24,FU24,FY24,GC24,GG24,GK24,GO24,GS24,GW24,HA24,HE24,HI24,HM24,HQ24,HU24,HY24,IC24,IG24,IK24,IO24,IS24,IW24,JA24,JE24,JI24,JM24,JQ24,JU24,JY24,KC24,KG24,KK24,KO24,KS24,KW24,LA24,LE24,LI24,LM24,LQ24,LU24,LY24,MC24,MH24,MK24,MO24,MS24,MW24,NA24,NE24,NI24,NM24,NQ24,NU24,NY24,OC24,OG24,OK24,OO24,OS24,OW24,PA24,PE24,PI24,PM24,PQ24)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X24" s="4">
-        <f>SUM(DA24,DE24,DI24,DM24,DQ24,DU24,DY24,EC24,EG24,EK24,EO24,ES24,EW24,FA24,FE24,FI24,FM24,FQ24,FU24,FY24,GC24,GG24,GK24,GO24,GS24,GW24,HA24,HE24,HI24,HM24,HQ24,HU24,HY24,IC24,IG24,IK24,IO24,IS24,IW24,JA24,JE24,JI24,JM24,JQ24,JU24,JY24,KC24,KG24,KK24,KO24,KS24,KW24,LA24,LE24,LI24,LM24,LQ24,LU24,LY24,MC24,MH24,MK24,MO24,MS24,MW24,NA24,NE24,NI24,NM24,NQ24,NU24,NY24,OC24,OG24,OK24,OO24,OS24,OW24,PA24,PE24,PI24,PM24,PQ24)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y24" s="4" t="e">
@@ -5802,31 +5734,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB24">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE24">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG24">
-        <f>SUM(IW24,JA24,JE24,JI24,JM24,JQ24,JU24,JY24,KC24,KG24,KK24,KO24,KS24,KW24,LA24,LE24,LI24,LM24,LQ24,LU24,LY24,MC24,MH24,MK24,MO24,MS24,MW24,NA24,NE24,NI24,NM24,NQ24,NU24,NY24,OC24,OG24,OK24,OO24,OS24,OW24,PA24,PE24,PI24,PM24,PQ24)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH24" t="e">
@@ -5834,108 +5766,108 @@
         <v>#REF!</v>
       </c>
       <c r="PS24" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT24" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU24" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M25" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N25" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P25" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q25" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R25" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T25" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V25" s="3">
@@ -5943,11 +5875,11 @@
         <v>0</v>
       </c>
       <c r="W25" s="3">
-        <f>SUM(AK25,AO25,AS25,AW25,BA25,BE25,BI25,BM25,BQ25,BU25,BY25,CC25,CG25,CK25,CO25,CS25,CW25,DA25,DE25,DI25,DM25,DQ25,DU25,DY25,EC25,EG25,EK25,EO25,ES25,EW25,FA25,FE25,FI25,FM25,FQ25,FU25,FY25,GC25,GG25,GK25,GO25,GS25,GW25,HA25,HE25,HI25,HM25,HQ25,HU25,HY25,IC25,IG25,IK25,IO25,IS25,IW25,JA25,JE25,JI25,JM25,JQ25,JU25,JY25,KC25,KG25,KK25,KO25,KS25,KW25,LA25,LE25,LI25,LM25,LQ25,LU25,LY25,MC25,MH25,MK25,MO25,MS25,MW25,NA25,NE25,NI25,NM25,NQ25,NU25,NY25,OC25,OG25,OK25,OO25,OS25,OW25,PA25,PE25,PI25,PM25,PQ25)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X25" s="4">
-        <f>SUM(DA25,DE25,DI25,DM25,DQ25,DU25,DY25,EC25,EG25,EK25,EO25,ES25,EW25,FA25,FE25,FI25,FM25,FQ25,FU25,FY25,GC25,GG25,GK25,GO25,GS25,GW25,HA25,HE25,HI25,HM25,HQ25,HU25,HY25,IC25,IG25,IK25,IO25,IS25,IW25,JA25,JE25,JI25,JM25,JQ25,JU25,JY25,KC25,KG25,KK25,KO25,KS25,KW25,LA25,LE25,LI25,LM25,LQ25,LU25,LY25,MC25,MH25,MK25,MO25,MS25,MW25,NA25,NE25,NI25,NM25,NQ25,NU25,NY25,OC25,OG25,OK25,OO25,OS25,OW25,PA25,PE25,PI25,PM25,PQ25)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y25" s="4" t="e">
@@ -5959,31 +5891,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC25">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD25">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF25">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG25">
-        <f>SUM(IW25,JA25,JE25,JI25,JM25,JQ25,JU25,JY25,KC25,KG25,KK25,KO25,KS25,KW25,LA25,LE25,LI25,LM25,LQ25,LU25,LY25,MC25,MH25,MK25,MO25,MS25,MW25,NA25,NE25,NI25,NM25,NQ25,NU25,NY25,OC25,OG25,OK25,OO25,OS25,OW25,PA25,PE25,PI25,PM25,PQ25)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH25" t="e">
@@ -5991,23 +5923,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS25" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU25" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW25">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -6016,83 +5948,83 @@
         <v>116</v>
       </c>
       <c r="B26">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N26" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O26">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R26" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S26">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T26" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U26" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V26" s="3">
@@ -6100,11 +6032,11 @@
         <v>0</v>
       </c>
       <c r="W26" s="3">
-        <f>SUM(AK26,AO26,AS26,AW26,BA26,BE26,BI26,BM26,BQ26,BU26,BY26,CC26,CG26,CK26,CO26,CS26,CW26,DA26,DE26,DI26,DM26,DQ26,DU26,DY26,EC26,EG26,EK26,EO26,ES26,EW26,FA26,FE26,FI26,FM26,FQ26,FU26,FY26,GC26,GG26,GK26,GO26,GS26,GW26,HA26,HE26,HI26,HM26,HQ26,HU26,HY26,IC26,IG26,IK26,IO26,IS26,IW26,JA26,JE26,JI26,JM26,JQ26,JU26,JY26,KC26,KG26,KK26,KO26,KS26,KW26,LA26,LE26,LI26,LM26,LQ26,LU26,LY26,MC26,MH26,MK26,MO26,MS26,MW26,NA26,NE26,NI26,NM26,NQ26,NU26,NY26,OC26,OG26,OK26,OO26,OS26,OW26,PA26,PE26,PI26,PM26,PQ26)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X26" s="4">
-        <f>SUM(DA26,DE26,DI26,DM26,DQ26,DU26,DY26,EC26,EG26,EK26,EO26,ES26,EW26,FA26,FE26,FI26,FM26,FQ26,FU26,FY26,GC26,GG26,GK26,GO26,GS26,GW26,HA26,HE26,HI26,HM26,HQ26,HU26,HY26,IC26,IG26,IK26,IO26,IS26,IW26,JA26,JE26,JI26,JM26,JQ26,JU26,JY26,KC26,KG26,KK26,KO26,KS26,KW26,LA26,LE26,LI26,LM26,LQ26,LU26,LY26,MC26,MH26,MK26,MO26,MS26,MW26,NA26,NE26,NI26,NM26,NQ26,NU26,NY26,OC26,OG26,OK26,OO26,OS26,OW26,PA26,PE26,PI26,PM26,PQ26)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y26" s="4" t="e">
@@ -6116,31 +6048,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA26">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB26">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC26">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD26">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE26">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF26">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG26">
-        <f>SUM(IW26,JA26,JE26,JI26,JM26,JQ26,JU26,JY26,KC26,KG26,KK26,KO26,KS26,KW26,LA26,LE26,LI26,LM26,LQ26,LU26,LY26,MC26,MH26,MK26,MO26,MS26,MW26,NA26,NE26,NI26,NM26,NQ26,NU26,NY26,OC26,OG26,OK26,OO26,OS26,OW26,PA26,PE26,PI26,PM26,PQ26)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH26" t="e">
@@ -6148,105 +6080,105 @@
         <v>#REF!</v>
       </c>
       <c r="PS26" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT26" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU26" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW26">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B27">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M27" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N27" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P27" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R27" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T27" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V27" s="3">
@@ -6254,11 +6186,11 @@
         <v>0</v>
       </c>
       <c r="W27" s="3">
-        <f>SUM(AK27,AO27,AS27,AW27,BA27,BE27,BI27,BM27,BQ27,BU27,BY27,CC27,CG27,CK27,CO27,CS27,CW27,DA27,DE27,DI27,DM27,DQ27,DU27,DY27,EC27,EG27,EK27,EO27,ES27,EW27,FA27,FE27,FI27,FM27,FQ27,FU27,FY27,GC27,GG27,GK27,GO27,GS27,GW27,HA27,HE27,HI27,HM27,HQ27,HU27,HY27,IC27,IG27,IK27,IO27,IS27,IW27,JA27,JE27,JI27,JM27,JQ27,JU27,JY27,KC27,KG27,KK27,KO27,KS27,KW27,LA27,LE27,LI27,LM27,LQ27,LU27,LY27,MC27,MH27,MK27,MO27,MS27,MW27,NA27,NE27,NI27,NM27,NQ27,NU27,NY27,OC27,OG27,OK27,OO27,OS27,OW27,PA27,PE27,PI27,PM27,PQ27)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X27" s="4">
-        <f>SUM(DA27,DE27,DI27,DM27,DQ27,DU27,DY27,EC27,EG27,EK27,EO27,ES27,EW27,FA27,FE27,FI27,FM27,FQ27,FU27,FY27,GC27,GG27,GK27,GO27,GS27,GW27,HA27,HE27,HI27,HM27,HQ27,HU27,HY27,IC27,IG27,IK27,IO27,IS27,IW27,JA27,JE27,JI27,JM27,JQ27,JU27,JY27,KC27,KG27,KK27,KO27,KS27,KW27,LA27,LE27,LI27,LM27,LQ27,LU27,LY27,MC27,MH27,MK27,MO27,MS27,MW27,NA27,NE27,NI27,NM27,NQ27,NU27,NY27,OC27,OG27,OK27,OO27,OS27,OW27,PA27,PE27,PI27,PM27,PQ27)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y27" s="4" t="e">
@@ -6270,31 +6202,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA27">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB27">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG27">
-        <f>SUM(IW27,JA27,JE27,JI27,JM27,JQ27,JU27,JY27,KC27,KG27,KK27,KO27,KS27,KW27,LA27,LE27,LI27,LM27,LQ27,LU27,LY27,MC27,MH27,MK27,MO27,MS27,MW27,NA27,NE27,NI27,NM27,NQ27,NU27,NY27,OC27,OG27,OK27,OO27,OS27,OW27,PA27,PE27,PI27,PM27,PQ27)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH27" t="e">
@@ -6302,105 +6234,105 @@
         <v>#REF!</v>
       </c>
       <c r="PS27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT27" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW27">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B28">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L28" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M28" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N28" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P28" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q28" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R28" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S28">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T28" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U28" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V28" s="3">
@@ -6408,11 +6340,11 @@
         <v>0</v>
       </c>
       <c r="W28" s="3">
-        <f>SUM(AK28,AO28,AS28,AW28,BA28,BE28,BI28,BM28,BQ28,BU28,BY28,CC28,CG28,CK28,CO28,CS28,CW28,DA28,DE28,DI28,DM28,DQ28,DU28,DY28,EC28,EG28,EK28,EO28,ES28,EW28,FA28,FE28,FI28,FM28,FQ28,FU28,FY28,GC28,GG28,GK28,GO28,GS28,GW28,HA28,HE28,HI28,HM28,HQ28,HU28,HY28,IC28,IG28,IK28,IO28,IS28,IW28,JA28,JE28,JI28,JM28,JQ28,JU28,JY28,KC28,KG28,KK28,KO28,KS28,KW28,LA28,LE28,LI28,LM28,LQ28,LU28,LY28,MC28,MH28,MK28,MO28,MS28,MW28,NA28,NE28,NI28,NM28,NQ28,NU28,NY28,OC28,OG28,OK28,OO28,OS28,OW28,PA28,PE28,PI28,PM28,PQ28)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X28" s="4">
-        <f>SUM(DA28,DE28,DI28,DM28,DQ28,DU28,DY28,EC28,EG28,EK28,EO28,ES28,EW28,FA28,FE28,FI28,FM28,FQ28,FU28,FY28,GC28,GG28,GK28,GO28,GS28,GW28,HA28,HE28,HI28,HM28,HQ28,HU28,HY28,IC28,IG28,IK28,IO28,IS28,IW28,JA28,JE28,JI28,JM28,JQ28,JU28,JY28,KC28,KG28,KK28,KO28,KS28,KW28,LA28,LE28,LI28,LM28,LQ28,LU28,LY28,MC28,MH28,MK28,MO28,MS28,MW28,NA28,NE28,NI28,NM28,NQ28,NU28,NY28,OC28,OG28,OK28,OO28,OS28,OW28,PA28,PE28,PI28,PM28,PQ28)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y28" s="4" t="e">
@@ -6424,31 +6356,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA28">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC28">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG28">
-        <f>SUM(IW28,JA28,JE28,JI28,JM28,JQ28,JU28,JY28,KC28,KG28,KK28,KO28,KS28,KW28,LA28,LE28,LI28,LM28,LQ28,LU28,LY28,MC28,MH28,MK28,MO28,MS28,MW28,NA28,NE28,NI28,NM28,NQ28,NU28,NY28,OC28,OG28,OK28,OO28,OS28,OW28,PA28,PE28,PI28,PM28,PQ28)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH28" t="e">
@@ -6456,105 +6388,105 @@
         <v>#REF!</v>
       </c>
       <c r="PS28" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT28" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU28" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW28">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B29">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="C29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M29" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N29" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P29" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S29">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U29" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V29" s="3">
@@ -6562,11 +6494,11 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
-        <f>SUM(AK29,AO29,AS29,AW29,BA29,BE29,BI29,BM29,BQ29,BU29,BY29,CC29,CG29,CK29,CO29,CS29,CW29,DA29,DE29,DI29,DM29,DQ29,DU29,DY29,EC29,EG29,EK29,EO29,ES29,EW29,FA29,FE29,FI29,FM29,FQ29,FU29,FY29,GC29,GG29,GK29,GO29,GS29,GW29,HA29,HE29,HI29,HM29,HQ29,HU29,HY29,IC29,IG29,IK29,IO29,IS29,IW29,JA29,JE29,JI29,JM29,JQ29,JU29,JY29,KC29,KG29,KK29,KO29,KS29,KW29,LA29,LE29,LI29,LM29,LQ29,LU29,LY29,MC29,MH29,MK29,MO29,MS29,MW29,NA29,NE29,NI29,NM29,NQ29,NU29,NY29,OC29,OG29,OK29,OO29,OS29,OW29,PA29,PE29,PI29,PM29,PQ29)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X29" s="4">
-        <f>SUM(DA29,DE29,DI29,DM29,DQ29,DU29,DY29,EC29,EG29,EK29,EO29,ES29,EW29,FA29,FE29,FI29,FM29,FQ29,FU29,FY29,GC29,GG29,GK29,GO29,GS29,GW29,HA29,HE29,HI29,HM29,HQ29,HU29,HY29,IC29,IG29,IK29,IO29,IS29,IW29,JA29,JE29,JI29,JM29,JQ29,JU29,JY29,KC29,KG29,KK29,KO29,KS29,KW29,LA29,LE29,LI29,LM29,LQ29,LU29,LY29,MC29,MH29,MK29,MO29,MS29,MW29,NA29,NE29,NI29,NM29,NQ29,NU29,NY29,OC29,OG29,OK29,OO29,OS29,OW29,PA29,PE29,PI29,PM29,PQ29)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y29" s="4" t="e">
@@ -6578,31 +6510,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB29">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC29">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD29">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE29">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF29">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG29">
-        <f>SUM(IW29,JA29,JE29,JI29,JM29,JQ29,JU29,JY29,KC29,KG29,KK29,KO29,KS29,KW29,LA29,LE29,LI29,LM29,LQ29,LU29,LY29,MC29,MH29,MK29,MO29,MS29,MW29,NA29,NE29,NI29,NM29,NQ29,NU29,NY29,OC29,OG29,OK29,OO29,OS29,OW29,PA29,PE29,PI29,PM29,PQ29)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH29" t="e">
@@ -6610,117 +6542,117 @@
         <v>#REF!</v>
       </c>
       <c r="PS29" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="PT29" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="PU29" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PV29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW29">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B30">
-        <f t="shared" ref="B30" si="55">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
+        <f t="shared" ref="B30" si="58">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
         <v>0</v>
       </c>
       <c r="C30">
-        <f t="shared" ref="C30" si="56">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
+        <f t="shared" ref="C30" si="59">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
         <v>0</v>
       </c>
       <c r="D30">
-        <f t="shared" ref="D30" si="57">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
+        <f t="shared" ref="D30" si="60">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
         <v>0</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30" si="58">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
+        <f t="shared" ref="E30" si="61">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
         <v>0</v>
       </c>
       <c r="F30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G30">
-        <f t="shared" ref="G30" si="59">SUM(H30:I30)</f>
+        <f t="shared" ref="G30" si="62">SUM(H30:I30)</f>
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" ref="H30" si="60">COUNTIF(AI30:PR30,"T")</f>
+        <f t="shared" ref="H30" si="63">COUNTIF(AI30:PR30,"T")</f>
         <v>0</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" ref="I30" si="61">COUNTIF(AI30:PR30,"R")</f>
+        <f t="shared" ref="I30" si="64">COUNTIF(AI30:PR30,"R")</f>
         <v>0</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" ref="J30" si="62">COUNTIF(AI30:PR30,"NR")</f>
+        <f t="shared" ref="J30" si="65">COUNTIF(AI30:PR30,"NR")</f>
         <v>0</v>
       </c>
       <c r="K30">
-        <f t="shared" ref="K30" si="63">SUM(L30:M30)</f>
+        <f t="shared" ref="K30" si="66">SUM(L30:M30)</f>
         <v>0</v>
       </c>
       <c r="L30" s="3">
-        <f t="shared" ref="L30" si="64">COUNTIF(CY30:GX30,"T")</f>
+        <f t="shared" ref="L30" si="67">COUNTIF(CY30:GX30,"T")</f>
         <v>0</v>
       </c>
       <c r="M30" s="3">
-        <f t="shared" ref="M30" si="65">COUNTIF(CY30:GX30,"R")</f>
+        <f t="shared" ref="M30" si="68">COUNTIF(CY30:GX30,"R")</f>
         <v>0</v>
       </c>
       <c r="N30" s="3">
-        <f t="shared" ref="N30" si="66">COUNTIF(CY30:GX30,"NR")</f>
+        <f t="shared" ref="N30" si="69">COUNTIF(CY30:GX30,"NR")</f>
         <v>0</v>
       </c>
       <c r="O30">
-        <f t="shared" ref="O30" si="67">SUM(P30:Q30)</f>
+        <f t="shared" ref="O30" si="70">SUM(P30:Q30)</f>
         <v>0</v>
       </c>
       <c r="P30" s="3">
-        <f t="shared" ref="P30" si="68">COUNTIF(GY30:IT30,"T")</f>
+        <f t="shared" ref="P30" si="71">COUNTIF(GY30:IT30,"T")</f>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" ref="Q30" si="69">COUNTIF(GY30:IT30,"R")</f>
+        <f t="shared" ref="Q30" si="72">COUNTIF(GY30:IT30,"R")</f>
         <v>0</v>
       </c>
       <c r="R30" s="3">
-        <f t="shared" ref="R30" si="70">COUNTIF(GY30:IT30,"NR")</f>
+        <f t="shared" ref="R30" si="73">COUNTIF(GY30:IT30,"NR")</f>
         <v>0</v>
       </c>
       <c r="S30">
-        <f t="shared" ref="S30" si="71">SUM(T30:U30)</f>
+        <f t="shared" ref="S30" si="74">SUM(T30:U30)</f>
         <v>0</v>
       </c>
       <c r="T30" s="3">
-        <f t="shared" ref="T30" si="72">COUNTIF(IU30:PR30,"T")</f>
+        <f t="shared" ref="T30" si="75">COUNTIF(IU30:PR30,"T")</f>
         <v>0</v>
       </c>
       <c r="U30" s="3">
-        <f t="shared" ref="U30" si="73">COUNTIF(IU30:PR30,"R")</f>
+        <f t="shared" ref="U30" si="76">COUNTIF(IU30:PR30,"R")</f>
         <v>0</v>
       </c>
       <c r="V30" s="3">
-        <f t="shared" ref="V30" si="74">COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" ref="V30" si="77">COUNTIF(IU:PR,"NR")</f>
         <v>0</v>
       </c>
       <c r="W30" s="3">
-        <f>SUM(AK30,AO30,AS30,AW30,BA30,BE30,BI30,BM30,BQ30,BU30,BY30,CC30,CG30,CK30,CO30,CS30,CW30,DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30,HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30,IW30,JA30,JE30,JI30,JM30,JQ30,JU30,JY30,KC30,KG30,KK30,KO30,KS30,KW30,LA30,LE30,LI30,LM30,LQ30,LU30,LY30,MC30,MH30,MK30,MO30,MS30,MW30,NA30,NE30,NI30,NM30,NQ30,NU30,NY30,OC30,OG30,OK30,OO30,OS30,OW30,PA30,PE30,PI30,PM30,PQ30)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X30" s="4">
-        <f>SUM(DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30,HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30,IW30,JA30,JE30,JI30,JM30,JQ30,JU30,JY30,KC30,KG30,KK30,KO30,KS30,KW30,LA30,LE30,LI30,LM30,LQ30,LU30,LY30,MC30,MH30,MK30,MO30,MS30,MW30,NA30,NE30,NI30,NM30,NQ30,NU30,NY30,OC30,OG30,OK30,OO30,OS30,OW30,PA30,PE30,PI30,PM30,PQ30)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y30" s="4" t="e">
@@ -6732,31 +6664,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA30">
-        <f t="shared" ref="AA30" si="75">SUM(DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30)</f>
+        <f t="shared" ref="AA30" si="78">SUM(DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30)</f>
         <v>0</v>
       </c>
       <c r="AB30">
-        <f t="shared" ref="AB30" si="76">SUM(DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30)</f>
+        <f t="shared" ref="AB30" si="79">SUM(DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30)</f>
         <v>0</v>
       </c>
       <c r="AC30">
-        <f t="shared" ref="AC30" si="77">SUM(HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30)</f>
+        <f t="shared" ref="AC30" si="80">SUM(HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30)</f>
         <v>0</v>
       </c>
       <c r="AD30">
-        <f t="shared" ref="AD30" si="78">SUM(HB30,HF30,HJ30,HN30,HR30,HV30,HZ30,ID30,IH30,IL30,IP30,IT30)</f>
+        <f t="shared" ref="AD30" si="81">SUM(HB30,HF30,HJ30,HN30,HR30,HV30,HZ30,ID30,IH30,IL30,IP30,IT30)</f>
         <v>0</v>
       </c>
       <c r="AE30">
-        <f t="shared" ref="AE30" si="79">SUM(AK30,AO30,AS30,AW30,BA30,BE30,BI30,BM30,BQ30,BU30,BY30,CC30,CG30,CK30,CO30,CS30,CW30)</f>
+        <f t="shared" ref="AE30" si="82">SUM(AK30,AO30,AS30,AW30,BA30,BE30,BI30,BM30,BQ30,BU30,BY30,CC30,CG30,CK30,CO30,CS30,CW30)</f>
         <v>0</v>
       </c>
       <c r="AF30">
-        <f t="shared" ref="AF30" si="80">SUM(AL30,AP30,AT30,AX30,BB30,BF30,BJ30,BN30,BR30,BV30,BZ30,CD30,CH30,CL30,CP30,CT30,CX30)</f>
+        <f t="shared" ref="AF30" si="83">SUM(AL30,AP30,AT30,AX30,BB30,BF30,BJ30,BN30,BR30,BV30,BZ30,CD30,CH30,CL30,CP30,CT30,CX30)</f>
         <v>0</v>
       </c>
       <c r="AG30">
-        <f>SUM(IW30,JA30,JE30,JI30,JM30,JQ30,JU30,JY30,KC30,KG30,KK30,KO30,KS30,KW30,LA30,LE30,LI30,LM30,LQ30,LU30,LY30,MC30,MH30,MK30,MO30,MS30,MW30,NA30,NE30,NI30,NM30,NQ30,NU30,NY30,OC30,OG30,OK30,OO30,OS30,OW30,PA30,PE30,PI30,PM30,PQ30)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH30" t="e">
@@ -6764,117 +6696,117 @@
         <v>#REF!</v>
       </c>
       <c r="PS30" s="3">
-        <f t="shared" ref="PS30" si="81">COUNTIF(AI30:PR30,"HG")</f>
+        <f t="shared" ref="PS30" si="84">COUNTIF(AI30:PR30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT30" s="3">
-        <f t="shared" ref="PT30" si="82">COUNTIF(CY30:GX30,"HG")</f>
+        <f t="shared" ref="PT30" si="85">COUNTIF(CY30:GX30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU30" s="3">
-        <f t="shared" ref="PU30" si="83">COUNTIF(GY30:IT30,"HG")</f>
+        <f t="shared" ref="PU30" si="86">COUNTIF(GY30:IT30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV30">
-        <f t="shared" ref="PV30" si="84">COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" ref="PV30" si="87">COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW30">
-        <f t="shared" ref="PW30" si="85">G30-(K30+O30+S30)</f>
+        <f t="shared" ref="PW30" si="88">G30-(K30+O30+S30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B31">
-        <f t="shared" ref="B31" si="86">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
+        <f t="shared" ref="B31" si="89">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
         <v>0</v>
       </c>
       <c r="C31">
-        <f t="shared" ref="C31" si="87">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
+        <f t="shared" ref="C31" si="90">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
         <v>0</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31" si="88">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
+        <f t="shared" ref="D31" si="91">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
         <v>0</v>
       </c>
       <c r="E31">
-        <f t="shared" ref="E31" si="89">SUM(IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
+        <f t="shared" ref="E31" si="92">SUM(IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
         <v>0</v>
       </c>
       <c r="F31">
-        <f t="shared" ref="F31" si="90">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31)</f>
+        <f t="shared" ref="F31" si="93">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31)</f>
         <v>0</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="91">SUM(H31:I31)</f>
+        <f t="shared" ref="G31" si="94">SUM(H31:I31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" ref="H31" si="92">COUNTIF(AI31:PR31,"T")</f>
+        <f t="shared" ref="H31" si="95">COUNTIF(AI31:PR31,"T")</f>
         <v>0</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" ref="I31" si="93">COUNTIF(AI31:PR31,"R")</f>
+        <f t="shared" ref="I31" si="96">COUNTIF(AI31:PR31,"R")</f>
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" ref="J31" si="94">COUNTIF(AI31:PR31,"NR")</f>
+        <f t="shared" ref="J31" si="97">COUNTIF(AI31:PR31,"NR")</f>
         <v>0</v>
       </c>
       <c r="K31">
-        <f t="shared" ref="K31" si="95">SUM(L31:M31)</f>
+        <f t="shared" ref="K31" si="98">SUM(L31:M31)</f>
         <v>0</v>
       </c>
       <c r="L31" s="3">
-        <f t="shared" ref="L31" si="96">COUNTIF(CY31:GX31,"T")</f>
+        <f t="shared" ref="L31" si="99">COUNTIF(CY31:GX31,"T")</f>
         <v>0</v>
       </c>
       <c r="M31" s="3">
-        <f t="shared" ref="M31" si="97">COUNTIF(CY31:GX31,"R")</f>
+        <f t="shared" ref="M31" si="100">COUNTIF(CY31:GX31,"R")</f>
         <v>0</v>
       </c>
       <c r="N31" s="3">
-        <f t="shared" ref="N31" si="98">COUNTIF(CY31:GX31,"NR")</f>
+        <f t="shared" ref="N31" si="101">COUNTIF(CY31:GX31,"NR")</f>
         <v>0</v>
       </c>
       <c r="O31">
-        <f t="shared" ref="O31" si="99">SUM(P31:Q31)</f>
+        <f t="shared" ref="O31" si="102">SUM(P31:Q31)</f>
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f t="shared" ref="P31" si="100">COUNTIF(GY31:IT31,"T")</f>
+        <f t="shared" ref="P31" si="103">COUNTIF(GY31:IT31,"T")</f>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <f t="shared" ref="Q31" si="101">COUNTIF(GY31:IT31,"R")</f>
+        <f t="shared" ref="Q31" si="104">COUNTIF(GY31:IT31,"R")</f>
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <f t="shared" ref="R31" si="102">COUNTIF(GY31:IT31,"NR")</f>
+        <f t="shared" ref="R31" si="105">COUNTIF(GY31:IT31,"NR")</f>
         <v>0</v>
       </c>
       <c r="S31">
-        <f t="shared" ref="S31" si="103">SUM(T31:U31)</f>
+        <f t="shared" ref="S31" si="106">SUM(T31:U31)</f>
         <v>0</v>
       </c>
       <c r="T31" s="3">
-        <f t="shared" ref="T31" si="104">COUNTIF(IU31:PR31,"T")</f>
+        <f t="shared" ref="T31" si="107">COUNTIF(IU31:PR31,"T")</f>
         <v>0</v>
       </c>
       <c r="U31" s="3">
-        <f t="shared" ref="U31" si="105">COUNTIF(IU31:PR31,"R")</f>
+        <f t="shared" ref="U31" si="108">COUNTIF(IU31:PR31,"R")</f>
         <v>0</v>
       </c>
       <c r="V31" s="3">
-        <f t="shared" ref="V31" si="106">COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" ref="V31" si="109">COUNTIF(IU:PR,"NR")</f>
         <v>0</v>
       </c>
       <c r="W31" s="3">
-        <f>SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31,DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MH31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X31" s="4">
-        <f>SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MH31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y31" s="4" t="e">
@@ -6886,31 +6818,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA31">
-        <f t="shared" ref="AA31" si="107">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
+        <f t="shared" ref="AA31" si="110">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
         <v>0</v>
       </c>
       <c r="AB31">
-        <f t="shared" ref="AB31" si="108">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
+        <f t="shared" ref="AB31" si="111">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
         <v>0</v>
       </c>
       <c r="AC31">
-        <f t="shared" ref="AC31" si="109">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
+        <f t="shared" ref="AC31" si="112">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
         <v>0</v>
       </c>
       <c r="AD31">
-        <f t="shared" ref="AD31" si="110">SUM(HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31)</f>
+        <f t="shared" ref="AD31" si="113">SUM(HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31)</f>
         <v>0</v>
       </c>
       <c r="AE31">
-        <f t="shared" ref="AE31" si="111">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31)</f>
+        <f t="shared" ref="AE31" si="114">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31)</f>
         <v>0</v>
       </c>
       <c r="AF31">
-        <f t="shared" ref="AF31" si="112">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31)</f>
+        <f t="shared" ref="AF31" si="115">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31)</f>
         <v>0</v>
       </c>
       <c r="AG31">
-        <f>SUM(IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MH31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH31" t="e">
@@ -6918,117 +6850,117 @@
         <v>#REF!</v>
       </c>
       <c r="PS31" s="3">
-        <f t="shared" ref="PS31" si="113">COUNTIF(AI31:PR31,"HG")</f>
+        <f t="shared" ref="PS31" si="116">COUNTIF(AI31:PR31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT31" s="3">
-        <f t="shared" ref="PT31" si="114">COUNTIF(CY31:GX31,"HG")</f>
+        <f t="shared" ref="PT31" si="117">COUNTIF(CY31:GX31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU31" s="3">
-        <f t="shared" ref="PU31" si="115">COUNTIF(GY31:IT31,"HG")</f>
+        <f t="shared" ref="PU31" si="118">COUNTIF(GY31:IT31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV31">
-        <f t="shared" ref="PV31" si="116">COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" ref="PV31" si="119">COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW31">
-        <f t="shared" ref="PW31" si="117">G31-(K31+O31+S31)</f>
+        <f t="shared" ref="PW31" si="120">G31-(K31+O31+S31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B32">
-        <f t="shared" ref="B32" si="118">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
+        <f t="shared" ref="B32" si="121">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
         <v>0</v>
       </c>
       <c r="C32">
-        <f t="shared" ref="C32" si="119">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
+        <f t="shared" ref="C32" si="122">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
         <v>0</v>
       </c>
       <c r="D32">
-        <f t="shared" ref="D32" si="120">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
+        <f t="shared" ref="D32" si="123">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
         <v>0</v>
       </c>
       <c r="E32">
-        <f t="shared" ref="E32" si="121">SUM(IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
+        <f t="shared" ref="E32" si="124">SUM(IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
         <v>0</v>
       </c>
       <c r="F32">
-        <f t="shared" ref="F32" si="122">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32)</f>
+        <f t="shared" ref="F32" si="125">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32)</f>
         <v>0</v>
       </c>
       <c r="G32">
-        <f t="shared" ref="G32" si="123">SUM(H32:I32)</f>
+        <f t="shared" ref="G32" si="126">SUM(H32:I32)</f>
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" ref="H32" si="124">COUNTIF(AI32:PR32,"T")</f>
+        <f t="shared" ref="H32" si="127">COUNTIF(AI32:PR32,"T")</f>
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <f t="shared" ref="I32" si="125">COUNTIF(AI32:PR32,"R")</f>
+        <f t="shared" ref="I32" si="128">COUNTIF(AI32:PR32,"R")</f>
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" ref="J32" si="126">COUNTIF(AI32:PR32,"NR")</f>
+        <f t="shared" ref="J32" si="129">COUNTIF(AI32:PR32,"NR")</f>
         <v>0</v>
       </c>
       <c r="K32">
-        <f t="shared" ref="K32" si="127">SUM(L32:M32)</f>
+        <f t="shared" ref="K32" si="130">SUM(L32:M32)</f>
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <f t="shared" ref="L32" si="128">COUNTIF(CY32:GX32,"T")</f>
+        <f t="shared" ref="L32" si="131">COUNTIF(CY32:GX32,"T")</f>
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <f t="shared" ref="M32" si="129">COUNTIF(CY32:GX32,"R")</f>
+        <f t="shared" ref="M32" si="132">COUNTIF(CY32:GX32,"R")</f>
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <f t="shared" ref="N32" si="130">COUNTIF(CY32:GX32,"NR")</f>
+        <f t="shared" ref="N32" si="133">COUNTIF(CY32:GX32,"NR")</f>
         <v>0</v>
       </c>
       <c r="O32">
-        <f t="shared" ref="O32" si="131">SUM(P32:Q32)</f>
+        <f t="shared" ref="O32" si="134">SUM(P32:Q32)</f>
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <f t="shared" ref="P32" si="132">COUNTIF(GY32:IT32,"T")</f>
+        <f t="shared" ref="P32" si="135">COUNTIF(GY32:IT32,"T")</f>
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <f t="shared" ref="Q32" si="133">COUNTIF(GY32:IT32,"R")</f>
+        <f t="shared" ref="Q32" si="136">COUNTIF(GY32:IT32,"R")</f>
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <f t="shared" ref="R32" si="134">COUNTIF(GY32:IT32,"NR")</f>
+        <f t="shared" ref="R32" si="137">COUNTIF(GY32:IT32,"NR")</f>
         <v>0</v>
       </c>
       <c r="S32">
-        <f t="shared" ref="S32" si="135">SUM(T32:U32)</f>
+        <f t="shared" ref="S32" si="138">SUM(T32:U32)</f>
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <f t="shared" ref="T32" si="136">COUNTIF(IU32:PR32,"T")</f>
+        <f t="shared" ref="T32" si="139">COUNTIF(IU32:PR32,"T")</f>
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <f t="shared" ref="U32" si="137">COUNTIF(IU32:PR32,"R")</f>
+        <f t="shared" ref="U32" si="140">COUNTIF(IU32:PR32,"R")</f>
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <f t="shared" ref="V32" si="138">COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" ref="V32" si="141">COUNTIF(IU:PR,"NR")</f>
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <f>SUM(AK32,AO32,AS32,AW32,BA32,BE32,BI32,BM32,BQ32,BU32,BY32,CC32,CG32,CK32,CO32,CS32,CW32,DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32,HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32,IW32,JA32,JE32,JI32,JM32,JQ32,JU32,JY32,KC32,KG32,KK32,KO32,KS32,KW32,LA32,LE32,LI32,LM32,LQ32,LU32,LY32,MC32,MH32,MK32,MO32,MS32,MW32,NA32,NE32,NI32,NM32,NQ32,NU32,NY32,OC32,OG32,OK32,OO32,OS32,OW32,PA32,PE32,PI32,PM32,PQ32)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X32" s="4">
-        <f>SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32,HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32,IW32,JA32,JE32,JI32,JM32,JQ32,JU32,JY32,KC32,KG32,KK32,KO32,KS32,KW32,LA32,LE32,LI32,LM32,LQ32,LU32,LY32,MC32,MH32,MK32,MO32,MS32,MW32,NA32,NE32,NI32,NM32,NQ32,NU32,NY32,OC32,OG32,OK32,OO32,OS32,OW32,PA32,PE32,PI32,PM32,PQ32)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y32" s="4" t="e">
@@ -7040,31 +6972,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA32">
-        <f t="shared" ref="AA32" si="139">SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32)</f>
+        <f t="shared" ref="AA32" si="142">SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32)</f>
         <v>0</v>
       </c>
       <c r="AB32">
-        <f t="shared" ref="AB32" si="140">SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32)</f>
+        <f t="shared" ref="AB32" si="143">SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32)</f>
         <v>0</v>
       </c>
       <c r="AC32">
-        <f t="shared" ref="AC32" si="141">SUM(HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32)</f>
+        <f t="shared" ref="AC32" si="144">SUM(HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32)</f>
         <v>0</v>
       </c>
       <c r="AD32">
-        <f t="shared" ref="AD32" si="142">SUM(HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32)</f>
+        <f t="shared" ref="AD32" si="145">SUM(HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32)</f>
         <v>0</v>
       </c>
       <c r="AE32">
-        <f t="shared" ref="AE32" si="143">SUM(AK32,AO32,AS32,AW32,BA32,BE32,BI32,BM32,BQ32,BU32,BY32,CC32,CG32,CK32,CO32,CS32,CW32)</f>
+        <f t="shared" ref="AE32" si="146">SUM(AK32,AO32,AS32,AW32,BA32,BE32,BI32,BM32,BQ32,BU32,BY32,CC32,CG32,CK32,CO32,CS32,CW32)</f>
         <v>0</v>
       </c>
       <c r="AF32">
-        <f t="shared" ref="AF32" si="144">SUM(AL32,AP32,AT32,AX32,BB32,BF32,BJ32,BN32,BR32,BV32,BZ32,CD32,CH32,CL32,CP32,CT32,CX32)</f>
+        <f t="shared" ref="AF32" si="147">SUM(AL32,AP32,AT32,AX32,BB32,BF32,BJ32,BN32,BR32,BV32,BZ32,CD32,CH32,CL32,CP32,CT32,CX32)</f>
         <v>0</v>
       </c>
       <c r="AG32">
-        <f>SUM(IW32,JA32,JE32,JI32,JM32,JQ32,JU32,JY32,KC32,KG32,KK32,KO32,KS32,KW32,LA32,LE32,LI32,LM32,LQ32,LU32,LY32,MC32,MH32,MK32,MO32,MS32,MW32,NA32,NE32,NI32,NM32,NQ32,NU32,NY32,OC32,OG32,OK32,OO32,OS32,OW32,PA32,PE32,PI32,PM32,PQ32)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH32" t="e">
@@ -7072,23 +7004,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS32" s="3">
-        <f t="shared" ref="PS32" si="145">COUNTIF(AI32:PR32,"HG")</f>
+        <f t="shared" ref="PS32" si="148">COUNTIF(AI32:PR32,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT32" s="3">
-        <f t="shared" ref="PT32" si="146">COUNTIF(CY32:GX32,"HG")</f>
+        <f t="shared" ref="PT32" si="149">COUNTIF(CY32:GX32,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU32" s="3">
-        <f t="shared" ref="PU32" si="147">COUNTIF(GY32:IT32,"HG")</f>
+        <f t="shared" ref="PU32" si="150">COUNTIF(GY32:IT32,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV32">
-        <f t="shared" ref="PV32" si="148">COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" ref="PV32" si="151">COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW32">
-        <f t="shared" ref="PW32" si="149">G32-(K32+O32+S32)</f>
+        <f t="shared" ref="PW32" si="152">G32-(K32+O32+S32)</f>
         <v>0</v>
       </c>
     </row>

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209D92CF-B366-CB46-8259-0512C8FAEC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A78FF1-E415-5F43-85A4-4D40E10298D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -446,9 +446,6 @@
     <t>Sandro Marcon</t>
   </si>
   <si>
-    <t xml:space="preserve">Bradley </t>
-  </si>
-  <si>
     <t>Pharell Cafara</t>
   </si>
   <si>
@@ -462,6 +459,9 @@
   </si>
   <si>
     <t>Fares Farhi</t>
+  </si>
+  <si>
+    <t>Brady Gouandjia</t>
   </si>
 </sst>
 </file>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="20" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B20">
         <f t="shared" si="34"/>
@@ -5160,7 +5160,7 @@
     </row>
     <row r="21" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B21">
         <f t="shared" si="34"/>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="22" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B22">
         <f t="shared" si="34"/>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="23" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B23">
         <f t="shared" si="34"/>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="24" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B24">
         <f t="shared" si="34"/>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="25" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B25">
         <f t="shared" si="34"/>

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A78FF1-E415-5F43-85A4-4D40E10298D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392FB665-0850-D344-9131-5E677E4D76A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="148">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -462,6 +462,24 @@
   </si>
   <si>
     <t>Brady Gouandjia</t>
+  </si>
+  <si>
+    <t>Cedrick Koffi</t>
+  </si>
+  <si>
+    <t>Antoine Leberre</t>
+  </si>
+  <si>
+    <t>Kamal Bafounta</t>
+  </si>
+  <si>
+    <t>Romain Antunes</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>R</t>
   </si>
 </sst>
 </file>
@@ -2495,7 +2513,7 @@
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B29" si="34">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <f t="shared" si="5"/>
@@ -2511,15 +2529,15 @@
       </c>
       <c r="F4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G4">
         <f t="shared" ref="G4" si="35">SUM(H4:I4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4" si="36">COUNTIF(AI4:PR4,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" ref="I4" si="37">COUNTIF(AI4:PR4,"R")</f>
@@ -2625,6 +2643,12 @@
         <f>SUM(IX4,JB4,JF4,JJ4,JN4,JR4,JV4,JZ4,KD4,KH4,KL4,KP4,KT4,KX4,LB4,LF4,LJ4,LN4,LR4,LV4,LZ4,MD4,#REF!,ML4,MP4,MT4,MX4,NB4,NF4,NJ4,NN4,NR4,NV4,NZ4,OD4,OH4,OL4,OP4,OT4,OX4,PB4,PF4,PJ4,PN4,PR4)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI4">
+        <v>45</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>146</v>
+      </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="54">COUNTIF(AI4:PR4,"HG")</f>
         <v>0</v>
@@ -2643,7 +2667,7 @@
       </c>
       <c r="PW4">
         <f t="shared" ref="PW4" si="57">G4-(K4+O4+S4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:439" x14ac:dyDescent="0.2">
@@ -2809,7 +2833,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
@@ -2825,11 +2849,11 @@
       </c>
       <c r="F6">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
@@ -2837,7 +2861,7 @@
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="12"/>
@@ -2939,6 +2963,12 @@
         <f>SUM(IX6,JB6,JF6,JJ6,JN6,JR6,JV6,JZ6,KD6,KH6,KL6,KP6,KT6,KX6,LB6,LF6,LJ6,LN6,LR6,LV6,LZ6,MD6,#REF!,ML6,MP6,MT6,MX6,NB6,NF6,NJ6,NN6,NR6,NV6,NZ6,OD6,OH6,OL6,OP6,OT6,OX6,PB6,PF6,PJ6,PN6,PR6)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI6">
+        <v>45</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>147</v>
+      </c>
       <c r="PS6" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -2957,7 +2987,7 @@
       </c>
       <c r="PW6">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:439" x14ac:dyDescent="0.2">
@@ -3123,7 +3153,7 @@
       </c>
       <c r="B8">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C8">
         <f t="shared" si="5"/>
@@ -3139,11 +3169,11 @@
       </c>
       <c r="F8">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G8">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="10"/>
@@ -3151,7 +3181,7 @@
       </c>
       <c r="I8" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="12"/>
@@ -3253,6 +3283,12 @@
         <f>SUM(IX8,JB8,JF8,JJ8,JN8,JR8,JV8,JZ8,KD8,KH8,KL8,KP8,KT8,KX8,LB8,LF8,LJ8,LN8,LR8,LV8,LZ8,MD8,#REF!,ML8,MP8,MT8,MX8,NB8,NF8,NJ8,NN8,NR8,NV8,NZ8,OD8,OH8,OL8,OP8,OT8,OX8,PB8,PF8,PJ8,PN8,PR8)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI8">
+        <v>45</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>147</v>
+      </c>
       <c r="PS8" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -3271,7 +3307,7 @@
       </c>
       <c r="PW8">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:439" x14ac:dyDescent="0.2">
@@ -3437,7 +3473,7 @@
       </c>
       <c r="B10">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
@@ -3453,11 +3489,11 @@
       </c>
       <c r="F10">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
@@ -3465,7 +3501,7 @@
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="12"/>
@@ -3567,6 +3603,12 @@
         <f>SUM(IX10,JB10,JF10,JJ10,JN10,JR10,JV10,JZ10,KD10,KH10,KL10,KP10,KT10,KX10,LB10,LF10,LJ10,LN10,LR10,LV10,LZ10,MD10,#REF!,ML10,MP10,MT10,MX10,NB10,NF10,NJ10,NN10,NR10,NV10,NZ10,OD10,OH10,OL10,OP10,OT10,OX10,PB10,PF10,PJ10,PN10,PR10)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI10">
+        <v>45</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>147</v>
+      </c>
       <c r="PS10" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -3585,7 +3627,7 @@
       </c>
       <c r="PW10">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:439" x14ac:dyDescent="0.2">
@@ -3594,7 +3636,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <f t="shared" si="5"/>
@@ -3610,15 +3652,15 @@
       </c>
       <c r="F11">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="11"/>
@@ -3724,6 +3766,12 @@
         <f>SUM(IX11,JB11,JF11,JJ11,JN11,JR11,JV11,JZ11,KD11,KH11,KL11,KP11,KT11,KX11,LB11,LF11,LJ11,LN11,LR11,LV11,LZ11,MD11,#REF!,ML11,MP11,MT11,MX11,NB11,NF11,NJ11,NN11,NR11,NV11,NZ11,OD11,OH11,OL11,OP11,OT11,OX11,PB11,PF11,PJ11,PN11,PR11)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI11">
+        <v>45</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>146</v>
+      </c>
       <c r="PS11" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -3742,7 +3790,7 @@
       </c>
       <c r="PW11">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:439" x14ac:dyDescent="0.2">
@@ -3751,7 +3799,7 @@
       </c>
       <c r="B12">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C12">
         <f t="shared" si="5"/>
@@ -3767,15 +3815,15 @@
       </c>
       <c r="F12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="11"/>
@@ -3881,6 +3929,12 @@
         <f>SUM(IX12,JB12,JF12,JJ12,JN12,JR12,JV12,JZ12,KD12,KH12,KL12,KP12,KT12,KX12,LB12,LF12,LJ12,LN12,LR12,LV12,LZ12,MD12,#REF!,ML12,MP12,MT12,MX12,NB12,NF12,NJ12,NN12,NR12,NV12,NZ12,OD12,OH12,OL12,OP12,OT12,OX12,PB12,PF12,PJ12,PN12,PR12)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI12">
+        <v>45</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>146</v>
+      </c>
       <c r="PS12" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -3899,7 +3953,7 @@
       </c>
       <c r="PW12">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:439" x14ac:dyDescent="0.2">
@@ -3908,7 +3962,7 @@
       </c>
       <c r="B13">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C13">
         <f t="shared" si="5"/>
@@ -3924,11 +3978,11 @@
       </c>
       <c r="F13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="10"/>
@@ -3936,7 +3990,7 @@
       </c>
       <c r="I13" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="12"/>
@@ -4038,6 +4092,12 @@
         <f>SUM(IX13,JB13,JF13,JJ13,JN13,JR13,JV13,JZ13,KD13,KH13,KL13,KP13,KT13,KX13,LB13,LF13,LJ13,LN13,LR13,LV13,LZ13,MD13,#REF!,ML13,MP13,MT13,MX13,NB13,NF13,NJ13,NN13,NR13,NV13,NZ13,OD13,OH13,OL13,OP13,OT13,OX13,PB13,PF13,PJ13,PN13,PR13)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI13">
+        <v>45</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>147</v>
+      </c>
       <c r="PS13" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -4056,7 +4116,7 @@
       </c>
       <c r="PW13">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:439" x14ac:dyDescent="0.2">
@@ -4065,7 +4125,7 @@
       </c>
       <c r="B14">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
@@ -4081,11 +4141,11 @@
       </c>
       <c r="F14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
@@ -4093,7 +4153,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="12"/>
@@ -4195,6 +4255,12 @@
         <f>SUM(IX14,JB14,JF14,JJ14,JN14,JR14,JV14,JZ14,KD14,KH14,KL14,KP14,KT14,KX14,LB14,LF14,LJ14,LN14,LR14,LV14,LZ14,MD14,#REF!,ML14,MP14,MT14,MX14,NB14,NF14,NJ14,NN14,NR14,NV14,NZ14,OD14,OH14,OL14,OP14,OT14,OX14,PB14,PF14,PJ14,PN14,PR14)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI14">
+        <v>45</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>147</v>
+      </c>
       <c r="PS14" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -4213,7 +4279,7 @@
       </c>
       <c r="PW14">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:439" x14ac:dyDescent="0.2">
@@ -4222,7 +4288,7 @@
       </c>
       <c r="B15">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <f t="shared" si="5"/>
@@ -4238,15 +4304,15 @@
       </c>
       <c r="F15">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G15">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="11"/>
@@ -4352,6 +4418,12 @@
         <f>SUM(IX15,JB15,JF15,JJ15,JN15,JR15,JV15,JZ15,KD15,KH15,KL15,KP15,KT15,KX15,LB15,LF15,LJ15,LN15,LR15,LV15,LZ15,MD15,#REF!,ML15,MP15,MT15,MX15,NB15,NF15,NJ15,NN15,NR15,NV15,NZ15,OD15,OH15,OL15,OP15,OT15,OX15,PB15,PF15,PJ15,PN15,PR15)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI15">
+        <v>45</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>146</v>
+      </c>
       <c r="PS15" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -4370,7 +4442,7 @@
       </c>
       <c r="PW15">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:439" x14ac:dyDescent="0.2">
@@ -4379,7 +4451,7 @@
       </c>
       <c r="B16">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <f t="shared" si="5"/>
@@ -4395,11 +4467,11 @@
       </c>
       <c r="F16">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G16">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="10"/>
@@ -4407,7 +4479,7 @@
       </c>
       <c r="I16" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3">
         <f t="shared" si="12"/>
@@ -4463,7 +4535,7 @@
       </c>
       <c r="W16" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="4">
         <f t="shared" si="2"/>
@@ -4495,7 +4567,7 @@
       </c>
       <c r="AE16">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16">
         <f t="shared" si="29"/>
@@ -4509,6 +4581,15 @@
         <f>SUM(IX16,JB16,JF16,JJ16,JN16,JR16,JV16,JZ16,KD16,KH16,KL16,KP16,KT16,KX16,LB16,LF16,LJ16,LN16,LR16,LV16,LZ16,MD16,#REF!,ML16,MP16,MT16,MX16,NB16,NF16,NJ16,NN16,NR16,NV16,NZ16,OD16,OH16,OL16,OP16,OT16,OX16,PB16,PF16,PJ16,PN16,PR16)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI16">
+        <v>45</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK16">
+        <v>1</v>
+      </c>
       <c r="PS16" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -4527,7 +4608,7 @@
       </c>
       <c r="PW16">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:439" x14ac:dyDescent="0.2">
@@ -4536,7 +4617,7 @@
       </c>
       <c r="B17">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C17">
         <f t="shared" si="5"/>
@@ -4552,15 +4633,15 @@
       </c>
       <c r="F17">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G17">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="3">
         <f t="shared" si="11"/>
@@ -4666,6 +4747,12 @@
         <f>SUM(IX17,JB17,JF17,JJ17,JN17,JR17,JV17,JZ17,KD17,KH17,KL17,KP17,KT17,KX17,LB17,LF17,LJ17,LN17,LR17,LV17,LZ17,MD17,#REF!,ML17,MP17,MT17,MX17,NB17,NF17,NJ17,NN17,NR17,NV17,NZ17,OD17,OH17,OL17,OP17,OT17,OX17,PB17,PF17,PJ17,PN17,PR17)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI17">
+        <v>45</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>146</v>
+      </c>
       <c r="PS17" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -4684,7 +4771,7 @@
       </c>
       <c r="PW17">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:439" x14ac:dyDescent="0.2">
@@ -4693,7 +4780,7 @@
       </c>
       <c r="B18">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <f t="shared" si="5"/>
@@ -4709,11 +4796,11 @@
       </c>
       <c r="F18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G18">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="10"/>
@@ -4721,7 +4808,7 @@
       </c>
       <c r="I18" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="12"/>
@@ -4777,7 +4864,7 @@
       </c>
       <c r="W18" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="2"/>
@@ -4809,7 +4896,7 @@
       </c>
       <c r="AE18">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18">
         <f t="shared" si="29"/>
@@ -4823,6 +4910,15 @@
         <f>SUM(IX18,JB18,JF18,JJ18,JN18,JR18,JV18,JZ18,KD18,KH18,KL18,KP18,KT18,KX18,LB18,LF18,LJ18,LN18,LR18,LV18,LZ18,MD18,#REF!,ML18,MP18,MT18,MX18,NB18,NF18,NJ18,NN18,NR18,NV18,NZ18,OD18,OH18,OL18,OP18,OT18,OX18,PB18,PF18,PJ18,PN18,PR18)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI18">
+        <v>45</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK18">
+        <v>1</v>
+      </c>
       <c r="PS18" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -4841,7 +4937,7 @@
       </c>
       <c r="PW18">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:439" x14ac:dyDescent="0.2">
@@ -4850,7 +4946,7 @@
       </c>
       <c r="B19">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
@@ -4866,11 +4962,11 @@
       </c>
       <c r="F19">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G19">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="10"/>
@@ -4878,7 +4974,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="12"/>
@@ -4980,6 +5076,12 @@
         <f>SUM(IX19,JB19,JF19,JJ19,JN19,JR19,JV19,JZ19,KD19,KH19,KL19,KP19,KT19,KX19,LB19,LF19,LJ19,LN19,LR19,LV19,LZ19,MD19,#REF!,ML19,MP19,MT19,MX19,NB19,NF19,NJ19,NN19,NR19,NV19,NZ19,OD19,OH19,OL19,OP19,OT19,OX19,PB19,PF19,PJ19,PN19,PR19)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI19">
+        <v>45</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>147</v>
+      </c>
       <c r="PS19" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -4998,7 +5100,7 @@
       </c>
       <c r="PW19">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:439" x14ac:dyDescent="0.2">
@@ -5007,7 +5109,7 @@
       </c>
       <c r="B20">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <f t="shared" si="5"/>
@@ -5023,11 +5125,11 @@
       </c>
       <c r="F20">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G20">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="10"/>
@@ -5035,7 +5137,7 @@
       </c>
       <c r="I20" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3">
         <f t="shared" si="12"/>
@@ -5137,6 +5239,12 @@
         <f>SUM(IX20,JB20,JF20,JJ20,JN20,JR20,JV20,JZ20,KD20,KH20,KL20,KP20,KT20,KX20,LB20,LF20,LJ20,LN20,LR20,LV20,LZ20,MD20,#REF!,ML20,MP20,MT20,MX20,NB20,NF20,NJ20,NN20,NR20,NV20,NZ20,OD20,OH20,OL20,OP20,OT20,OX20,PB20,PF20,PJ20,PN20,PR20)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI20">
+        <v>45</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>147</v>
+      </c>
       <c r="PS20" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -5155,7 +5263,7 @@
       </c>
       <c r="PW20">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:439" x14ac:dyDescent="0.2">
@@ -5164,7 +5272,7 @@
       </c>
       <c r="B21">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C21">
         <f t="shared" si="5"/>
@@ -5180,11 +5288,11 @@
       </c>
       <c r="F21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G21">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="10"/>
@@ -5192,7 +5300,7 @@
       </c>
       <c r="I21" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3">
         <f t="shared" si="12"/>
@@ -5294,6 +5402,12 @@
         <f>SUM(IX21,JB21,JF21,JJ21,JN21,JR21,JV21,JZ21,KD21,KH21,KL21,KP21,KT21,KX21,LB21,LF21,LJ21,LN21,LR21,LV21,LZ21,MD21,#REF!,ML21,MP21,MT21,MX21,NB21,NF21,NJ21,NN21,NR21,NV21,NZ21,OD21,OH21,OL21,OP21,OT21,OX21,PB21,PF21,PJ21,PN21,PR21)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI21">
+        <v>22</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>147</v>
+      </c>
       <c r="PS21" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -5312,7 +5426,7 @@
       </c>
       <c r="PW21">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:439" x14ac:dyDescent="0.2">
@@ -5321,7 +5435,7 @@
       </c>
       <c r="B22">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <f t="shared" si="5"/>
@@ -5337,11 +5451,11 @@
       </c>
       <c r="F22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G22">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="10"/>
@@ -5349,7 +5463,7 @@
       </c>
       <c r="I22" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3">
         <f t="shared" si="12"/>
@@ -5441,7 +5555,7 @@
       </c>
       <c r="AF22">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22">
         <f t="shared" si="3"/>
@@ -5451,6 +5565,15 @@
         <f>SUM(IX22,JB22,JF22,JJ22,JN22,JR22,JV22,JZ22,KD22,KH22,KL22,KP22,KT22,KX22,LB22,LF22,LJ22,LN22,LR22,LV22,LZ22,MD22,#REF!,ML22,MP22,MT22,MX22,NB22,NF22,NJ22,NN22,NR22,NV22,NZ22,OD22,OH22,OL22,OP22,OT22,OX22,PB22,PF22,PJ22,PN22,PR22)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI22">
+        <v>22</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>147</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
       <c r="PS22" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -5469,7 +5592,7 @@
       </c>
       <c r="PW22">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:439" x14ac:dyDescent="0.2">
@@ -5478,7 +5601,7 @@
       </c>
       <c r="B23">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <f t="shared" si="5"/>
@@ -5494,15 +5617,15 @@
       </c>
       <c r="F23">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="3">
         <f t="shared" si="11"/>
@@ -5608,6 +5731,12 @@
         <f>SUM(IX23,JB23,JF23,JJ23,JN23,JR23,JV23,JZ23,KD23,KH23,KL23,KP23,KT23,KX23,LB23,LF23,LJ23,LN23,LR23,LV23,LZ23,MD23,#REF!,ML23,MP23,MT23,MX23,NB23,NF23,NJ23,NN23,NR23,NV23,NZ23,OD23,OH23,OL23,OP23,OT23,OX23,PB23,PF23,PJ23,PN23,PR23)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI23">
+        <v>45</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>146</v>
+      </c>
       <c r="PS23" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -5626,7 +5755,7 @@
       </c>
       <c r="PW23">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:439" x14ac:dyDescent="0.2">
@@ -5635,7 +5764,7 @@
       </c>
       <c r="B24">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <f t="shared" si="5"/>
@@ -5651,15 +5780,15 @@
       </c>
       <c r="F24">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G24">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="11"/>
@@ -5765,6 +5894,12 @@
         <f>SUM(IX24,JB24,JF24,JJ24,JN24,JR24,JV24,JZ24,KD24,KH24,KL24,KP24,KT24,KX24,LB24,LF24,LJ24,LN24,LR24,LV24,LZ24,MD24,#REF!,ML24,MP24,MT24,MX24,NB24,NF24,NJ24,NN24,NR24,NV24,NZ24,OD24,OH24,OL24,OP24,OT24,OX24,PB24,PF24,PJ24,PN24,PR24)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI24">
+        <v>45</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>146</v>
+      </c>
       <c r="PS24" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -5783,7 +5918,7 @@
       </c>
       <c r="PW24">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:439" x14ac:dyDescent="0.2">
@@ -5792,7 +5927,7 @@
       </c>
       <c r="B25">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <f t="shared" si="5"/>
@@ -5808,15 +5943,15 @@
       </c>
       <c r="F25">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G25">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="11"/>
@@ -5922,6 +6057,12 @@
         <f>SUM(IX25,JB25,JF25,JJ25,JN25,JR25,JV25,JZ25,KD25,KH25,KL25,KP25,KT25,KX25,LB25,LF25,LJ25,LN25,LR25,LV25,LZ25,MD25,#REF!,ML25,MP25,MT25,MX25,NB25,NF25,NJ25,NN25,NR25,NV25,NZ25,OD25,OH25,OL25,OP25,OT25,OX25,PB25,PF25,PJ25,PN25,PR25)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI25">
+        <v>45</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>146</v>
+      </c>
       <c r="PS25" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -5940,7 +6081,7 @@
       </c>
       <c r="PW25">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:439" x14ac:dyDescent="0.2">
@@ -6101,9 +6242,12 @@
       </c>
     </row>
     <row r="27" spans="1:439" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>142</v>
+      </c>
       <c r="B27">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <f t="shared" si="5"/>
@@ -6119,15 +6263,15 @@
       </c>
       <c r="F27">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G27">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="11"/>
@@ -6233,6 +6377,12 @@
         <f>SUM(IX27,JB27,JF27,JJ27,JN27,JR27,JV27,JZ27,KD27,KH27,KL27,KP27,KT27,KX27,LB27,LF27,LJ27,LN27,LR27,LV27,LZ27,MD27,#REF!,ML27,MP27,MT27,MX27,NB27,NF27,NJ27,NN27,NR27,NV27,NZ27,OD27,OH27,OL27,OP27,OT27,OX27,PB27,PF27,PJ27,PN27,PR27)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI27">
+        <v>45</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>146</v>
+      </c>
       <c r="PS27" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -6251,13 +6401,16 @@
       </c>
       <c r="PW27">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:439" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>143</v>
+      </c>
       <c r="B28">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
@@ -6273,15 +6426,15 @@
       </c>
       <c r="F28">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
@@ -6387,6 +6540,12 @@
         <f>SUM(IX28,JB28,JF28,JJ28,JN28,JR28,JV28,JZ28,KD28,KH28,KL28,KP28,KT28,KX28,LB28,LF28,LJ28,LN28,LR28,LV28,LZ28,MD28,#REF!,ML28,MP28,MT28,MX28,NB28,NF28,NJ28,NN28,NR28,NV28,NZ28,OD28,OH28,OL28,OP28,OT28,OX28,PB28,PF28,PJ28,PN28,PR28)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI28">
+        <v>45</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>146</v>
+      </c>
       <c r="PS28" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -6405,13 +6564,16 @@
       </c>
       <c r="PW28">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:439" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>144</v>
+      </c>
       <c r="B29">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C29">
         <f t="shared" si="5"/>
@@ -6427,15 +6589,15 @@
       </c>
       <c r="F29">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G29">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="11"/>
@@ -6541,6 +6703,12 @@
         <f>SUM(IX29,JB29,JF29,JJ29,JN29,JR29,JV29,JZ29,KD29,KH29,KL29,KP29,KT29,KX29,LB29,LF29,LJ29,LN29,LR29,LV29,LZ29,MD29,#REF!,ML29,MP29,MT29,MX29,NB29,NF29,NJ29,NN29,NR29,NV29,NZ29,OD29,OH29,OL29,OP29,OT29,OX29,PB29,PF29,PJ29,PN29,PR29)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI29">
+        <v>45</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>146</v>
+      </c>
       <c r="PS29" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
@@ -6559,13 +6727,16 @@
       </c>
       <c r="PW29">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:439" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>145</v>
+      </c>
       <c r="B30">
         <f t="shared" ref="B30" si="58">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="59">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
@@ -6581,15 +6752,15 @@
       </c>
       <c r="F30">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="62">SUM(H30:I30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="63">COUNTIF(AI30:PR30,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="64">COUNTIF(AI30:PR30,"R")</f>
@@ -6695,6 +6866,12 @@
         <f>SUM(IX30,JB30,JF30,JJ30,JN30,JR30,JV30,JZ30,KD30,KH30,KL30,KP30,KT30,KX30,LB30,LF30,LJ30,LN30,LR30,LV30,LZ30,MD30,#REF!,ML30,MP30,MT30,MX30,NB30,NF30,NJ30,NN30,NR30,NV30,NZ30,OD30,OH30,OL30,OP30,OT30,OX30,PB30,PF30,PJ30,PN30,PR30)</f>
         <v>#REF!</v>
       </c>
+      <c r="AI30">
+        <v>45</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>146</v>
+      </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="84">COUNTIF(AI30:PR30,"HG")</f>
         <v>0</v>
@@ -6713,7 +6890,7 @@
       </c>
       <c r="PW30">
         <f t="shared" ref="PW30" si="88">G30-(K30+O30+S30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:439" x14ac:dyDescent="0.2">

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392FB665-0850-D344-9131-5E677E4D76A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA475DC-5E9E-8241-BC42-EFFE849C6D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="147">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -462,9 +462,6 @@
   </si>
   <si>
     <t>Brady Gouandjia</t>
-  </si>
-  <si>
-    <t>Cedrick Koffi</t>
   </si>
   <si>
     <t>Antoine Leberre</t>
@@ -867,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F67B87-FE0E-FC4A-8FE6-DAAF2AFECC8B}">
-  <dimension ref="A1:PW32"/>
+  <dimension ref="A1:PW31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
@@ -2199,7 +2196,7 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
@@ -2215,15 +2212,15 @@
       </c>
       <c r="F2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2278,15 +2275,15 @@
         <v>0</v>
       </c>
       <c r="V2" s="3">
-        <f t="shared" ref="V2:V29" si="0">COUNTIF(IU:PR,"NR")</f>
+        <f>COUNTIF(IU:PR,"NR")</f>
         <v>0</v>
       </c>
       <c r="W2" s="3">
-        <f t="shared" ref="W2:W32" si="1">SUM(AK2,AO2,AS2,AW2,BA2,BE2,BI2,BM2,BQ2,BU2,BY2,CC2,CG2,CK2,CO2,CS2,CW2,DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <f t="shared" ref="W2:W31" si="0">SUM(AK2,AO2,AS2,AW2,BA2,BE2,BI2,BM2,BQ2,BU2,BY2,CC2,CG2,CK2,CO2,CS2,CW2,DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
         <v>0</v>
       </c>
       <c r="X2" s="4">
-        <f t="shared" ref="X2:X32" si="2">SUM(DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <f t="shared" ref="X2:X31" si="1">SUM(DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
         <v>0</v>
       </c>
       <c r="Y2" s="4" t="e">
@@ -2322,13 +2319,19 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <f t="shared" ref="AG2:AG32" si="3">SUM(IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <f t="shared" ref="AG2:AG31" si="2">SUM(IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
         <v>0</v>
       </c>
       <c r="AH2" t="e">
         <f>SUM(IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,#REF!,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
         <v>#REF!</v>
       </c>
+      <c r="AQ2">
+        <v>60</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>145</v>
+      </c>
       <c r="PS2" s="3">
         <f>COUNTIF(AI2:PR2,"HG")</f>
         <v>0</v>
@@ -2342,12 +2345,12 @@
         <v>0</v>
       </c>
       <c r="PV2">
-        <f t="shared" ref="PV2:PV29" si="4">COUNTIF(IU:PR,"HG")</f>
+        <f>COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW2">
         <f>G2-(K2+O2+S2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:439" x14ac:dyDescent="0.2">
@@ -2359,91 +2362,91 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C29" si="5">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
+        <f t="shared" ref="C3:C28" si="3">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D29" si="6">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
+        <f t="shared" ref="D3:D28" si="4">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E29" si="7">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
+        <f t="shared" ref="E3:E28" si="5">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F30" si="8">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
+        <f t="shared" ref="F3:F29" si="6">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G29" si="9">SUM(H3:I3)</f>
+        <f t="shared" ref="G3:G28" si="7">SUM(H3:I3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H29" si="10">COUNTIF(AI3:PR3,"T")</f>
+        <f t="shared" ref="H3:H28" si="8">COUNTIF(AI3:PR3,"T")</f>
         <v>0</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I29" si="11">COUNTIF(AI3:PR3,"R")</f>
+        <f t="shared" ref="I3:I28" si="9">COUNTIF(AI3:PR3,"R")</f>
         <v>0</v>
       </c>
       <c r="J3" s="3">
-        <f t="shared" ref="J3:J29" si="12">COUNTIF(AI3:PR3,"NR")</f>
+        <f t="shared" ref="J3:J28" si="10">COUNTIF(AI3:PR3,"NR")</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K29" si="13">SUM(L3:M3)</f>
+        <f t="shared" ref="K3:K28" si="11">SUM(L3:M3)</f>
         <v>0</v>
       </c>
       <c r="L3" s="3">
-        <f t="shared" ref="L3:L29" si="14">COUNTIF(CY3:GX3,"T")</f>
+        <f t="shared" ref="L3:L28" si="12">COUNTIF(CY3:GX3,"T")</f>
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <f t="shared" ref="M3:M29" si="15">COUNTIF(CY3:GX3,"R")</f>
+        <f t="shared" ref="M3:M28" si="13">COUNTIF(CY3:GX3,"R")</f>
         <v>0</v>
       </c>
       <c r="N3" s="3">
-        <f t="shared" ref="N3:N29" si="16">COUNTIF(CY3:GX3,"NR")</f>
+        <f t="shared" ref="N3:N28" si="14">COUNTIF(CY3:GX3,"NR")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O29" si="17">SUM(P3:Q3)</f>
+        <f t="shared" ref="O3:O28" si="15">SUM(P3:Q3)</f>
         <v>0</v>
       </c>
       <c r="P3" s="3">
-        <f t="shared" ref="P3:P29" si="18">COUNTIF(GY3:IT3,"T")</f>
+        <f t="shared" ref="P3:P28" si="16">COUNTIF(GY3:IT3,"T")</f>
         <v>0</v>
       </c>
       <c r="Q3" s="3">
-        <f t="shared" ref="Q3:Q29" si="19">COUNTIF(GY3:IT3,"R")</f>
+        <f t="shared" ref="Q3:Q28" si="17">COUNTIF(GY3:IT3,"R")</f>
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <f t="shared" ref="R3:R29" si="20">COUNTIF(GY3:IT3,"NR")</f>
+        <f t="shared" ref="R3:R28" si="18">COUNTIF(GY3:IT3,"NR")</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S29" si="21">SUM(T3:U3)</f>
+        <f t="shared" ref="S3:S28" si="19">SUM(T3:U3)</f>
         <v>0</v>
       </c>
       <c r="T3" s="3">
-        <f t="shared" ref="T3:T29" si="22">COUNTIF(IU3:PR3,"T")</f>
+        <f t="shared" ref="T3:T28" si="20">COUNTIF(IU3:PR3,"T")</f>
         <v>0</v>
       </c>
       <c r="U3" s="3">
-        <f t="shared" ref="U3:U29" si="23">COUNTIF(IU3:PR3,"R")</f>
+        <f t="shared" ref="U3:U28" si="21">COUNTIF(IU3:PR3,"R")</f>
         <v>0</v>
       </c>
       <c r="V3" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W3" s="3">
+      <c r="X3" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X3" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y3" s="4" t="e">
@@ -2455,31 +2458,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA3">
-        <f t="shared" ref="AA3:AA29" si="24">SUM(DA3,DE3,DI3,DM3,DQ3,DU3,DY3,EC3,EG3,EK3,EO3,ES3,EW3,FA3,FE3,FI3,FM3,FQ3,FU3,FY3,GC3,GG3,GK3,GO3,GS3,GW3)</f>
+        <f t="shared" ref="AA3:AA28" si="22">SUM(DA3,DE3,DI3,DM3,DQ3,DU3,DY3,EC3,EG3,EK3,EO3,ES3,EW3,FA3,FE3,FI3,FM3,FQ3,FU3,FY3,GC3,GG3,GK3,GO3,GS3,GW3)</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f t="shared" ref="AB3:AB29" si="25">SUM(DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3)</f>
+        <f t="shared" ref="AB3:AB28" si="23">SUM(DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3)</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" ref="AC3:AC29" si="26">SUM(HA3,HE3,HI3,HM3,HQ3,HU3,HY3,IC3,IG3,IK3,IO3,IS3)</f>
+        <f t="shared" ref="AC3:AC28" si="24">SUM(HA3,HE3,HI3,HM3,HQ3,HU3,HY3,IC3,IG3,IK3,IO3,IS3)</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD29" si="27">SUM(HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3)</f>
+        <f t="shared" ref="AD3:AD28" si="25">SUM(HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3)</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" ref="AE3:AE29" si="28">SUM(AK3,AO3,AS3,AW3,BA3,BE3,BI3,BM3,BQ3,BU3,BY3,CC3,CG3,CK3,CO3,CS3,CW3)</f>
+        <f t="shared" ref="AE3:AE28" si="26">SUM(AK3,AO3,AS3,AW3,BA3,BE3,BI3,BM3,BQ3,BU3,BY3,CC3,CG3,CK3,CO3,CS3,CW3)</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" ref="AF3:AF29" si="29">SUM(AL3,AP3,AT3,AX3,BB3,BF3,BJ3,BN3,BR3,BV3,BZ3,CD3,CH3,CL3,CP3,CT3,CX3)</f>
+        <f t="shared" ref="AF3:AF28" si="27">SUM(AL3,AP3,AT3,AX3,BB3,BF3,BJ3,BN3,BR3,BV3,BZ3,CD3,CH3,CL3,CP3,CT3,CX3)</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH3" t="e">
@@ -2487,23 +2490,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS3" s="3">
-        <f t="shared" ref="PS3:PS29" si="30">COUNTIF(AI3:PR3,"HG")</f>
+        <f t="shared" ref="PS3:PS28" si="28">COUNTIF(AI3:PR3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT3" s="3">
-        <f t="shared" ref="PT3:PT29" si="31">COUNTIF(CY3:GX3,"HG")</f>
+        <f t="shared" ref="PT3:PT28" si="29">COUNTIF(CY3:GX3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU3" s="3">
-        <f t="shared" ref="PU3:PU29" si="32">COUNTIF(GY3:IT3,"HG")</f>
+        <f t="shared" ref="PU3:PU28" si="30">COUNTIF(GY3:IT3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV3">
-        <f t="shared" si="4"/>
+        <f>COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW3">
-        <f t="shared" ref="PW3:PW29" si="33">G3-(K3+O3+S3)</f>
+        <f t="shared" ref="PW3:PW28" si="31">G3-(K3+O3+S3)</f>
         <v>0</v>
       </c>
     </row>
@@ -2512,95 +2515,95 @@
         <v>128</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B29" si="34">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
-        <v>45</v>
+        <f t="shared" ref="B4:B28" si="32">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
+        <v>120</v>
       </c>
       <c r="C4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="8"/>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4" si="35">SUM(H4:I4)</f>
+        <f t="shared" ref="G4" si="33">SUM(H4:I4)</f>
+        <v>3</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" ref="H4" si="34">COUNTIF(AI4:PR4,"T")</f>
+        <v>2</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" ref="I4" si="35">COUNTIF(AI4:PR4,"R")</f>
         <v>1</v>
       </c>
-      <c r="H4" s="3">
-        <f t="shared" ref="H4" si="36">COUNTIF(AI4:PR4,"T")</f>
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <f t="shared" ref="I4" si="37">COUNTIF(AI4:PR4,"R")</f>
-        <v>0</v>
-      </c>
       <c r="J4" s="3">
-        <f t="shared" ref="J4" si="38">COUNTIF(AI4:PR4,"NR")</f>
+        <f t="shared" ref="J4" si="36">COUNTIF(AI4:PR4,"NR")</f>
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4" si="39">SUM(L4:M4)</f>
+        <f t="shared" ref="K4" si="37">SUM(L4:M4)</f>
         <v>0</v>
       </c>
       <c r="L4" s="3">
-        <f t="shared" ref="L4" si="40">COUNTIF(CY4:GX4,"T")</f>
+        <f t="shared" ref="L4" si="38">COUNTIF(CY4:GX4,"T")</f>
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <f t="shared" ref="M4" si="41">COUNTIF(CY4:GX4,"R")</f>
+        <f t="shared" ref="M4" si="39">COUNTIF(CY4:GX4,"R")</f>
         <v>0</v>
       </c>
       <c r="N4" s="3">
-        <f t="shared" ref="N4" si="42">COUNTIF(CY4:GX4,"NR")</f>
+        <f t="shared" ref="N4" si="40">COUNTIF(CY4:GX4,"NR")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f t="shared" ref="O4" si="43">SUM(P4:Q4)</f>
+        <f t="shared" ref="O4" si="41">SUM(P4:Q4)</f>
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <f t="shared" ref="P4" si="44">COUNTIF(GY4:IT4,"T")</f>
+        <f t="shared" ref="P4" si="42">COUNTIF(GY4:IT4,"T")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="3">
-        <f t="shared" ref="Q4" si="45">COUNTIF(GY4:IT4,"R")</f>
+        <f t="shared" ref="Q4" si="43">COUNTIF(GY4:IT4,"R")</f>
         <v>0</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" ref="R4" si="46">COUNTIF(GY4:IT4,"NR")</f>
+        <f t="shared" ref="R4" si="44">COUNTIF(GY4:IT4,"NR")</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" ref="S4" si="47">SUM(T4:U4)</f>
+        <f t="shared" ref="S4" si="45">SUM(T4:U4)</f>
         <v>0</v>
       </c>
       <c r="T4" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U4" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V4" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W4" s="3">
+      <c r="X4" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X4" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y4" s="4" t="e">
@@ -2612,31 +2615,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA4">
-        <f t="shared" ref="AA4" si="48">SUM(DA4,DE4,DI4,DM4,DQ4,DU4,DY4,EC4,EG4,EK4,EO4,ES4,EW4,FA4,FE4,FI4,FM4,FQ4,FU4,FY4,GC4,GG4,GK4,GO4,GS4,GW4)</f>
+        <f t="shared" ref="AA4" si="46">SUM(DA4,DE4,DI4,DM4,DQ4,DU4,DY4,EC4,EG4,EK4,EO4,ES4,EW4,FA4,FE4,FI4,FM4,FQ4,FU4,FY4,GC4,GG4,GK4,GO4,GS4,GW4)</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f t="shared" ref="AB4" si="49">SUM(DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4)</f>
+        <f t="shared" ref="AB4" si="47">SUM(DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4)</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" ref="AC4" si="50">SUM(HA4,HE4,HI4,HM4,HQ4,HU4,HY4,IC4,IG4,IK4,IO4,IS4)</f>
+        <f t="shared" ref="AC4" si="48">SUM(HA4,HE4,HI4,HM4,HQ4,HU4,HY4,IC4,IG4,IK4,IO4,IS4)</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" ref="AD4" si="51">SUM(HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4)</f>
+        <f t="shared" ref="AD4" si="49">SUM(HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4)</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f t="shared" ref="AE4" si="52">SUM(AK4,AO4,AS4,AW4,BA4,BE4,BI4,BM4,BQ4,BU4,BY4,CC4,CG4,CK4,CO4,CS4,CW4)</f>
+        <f t="shared" ref="AE4" si="50">SUM(AK4,AO4,AS4,AW4,BA4,BE4,BI4,BM4,BQ4,BU4,BY4,CC4,CG4,CK4,CO4,CS4,CW4)</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" ref="AF4" si="53">SUM(AL4,AP4,AT4,AX4,BB4,BF4,BJ4,BN4,BR4,BV4,BZ4,CD4,CH4,CL4,CP4,CT4,CX4)</f>
+        <f t="shared" ref="AF4" si="51">SUM(AL4,AP4,AT4,AX4,BB4,BF4,BJ4,BN4,BR4,BV4,BZ4,CD4,CH4,CL4,CP4,CT4,CX4)</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH4" t="e">
@@ -2647,27 +2650,39 @@
         <v>45</v>
       </c>
       <c r="AJ4" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM4">
+        <v>45</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ4">
+        <v>30</v>
+      </c>
+      <c r="AR4" t="s">
         <v>146</v>
       </c>
       <c r="PS4" s="3">
-        <f t="shared" ref="PS4" si="54">COUNTIF(AI4:PR4,"HG")</f>
+        <f t="shared" ref="PS4" si="52">COUNTIF(AI4:PR4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT4" s="3">
-        <f t="shared" ref="PT4" si="55">COUNTIF(CY4:GX4,"HG")</f>
+        <f t="shared" ref="PT4" si="53">COUNTIF(CY4:GX4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU4" s="3">
-        <f t="shared" ref="PU4" si="56">COUNTIF(GY4:IT4,"HG")</f>
+        <f t="shared" ref="PU4" si="54">COUNTIF(GY4:IT4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV4">
-        <f t="shared" si="4"/>
+        <f>COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW4">
-        <f t="shared" ref="PW4" si="57">G4-(K4+O4+S4)</f>
-        <v>1</v>
+        <f t="shared" ref="PW4" si="55">G4-(K4+O4+S4)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:439" x14ac:dyDescent="0.2">
@@ -2675,95 +2690,95 @@
         <v>112</v>
       </c>
       <c r="B5">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="32"/>
+        <v>105</v>
       </c>
       <c r="C5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E5">
+        <v>105</v>
+      </c>
+      <c r="G5">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H5" s="3">
+      <c r="J5" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I5" s="3">
+      <c r="K5">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J5" s="3">
+      <c r="L5" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="M5" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L5" s="3">
+      <c r="N5" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M5" s="3">
+      <c r="O5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N5" s="3">
+      <c r="P5" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O5">
+      <c r="Q5" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P5" s="3">
+      <c r="R5" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="S5">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R5" s="3">
+      <c r="T5" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S5">
+      <c r="U5" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T5" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U5" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V5" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W5" s="3">
+      <c r="X5" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X5" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y5" s="4" t="e">
@@ -2775,56 +2790,68 @@
         <v>#REF!</v>
       </c>
       <c r="AA5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC5">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB5">
+      <c r="AD5">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC5">
+      <c r="AE5">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD5">
+      <c r="AF5">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE5">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH5" t="e">
         <f>SUM(IX5,JB5,JF5,JJ5,JN5,JR5,JV5,JZ5,KD5,KH5,KL5,KP5,KT5,KX5,LB5,LF5,LJ5,LN5,LR5,LV5,LZ5,MD5,#REF!,ML5,MP5,MT5,MX5,NB5,NF5,NJ5,NN5,NR5,NV5,NZ5,OD5,OH5,OL5,OP5,OT5,OX5,PB5,PF5,PJ5,PN5,PR5)</f>
         <v>#REF!</v>
       </c>
+      <c r="AM5">
+        <v>45</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ5">
+        <v>60</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>145</v>
+      </c>
       <c r="PS5" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT5" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU5" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT5" s="3">
+      <c r="PV5">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW5">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU5" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW5">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:439" x14ac:dyDescent="0.2">
@@ -2832,95 +2859,95 @@
         <v>129</v>
       </c>
       <c r="B6">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>120</v>
       </c>
       <c r="C6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E6">
+        <v>120</v>
+      </c>
+      <c r="G6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I6" s="3">
+      <c r="K6">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="M6" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L6" s="3">
+      <c r="N6" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M6" s="3">
+      <c r="O6">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N6" s="3">
+      <c r="P6" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O6">
+      <c r="Q6" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P6" s="3">
+      <c r="R6" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="S6">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R6" s="3">
+      <c r="T6" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S6">
+      <c r="U6" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T6" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U6" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V6" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W6" s="3">
+      <c r="X6" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X6" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y6" s="4" t="e">
@@ -2932,31 +2959,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA6">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC6">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB6">
+      <c r="AD6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD6">
+      <c r="AF6">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH6" t="e">
@@ -2967,27 +2994,39 @@
         <v>45</v>
       </c>
       <c r="AJ6" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="AM6">
+        <v>45</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ6">
+        <v>30</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>146</v>
       </c>
       <c r="PS6" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT6" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU6" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT6" s="3">
+      <c r="PV6">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW6">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU6" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW6">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:439" x14ac:dyDescent="0.2">
@@ -2995,95 +3034,95 @@
         <v>130</v>
       </c>
       <c r="B7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="C7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="H7" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="I7" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H7" s="3">
+      <c r="J7" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="K7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="L7" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="M7" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L7" s="3">
+      <c r="N7" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="O7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N7" s="3">
+      <c r="P7" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O7">
+      <c r="Q7" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P7" s="3">
+      <c r="R7" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="S7">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R7" s="3">
+      <c r="T7" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S7">
+      <c r="U7" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T7" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U7" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V7" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W7" s="3">
+      <c r="X7" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X7" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y7" s="4" t="e">
@@ -3095,31 +3134,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA7">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB7">
+      <c r="AD7">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC7">
+      <c r="AE7">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD7">
+      <c r="AF7">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE7">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH7" t="e">
@@ -3127,23 +3166,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS7" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT7" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU7" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT7" s="3">
+      <c r="PV7">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW7">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU7" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW7">
-        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -3152,71 +3191,71 @@
         <v>131</v>
       </c>
       <c r="B8">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>150</v>
       </c>
       <c r="C8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E8">
+        <v>150</v>
+      </c>
+      <c r="G8">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="3">
+        <v>2</v>
+      </c>
+      <c r="J8" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="M8" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O8">
+      <c r="Q8" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S8">
@@ -3224,23 +3263,23 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V8" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X8" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y8" s="4" t="e">
@@ -3252,31 +3291,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC8">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB8">
+      <c r="AD8">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC8">
+      <c r="AE8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD8">
+      <c r="AF8">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE8">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH8" t="e">
@@ -3287,27 +3326,39 @@
         <v>45</v>
       </c>
       <c r="AJ8" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="AM8">
+        <v>45</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>146</v>
+      </c>
+      <c r="AQ8">
+        <v>60</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>145</v>
       </c>
       <c r="PS8" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT8" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU8" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT8" s="3">
+      <c r="PV8">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW8">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU8" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW8">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:439" x14ac:dyDescent="0.2">
@@ -3315,95 +3366,95 @@
         <v>118</v>
       </c>
       <c r="B9">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="32"/>
+        <v>30</v>
       </c>
       <c r="C9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E9">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="G9">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G9">
+      <c r="I9" s="3">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="M9" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O9">
+      <c r="Q9" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S9">
+      <c r="U9" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T9" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U9" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V9" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X9" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y9" s="4" t="e">
@@ -3415,56 +3466,62 @@
         <v>#REF!</v>
       </c>
       <c r="AA9">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC9">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB9">
+      <c r="AD9">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC9">
+      <c r="AE9">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD9">
+      <c r="AF9">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE9">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH9" t="e">
         <f>SUM(IX9,JB9,JF9,JJ9,JN9,JR9,JV9,JZ9,KD9,KH9,KL9,KP9,KT9,KX9,LB9,LF9,LJ9,LN9,LR9,LV9,LZ9,MD9,#REF!,ML9,MP9,MT9,MX9,NB9,NF9,NJ9,NN9,NR9,NV9,NZ9,OD9,OH9,OL9,OP9,OT9,OX9,PB9,PF9,PJ9,PN9,PR9)</f>
         <v>#REF!</v>
       </c>
+      <c r="AQ9">
+        <v>30</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>146</v>
+      </c>
       <c r="PS9" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT9" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU9" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT9" s="3">
+      <c r="PV9">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW9">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU9" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW9">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:439" x14ac:dyDescent="0.2">
@@ -3472,95 +3529,95 @@
         <v>132</v>
       </c>
       <c r="B10">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>150</v>
       </c>
       <c r="C10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E10">
+        <v>150</v>
+      </c>
+      <c r="G10">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="I10" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="M10" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O10">
+      <c r="Q10" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S10">
+      <c r="U10" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T10" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y10" s="4" t="e">
@@ -3572,31 +3629,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC10">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB10">
+      <c r="AD10">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC10">
+      <c r="AE10">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD10">
+      <c r="AF10">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE10">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH10" t="e">
@@ -3607,27 +3664,39 @@
         <v>45</v>
       </c>
       <c r="AJ10" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="AM10">
+        <v>45</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ10">
+        <v>60</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>145</v>
       </c>
       <c r="PS10" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT10" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU10" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT10" s="3">
+      <c r="PV10">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW10">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU10" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW10">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:439" x14ac:dyDescent="0.2">
@@ -3635,95 +3704,95 @@
         <v>113</v>
       </c>
       <c r="B11">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>150</v>
       </c>
       <c r="C11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E11">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E11">
+        <v>150</v>
+      </c>
+      <c r="G11">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="H11" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H11" s="3">
+      <c r="J11" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="L11" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="M11" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L11" s="3">
+      <c r="N11" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M11" s="3">
+      <c r="O11">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N11" s="3">
+      <c r="P11" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O11">
+      <c r="Q11" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P11" s="3">
+      <c r="R11" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="S11">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R11" s="3">
+      <c r="T11" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S11">
+      <c r="U11" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T11" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V11" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W11" s="3">
+      <c r="X11" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y11" s="4" t="e">
@@ -3735,31 +3804,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA11">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC11">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB11">
+      <c r="AD11">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC11">
+      <c r="AE11">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD11">
+      <c r="AF11">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE11">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH11" t="e">
@@ -3770,27 +3839,39 @@
         <v>45</v>
       </c>
       <c r="AJ11" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM11">
+        <v>45</v>
+      </c>
+      <c r="AN11" t="s">
         <v>146</v>
       </c>
+      <c r="AQ11">
+        <v>60</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>145</v>
+      </c>
       <c r="PS11" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT11" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU11" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT11" s="3">
+      <c r="PV11">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW11">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU11" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW11">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:439" x14ac:dyDescent="0.2">
@@ -3798,95 +3879,95 @@
         <v>114</v>
       </c>
       <c r="B12">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>45</v>
       </c>
       <c r="C12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E12">
+        <v>45</v>
+      </c>
+      <c r="G12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="M12" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O12">
+      <c r="Q12" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S12">
+      <c r="U12" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T12" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V12" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y12" s="4" t="e">
@@ -3898,31 +3979,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA12">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC12">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB12">
+      <c r="AD12">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC12">
+      <c r="AE12">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD12">
+      <c r="AF12">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE12">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH12" t="e">
@@ -3933,26 +4014,26 @@
         <v>45</v>
       </c>
       <c r="AJ12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="PS12" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT12" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU12" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT12" s="3">
+      <c r="PV12">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW12">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU12" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW12">
-        <f t="shared" si="33"/>
         <v>1</v>
       </c>
     </row>
@@ -3961,95 +4042,95 @@
         <v>127</v>
       </c>
       <c r="B13">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>90</v>
       </c>
       <c r="C13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E13">
+        <v>90</v>
+      </c>
+      <c r="G13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="H13" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H13" s="3">
+        <v>2</v>
+      </c>
+      <c r="J13" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I13" s="3">
+      <c r="K13">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="M13" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L13" s="3">
+      <c r="N13" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M13" s="3">
+      <c r="O13">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N13" s="3">
+      <c r="P13" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O13">
+      <c r="Q13" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P13" s="3">
+      <c r="R13" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="S13">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R13" s="3">
+      <c r="T13" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S13">
+      <c r="U13" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T13" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V13" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W13" s="3">
+      <c r="X13" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X13" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y13" s="4" t="e">
@@ -4061,31 +4142,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA13">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC13">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB13">
+      <c r="AD13">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC13">
+      <c r="AE13">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD13">
+      <c r="AF13">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE13">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH13" t="e">
@@ -4096,27 +4177,33 @@
         <v>45</v>
       </c>
       <c r="AJ13" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="AM13">
+        <v>45</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>146</v>
       </c>
       <c r="PS13" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT13" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU13" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT13" s="3">
+      <c r="PV13">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW13">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU13" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW13">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:439" x14ac:dyDescent="0.2">
@@ -4124,95 +4211,95 @@
         <v>115</v>
       </c>
       <c r="B14">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>150</v>
       </c>
       <c r="C14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E14">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E14">
+        <v>150</v>
+      </c>
+      <c r="G14">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K14">
+      <c r="M14" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O14">
+      <c r="Q14" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S14">
+      <c r="U14" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T14" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y14" s="4" t="e">
@@ -4224,31 +4311,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB14">
+      <c r="AD14">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC14">
+      <c r="AE14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD14">
+      <c r="AF14">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE14">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH14" t="e">
@@ -4259,27 +4346,39 @@
         <v>45</v>
       </c>
       <c r="AJ14" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="AM14">
+        <v>45</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ14">
+        <v>60</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>145</v>
       </c>
       <c r="PS14" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT14" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU14" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT14" s="3">
+      <c r="PV14">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW14">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU14" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW14">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:439" x14ac:dyDescent="0.2">
@@ -4287,95 +4386,95 @@
         <v>133</v>
       </c>
       <c r="B15">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>120</v>
       </c>
       <c r="C15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E15">
+        <v>120</v>
+      </c>
+      <c r="G15">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K15">
+      <c r="M15" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O15">
+      <c r="Q15" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S15">
+      <c r="U15" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T15" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V15" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y15" s="4" t="e">
@@ -4387,31 +4486,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA15">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB15">
+      <c r="AD15">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC15">
+      <c r="AE15">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD15">
+      <c r="AF15">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE15">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH15" t="e">
@@ -4422,27 +4521,39 @@
         <v>45</v>
       </c>
       <c r="AJ15" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM15">
+        <v>45</v>
+      </c>
+      <c r="AN15" t="s">
         <v>146</v>
       </c>
+      <c r="AQ15">
+        <v>30</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>146</v>
+      </c>
       <c r="PS15" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT15" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU15" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT15" s="3">
+      <c r="PV15">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW15">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU15" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW15">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:439" x14ac:dyDescent="0.2">
@@ -4450,95 +4561,95 @@
         <v>134</v>
       </c>
       <c r="B16">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>67</v>
       </c>
       <c r="C16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E16">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E16">
+        <v>67</v>
+      </c>
+      <c r="G16">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
         <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="J16" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="3">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W16" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H16" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J16" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="3">
+      <c r="X16" s="4">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="X16" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y16" s="4" t="e">
@@ -4550,31 +4661,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA16">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC16">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB16">
+      <c r="AD16">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC16">
+      <c r="AE16">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE16">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="AF16">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH16" t="e">
@@ -4585,30 +4696,36 @@
         <v>45</v>
       </c>
       <c r="AJ16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK16">
         <v>1</v>
       </c>
+      <c r="AM16">
+        <v>22</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>146</v>
+      </c>
       <c r="PS16" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT16" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU16" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT16" s="3">
+      <c r="PV16">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW16">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU16" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV16">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW16">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:439" x14ac:dyDescent="0.2">
@@ -4616,95 +4733,95 @@
         <v>135</v>
       </c>
       <c r="B17">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>120</v>
       </c>
       <c r="C17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E17">
+        <v>120</v>
+      </c>
+      <c r="G17">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K17">
+      <c r="M17" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O17">
+      <c r="Q17" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S17">
+      <c r="U17" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T17" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V17" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y17" s="4" t="e">
@@ -4716,31 +4833,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC17">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB17">
+      <c r="AD17">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC17">
+      <c r="AE17">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD17">
+      <c r="AF17">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE17">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH17" t="e">
@@ -4751,27 +4868,39 @@
         <v>45</v>
       </c>
       <c r="AJ17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM17">
+        <v>45</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ17">
+        <v>30</v>
+      </c>
+      <c r="AR17" t="s">
         <v>146</v>
       </c>
       <c r="PS17" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT17" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU17" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT17" s="3">
+      <c r="PV17">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW17">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU17" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV17">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW17">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:439" x14ac:dyDescent="0.2">
@@ -4779,95 +4908,95 @@
         <v>119</v>
       </c>
       <c r="B18">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>150</v>
       </c>
       <c r="C18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D18">
+      <c r="F18">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E18">
+        <v>150</v>
+      </c>
+      <c r="G18">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="I18" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18">
         <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J18" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="4">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="X18" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y18" s="4" t="e">
@@ -4879,31 +5008,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC18">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB18">
+      <c r="AD18">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC18">
+      <c r="AE18">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE18">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="AF18">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH18" t="e">
@@ -4914,30 +5043,42 @@
         <v>45</v>
       </c>
       <c r="AJ18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK18">
         <v>1</v>
       </c>
+      <c r="AM18">
+        <v>45</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ18">
+        <v>60</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>145</v>
+      </c>
       <c r="PS18" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT18" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU18" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT18" s="3">
+      <c r="PV18">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW18">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU18" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW18">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:439" x14ac:dyDescent="0.2">
@@ -4945,71 +5086,71 @@
         <v>117</v>
       </c>
       <c r="B19">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>150</v>
       </c>
       <c r="C19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E19">
+        <v>150</v>
+      </c>
+      <c r="G19">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="H19" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="I19" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H19" s="3">
+      <c r="J19" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I19" s="3">
+      <c r="K19">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="M19" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L19" s="3">
+      <c r="N19" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M19" s="3">
+      <c r="O19">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N19" s="3">
+      <c r="P19" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O19">
+      <c r="Q19" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P19" s="3">
+      <c r="R19" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="3">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="3">
-        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S19">
@@ -5017,23 +5158,23 @@
         <v>0</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U19" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V19" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W19" s="3">
+      <c r="X19" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y19" s="4" t="e">
@@ -5045,31 +5186,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA19">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC19">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB19">
+      <c r="AD19">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC19">
+      <c r="AE19">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD19">
+      <c r="AF19">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE19">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH19" t="e">
@@ -5080,27 +5221,39 @@
         <v>45</v>
       </c>
       <c r="AJ19" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="AM19">
+        <v>45</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ19">
+        <v>60</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>145</v>
       </c>
       <c r="PS19" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT19" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU19" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT19" s="3">
+      <c r="PV19">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW19">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU19" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV19">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW19">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:439" x14ac:dyDescent="0.2">
@@ -5108,95 +5261,95 @@
         <v>141</v>
       </c>
       <c r="B20">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>75</v>
       </c>
       <c r="C20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E20">
+        <v>75</v>
+      </c>
+      <c r="G20">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="H20" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H20" s="3">
+        <v>2</v>
+      </c>
+      <c r="J20" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="M20" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O20">
+      <c r="Q20" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S20">
+      <c r="U20" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T20" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y20" s="4" t="e">
@@ -5208,31 +5361,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA20">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC20">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB20">
+      <c r="AD20">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC20">
+      <c r="AE20">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD20">
+      <c r="AF20">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE20">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH20" t="e">
@@ -5243,27 +5396,33 @@
         <v>45</v>
       </c>
       <c r="AJ20" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="AQ20">
+        <v>30</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>146</v>
       </c>
       <c r="PS20" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT20" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU20" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT20" s="3">
+      <c r="PV20">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW20">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU20" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV20">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW20">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:439" x14ac:dyDescent="0.2">
@@ -5271,95 +5430,95 @@
         <v>136</v>
       </c>
       <c r="B21">
-        <f t="shared" si="34"/>
-        <v>22</v>
+        <f t="shared" si="32"/>
+        <v>74</v>
       </c>
       <c r="C21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E21">
+        <v>74</v>
+      </c>
+      <c r="G21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3">
         <f t="shared" si="8"/>
-        <v>22</v>
-      </c>
-      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H21" s="3">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="M21" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O21">
+      <c r="Q21" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S21">
+      <c r="U21" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T21" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y21" s="4" t="e">
@@ -5371,31 +5530,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC21">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB21">
+      <c r="AD21">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC21">
+      <c r="AE21">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD21">
+      <c r="AF21">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE21">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH21" t="e">
@@ -5406,27 +5565,39 @@
         <v>22</v>
       </c>
       <c r="AJ21" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="AM21">
+        <v>22</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>146</v>
+      </c>
+      <c r="AQ21">
+        <v>30</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>146</v>
       </c>
       <c r="PS21" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT21" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU21" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT21" s="3">
+      <c r="PV21">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW21">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU21" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW21">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:439" x14ac:dyDescent="0.2">
@@ -5434,95 +5605,95 @@
         <v>137</v>
       </c>
       <c r="B22">
-        <f t="shared" si="34"/>
-        <v>22</v>
+        <f t="shared" si="32"/>
+        <v>82</v>
       </c>
       <c r="C22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E22">
+        <v>82</v>
+      </c>
+      <c r="G22">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <f t="shared" si="8"/>
-        <v>22</v>
-      </c>
-      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H22" s="3">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="M22" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O22">
+      <c r="Q22" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S22">
+      <c r="U22" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T22" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y22" s="4" t="e">
@@ -5534,31 +5705,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA22">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC22">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB22">
+      <c r="AD22">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC22">
+      <c r="AE22">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD22">
+      <c r="AF22">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AG22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH22" t="e">
@@ -5569,30 +5740,42 @@
         <v>22</v>
       </c>
       <c r="AJ22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AL22">
         <v>1</v>
       </c>
+      <c r="AM22">
+        <v>30</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>146</v>
+      </c>
+      <c r="AQ22">
+        <v>30</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>146</v>
+      </c>
       <c r="PS22" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT22" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU22" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT22" s="3">
+      <c r="PV22">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW22">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU22" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV22">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW22">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:439" x14ac:dyDescent="0.2">
@@ -5600,95 +5783,95 @@
         <v>138</v>
       </c>
       <c r="B23">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>60</v>
       </c>
       <c r="C23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E23">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E23">
+        <v>60</v>
+      </c>
+      <c r="G23">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="H23" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I23" s="3">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X23" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y23" s="4" t="e">
@@ -5700,31 +5883,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA23">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB23">
+      <c r="AD23">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC23">
+      <c r="AE23">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AF23">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE23">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH23" t="e">
@@ -5735,27 +5918,36 @@
         <v>45</v>
       </c>
       <c r="AJ23" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM23">
+        <v>15</v>
+      </c>
+      <c r="AN23" t="s">
         <v>146</v>
       </c>
+      <c r="AO23">
+        <v>1</v>
+      </c>
       <c r="PS23" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT23" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU23" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT23" s="3">
+      <c r="PV23">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW23">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU23" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV23">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW23">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:439" x14ac:dyDescent="0.2">
@@ -5763,95 +5955,95 @@
         <v>140</v>
       </c>
       <c r="B24">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>90</v>
       </c>
       <c r="C24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E24">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E24">
+        <v>90</v>
+      </c>
+      <c r="G24">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="H24" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K24">
+      <c r="M24" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O24">
+      <c r="Q24" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S24">
+      <c r="U24" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T24" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y24" s="4" t="e">
@@ -5863,31 +6055,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA24">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC24">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB24">
+      <c r="AD24">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC24">
+      <c r="AE24">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD24">
+      <c r="AF24">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE24">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH24" t="e">
@@ -5898,27 +6090,33 @@
         <v>45</v>
       </c>
       <c r="AJ24" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM24">
+        <v>45</v>
+      </c>
+      <c r="AN24" t="s">
         <v>146</v>
       </c>
       <c r="PS24" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT24" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU24" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT24" s="3">
+      <c r="PV24">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW24">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU24" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV24">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW24">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:439" x14ac:dyDescent="0.2">
@@ -5926,95 +6124,95 @@
         <v>139</v>
       </c>
       <c r="B25">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>120</v>
       </c>
       <c r="C25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E25">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D25">
+      <c r="F25">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E25">
+        <v>120</v>
+      </c>
+      <c r="G25">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="H25" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
         <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="J25" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H25" s="3">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="I25" s="3">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="3">
+      <c r="X25" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y25" s="4" t="e">
@@ -6026,31 +6224,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA25">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC25">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB25">
+      <c r="AD25">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC25">
+      <c r="AE25">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AD25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE25">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH25" t="e">
@@ -6061,27 +6259,42 @@
         <v>45</v>
       </c>
       <c r="AJ25" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM25">
+        <v>45</v>
+      </c>
+      <c r="AN25" t="s">
         <v>146</v>
       </c>
+      <c r="AQ25">
+        <v>30</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>146</v>
+      </c>
+      <c r="AS25">
+        <v>1</v>
+      </c>
       <c r="PS25" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT25" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU25" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT25" s="3">
+      <c r="PV25">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW25">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU25" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV25">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW25">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:439" x14ac:dyDescent="0.2">
@@ -6089,95 +6302,95 @@
         <v>116</v>
       </c>
       <c r="B26">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="C26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E26">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D26">
+      <c r="F26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="H26" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G26">
+      <c r="I26" s="3">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K26">
+      <c r="M26" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O26">
+      <c r="Q26" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S26">
+      <c r="U26" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T26" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y26" s="4" t="e">
@@ -6189,31 +6402,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA26">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC26">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB26">
+      <c r="AD26">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC26">
+      <c r="AE26">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD26">
+      <c r="AF26">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE26">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH26" t="e">
@@ -6221,23 +6434,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS26" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT26" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU26" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT26" s="3">
+      <c r="PV26">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW26">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU26" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV26">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW26">
-        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -6246,95 +6459,95 @@
         <v>142</v>
       </c>
       <c r="B27">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>90</v>
       </c>
       <c r="C27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E27">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D27">
+      <c r="F27">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E27">
+        <v>90</v>
+      </c>
+      <c r="G27">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="H27" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K27">
+      <c r="M27" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O27">
+      <c r="Q27" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S27">
+      <c r="U27" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T27" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y27" s="4" t="e">
@@ -6346,31 +6559,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA27">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC27">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB27">
+      <c r="AD27">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC27">
+      <c r="AE27">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD27">
+      <c r="AF27">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE27">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH27" t="e">
@@ -6381,27 +6594,33 @@
         <v>45</v>
       </c>
       <c r="AJ27" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM27">
+        <v>45</v>
+      </c>
+      <c r="AN27" t="s">
         <v>146</v>
       </c>
       <c r="PS27" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT27" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU27" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT27" s="3">
+      <c r="PV27">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW27">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU27" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV27">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW27">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:439" x14ac:dyDescent="0.2">
@@ -6409,95 +6628,95 @@
         <v>143</v>
       </c>
       <c r="B28">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" si="32"/>
+        <v>120</v>
       </c>
       <c r="C28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E28">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E28">
+        <v>120</v>
+      </c>
+      <c r="G28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="H28" s="3">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H28" s="3">
+        <v>2</v>
+      </c>
+      <c r="J28" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J28" s="3">
+      <c r="L28" s="3">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K28">
+      <c r="M28" s="3">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L28" s="3">
+      <c r="N28" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M28" s="3">
+      <c r="O28">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N28" s="3">
+      <c r="P28" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O28">
+      <c r="Q28" s="3">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P28" s="3">
+      <c r="R28" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="S28">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R28" s="3">
+      <c r="T28" s="3">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S28">
+      <c r="U28" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="T28" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="V28" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W28" s="3">
+      <c r="X28" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y28" s="4" t="e">
@@ -6509,31 +6728,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA28">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AC28">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AB28">
+      <c r="AD28">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AC28">
+      <c r="AE28">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AD28">
+      <c r="AF28">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AE28">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="AG28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH28" t="e">
@@ -6544,27 +6763,39 @@
         <v>45</v>
       </c>
       <c r="AJ28" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM28">
+        <v>45</v>
+      </c>
+      <c r="AN28" t="s">
         <v>146</v>
       </c>
+      <c r="AQ28">
+        <v>30</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>146</v>
+      </c>
       <c r="PS28" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="PT28" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="PU28" s="3">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="PT28" s="3">
+      <c r="PV28">
+        <f>COUNTIF(IU:PR,"HG")</f>
+        <v>0</v>
+      </c>
+      <c r="PW28">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="PU28" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="PV28">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="PW28">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:439" x14ac:dyDescent="0.2">
@@ -6572,95 +6803,95 @@
         <v>144</v>
       </c>
       <c r="B29">
-        <f t="shared" si="34"/>
-        <v>45</v>
+        <f t="shared" ref="B29" si="56">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
+        <v>120</v>
       </c>
       <c r="C29">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C29" si="57">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
         <v>0</v>
       </c>
       <c r="D29">
+        <f t="shared" ref="D29" si="58">SUM(GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29)</f>
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ref="E29" si="59">SUM(IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
+        <v>0</v>
+      </c>
+      <c r="F29">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="8"/>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="G29">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="G29" si="60">SUM(H29:I29)</f>
+        <v>3</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" ref="H29" si="61">COUNTIF(AI29:PR29,"T")</f>
         <v>1</v>
       </c>
-      <c r="H29" s="3">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
       <c r="I29" s="3">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" ref="I29" si="62">COUNTIF(AI29:PR29,"R")</f>
+        <v>2</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="J29" si="63">COUNTIF(AI29:PR29,"NR")</f>
         <v>0</v>
       </c>
       <c r="K29">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="K29" si="64">SUM(L29:M29)</f>
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="L29" si="65">COUNTIF(CY29:GX29,"T")</f>
         <v>0</v>
       </c>
       <c r="M29" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="M29" si="66">COUNTIF(CY29:GX29,"R")</f>
         <v>0</v>
       </c>
       <c r="N29" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="N29" si="67">COUNTIF(CY29:GX29,"NR")</f>
         <v>0</v>
       </c>
       <c r="O29">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="O29" si="68">SUM(P29:Q29)</f>
         <v>0</v>
       </c>
       <c r="P29" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="P29" si="69">COUNTIF(GY29:IT29,"T")</f>
         <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="Q29" si="70">COUNTIF(GY29:IT29,"R")</f>
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="R29" si="71">COUNTIF(GY29:IT29,"NR")</f>
         <v>0</v>
       </c>
       <c r="S29">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="S29" si="72">SUM(T29:U29)</f>
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="T29" si="73">COUNTIF(IU29:PR29,"T")</f>
         <v>0</v>
       </c>
       <c r="U29" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="U29" si="74">COUNTIF(IU29:PR29,"R")</f>
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <f>COUNTIF(IU:PR,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X29" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y29" s="4" t="e">
@@ -6672,31 +6903,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA29">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="AA29" si="75">SUM(DA29,DE29,DI29,DM29,DQ29,DU29,DY29,EC29,EG29,EK29,EO29,ES29,EW29,FA29,FE29,FI29,FM29,FQ29,FU29,FY29,GC29,GG29,GK29,GO29,GS29,GW29)</f>
         <v>0</v>
       </c>
       <c r="AB29">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="AB29" si="76">SUM(DB29,DF29,DJ29,DN29,DR29,DV29,DZ29,ED29,EH29,EL29,EP29,ET29,EX29,FB29,FF29,FJ29,FN29,FR29,FV29,FZ29,GD29,GH29,GL29,GP29,GT29,GX29)</f>
         <v>0</v>
       </c>
       <c r="AC29">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="AC29" si="77">SUM(HA29,HE29,HI29,HM29,HQ29,HU29,HY29,IC29,IG29,IK29,IO29,IS29)</f>
         <v>0</v>
       </c>
       <c r="AD29">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="AD29" si="78">SUM(HB29,HF29,HJ29,HN29,HR29,HV29,HZ29,ID29,IH29,IL29,IP29,IT29)</f>
         <v>0</v>
       </c>
       <c r="AE29">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="AE29" si="79">SUM(AK29,AO29,AS29,AW29,BA29,BE29,BI29,BM29,BQ29,BU29,BY29,CC29,CG29,CK29,CO29,CS29,CW29)</f>
         <v>0</v>
       </c>
       <c r="AF29">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="AF29" si="80">SUM(AL29,AP29,AT29,AX29,BB29,BF29,BJ29,BN29,BR29,BV29,BZ29,CD29,CH29,CL29,CP29,CT29,CX29)</f>
         <v>0</v>
       </c>
       <c r="AG29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH29" t="e">
@@ -6707,123 +6938,132 @@
         <v>45</v>
       </c>
       <c r="AJ29" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM29">
+        <v>45</v>
+      </c>
+      <c r="AN29" t="s">
         <v>146</v>
       </c>
+      <c r="AQ29">
+        <v>30</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>146</v>
+      </c>
       <c r="PS29" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="PS29" si="81">COUNTIF(AI29:PR29,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT29" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="PT29" si="82">COUNTIF(CY29:GX29,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU29" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="PU29" si="83">COUNTIF(GY29:IT29,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV29">
-        <f t="shared" si="4"/>
+        <f>COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW29">
-        <f t="shared" si="33"/>
-        <v>1</v>
+        <f t="shared" ref="PW29" si="84">G29-(K29+O29+S29)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:439" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>145</v>
-      </c>
       <c r="B30">
-        <f t="shared" ref="B30" si="58">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>45</v>
+        <f t="shared" ref="B30" si="85">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
+        <v>0</v>
       </c>
       <c r="C30">
-        <f t="shared" ref="C30" si="59">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
+        <f t="shared" ref="C30" si="86">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
         <v>0</v>
       </c>
       <c r="D30">
-        <f t="shared" ref="D30" si="60">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
+        <f t="shared" ref="D30" si="87">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
         <v>0</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30" si="61">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
+        <f t="shared" ref="E30" si="88">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
         <v>0</v>
       </c>
       <c r="F30">
-        <f t="shared" si="8"/>
-        <v>45</v>
+        <f t="shared" ref="F30" si="89">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30)</f>
+        <v>0</v>
       </c>
       <c r="G30">
-        <f t="shared" ref="G30" si="62">SUM(H30:I30)</f>
-        <v>1</v>
+        <f t="shared" ref="G30" si="90">SUM(H30:I30)</f>
+        <v>0</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" ref="H30" si="63">COUNTIF(AI30:PR30,"T")</f>
-        <v>1</v>
+        <f t="shared" ref="H30" si="91">COUNTIF(AI30:PR30,"T")</f>
+        <v>0</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" ref="I30" si="64">COUNTIF(AI30:PR30,"R")</f>
+        <f t="shared" ref="I30" si="92">COUNTIF(AI30:PR30,"R")</f>
         <v>0</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" ref="J30" si="65">COUNTIF(AI30:PR30,"NR")</f>
+        <f t="shared" ref="J30" si="93">COUNTIF(AI30:PR30,"NR")</f>
         <v>0</v>
       </c>
       <c r="K30">
-        <f t="shared" ref="K30" si="66">SUM(L30:M30)</f>
+        <f t="shared" ref="K30" si="94">SUM(L30:M30)</f>
         <v>0</v>
       </c>
       <c r="L30" s="3">
-        <f t="shared" ref="L30" si="67">COUNTIF(CY30:GX30,"T")</f>
+        <f t="shared" ref="L30" si="95">COUNTIF(CY30:GX30,"T")</f>
         <v>0</v>
       </c>
       <c r="M30" s="3">
-        <f t="shared" ref="M30" si="68">COUNTIF(CY30:GX30,"R")</f>
+        <f t="shared" ref="M30" si="96">COUNTIF(CY30:GX30,"R")</f>
         <v>0</v>
       </c>
       <c r="N30" s="3">
-        <f t="shared" ref="N30" si="69">COUNTIF(CY30:GX30,"NR")</f>
+        <f t="shared" ref="N30" si="97">COUNTIF(CY30:GX30,"NR")</f>
         <v>0</v>
       </c>
       <c r="O30">
-        <f t="shared" ref="O30" si="70">SUM(P30:Q30)</f>
+        <f t="shared" ref="O30" si="98">SUM(P30:Q30)</f>
         <v>0</v>
       </c>
       <c r="P30" s="3">
-        <f t="shared" ref="P30" si="71">COUNTIF(GY30:IT30,"T")</f>
+        <f t="shared" ref="P30" si="99">COUNTIF(GY30:IT30,"T")</f>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" ref="Q30" si="72">COUNTIF(GY30:IT30,"R")</f>
+        <f t="shared" ref="Q30" si="100">COUNTIF(GY30:IT30,"R")</f>
         <v>0</v>
       </c>
       <c r="R30" s="3">
-        <f t="shared" ref="R30" si="73">COUNTIF(GY30:IT30,"NR")</f>
+        <f t="shared" ref="R30" si="101">COUNTIF(GY30:IT30,"NR")</f>
         <v>0</v>
       </c>
       <c r="S30">
-        <f t="shared" ref="S30" si="74">SUM(T30:U30)</f>
+        <f t="shared" ref="S30" si="102">SUM(T30:U30)</f>
         <v>0</v>
       </c>
       <c r="T30" s="3">
-        <f t="shared" ref="T30" si="75">COUNTIF(IU30:PR30,"T")</f>
+        <f t="shared" ref="T30" si="103">COUNTIF(IU30:PR30,"T")</f>
         <v>0</v>
       </c>
       <c r="U30" s="3">
-        <f t="shared" ref="U30" si="76">COUNTIF(IU30:PR30,"R")</f>
+        <f t="shared" ref="U30" si="104">COUNTIF(IU30:PR30,"R")</f>
         <v>0</v>
       </c>
       <c r="V30" s="3">
-        <f t="shared" ref="V30" si="77">COUNTIF(IU:PR,"NR")</f>
+        <f>COUNTIF(IU:PR,"NR")</f>
         <v>0</v>
       </c>
       <c r="W30" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X30" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y30" s="4" t="e">
@@ -6835,155 +7075,149 @@
         <v>#REF!</v>
       </c>
       <c r="AA30">
-        <f t="shared" ref="AA30" si="78">SUM(DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30)</f>
+        <f t="shared" ref="AA30" si="105">SUM(DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30)</f>
         <v>0</v>
       </c>
       <c r="AB30">
-        <f t="shared" ref="AB30" si="79">SUM(DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30)</f>
+        <f t="shared" ref="AB30" si="106">SUM(DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30)</f>
         <v>0</v>
       </c>
       <c r="AC30">
-        <f t="shared" ref="AC30" si="80">SUM(HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30)</f>
+        <f t="shared" ref="AC30" si="107">SUM(HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30)</f>
         <v>0</v>
       </c>
       <c r="AD30">
-        <f t="shared" ref="AD30" si="81">SUM(HB30,HF30,HJ30,HN30,HR30,HV30,HZ30,ID30,IH30,IL30,IP30,IT30)</f>
+        <f t="shared" ref="AD30" si="108">SUM(HB30,HF30,HJ30,HN30,HR30,HV30,HZ30,ID30,IH30,IL30,IP30,IT30)</f>
         <v>0</v>
       </c>
       <c r="AE30">
-        <f t="shared" ref="AE30" si="82">SUM(AK30,AO30,AS30,AW30,BA30,BE30,BI30,BM30,BQ30,BU30,BY30,CC30,CG30,CK30,CO30,CS30,CW30)</f>
+        <f t="shared" ref="AE30" si="109">SUM(AK30,AO30,AS30,AW30,BA30,BE30,BI30,BM30,BQ30,BU30,BY30,CC30,CG30,CK30,CO30,CS30,CW30)</f>
         <v>0</v>
       </c>
       <c r="AF30">
-        <f t="shared" ref="AF30" si="83">SUM(AL30,AP30,AT30,AX30,BB30,BF30,BJ30,BN30,BR30,BV30,BZ30,CD30,CH30,CL30,CP30,CT30,CX30)</f>
+        <f t="shared" ref="AF30" si="110">SUM(AL30,AP30,AT30,AX30,BB30,BF30,BJ30,BN30,BR30,BV30,BZ30,CD30,CH30,CL30,CP30,CT30,CX30)</f>
         <v>0</v>
       </c>
       <c r="AG30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH30" t="e">
         <f>SUM(IX30,JB30,JF30,JJ30,JN30,JR30,JV30,JZ30,KD30,KH30,KL30,KP30,KT30,KX30,LB30,LF30,LJ30,LN30,LR30,LV30,LZ30,MD30,#REF!,ML30,MP30,MT30,MX30,NB30,NF30,NJ30,NN30,NR30,NV30,NZ30,OD30,OH30,OL30,OP30,OT30,OX30,PB30,PF30,PJ30,PN30,PR30)</f>
         <v>#REF!</v>
       </c>
-      <c r="AI30">
-        <v>45</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>146</v>
-      </c>
       <c r="PS30" s="3">
-        <f t="shared" ref="PS30" si="84">COUNTIF(AI30:PR30,"HG")</f>
+        <f t="shared" ref="PS30" si="111">COUNTIF(AI30:PR30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT30" s="3">
-        <f t="shared" ref="PT30" si="85">COUNTIF(CY30:GX30,"HG")</f>
+        <f t="shared" ref="PT30" si="112">COUNTIF(CY30:GX30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU30" s="3">
-        <f t="shared" ref="PU30" si="86">COUNTIF(GY30:IT30,"HG")</f>
+        <f t="shared" ref="PU30" si="113">COUNTIF(GY30:IT30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV30">
-        <f t="shared" ref="PV30" si="87">COUNTIF(IU:PR,"HG")</f>
+        <f>COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW30">
-        <f t="shared" ref="PW30" si="88">G30-(K30+O30+S30)</f>
-        <v>1</v>
+        <f t="shared" ref="PW30" si="114">G30-(K30+O30+S30)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B31">
-        <f t="shared" ref="B31" si="89">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
+        <f t="shared" ref="B31" si="115">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
         <v>0</v>
       </c>
       <c r="C31">
-        <f t="shared" ref="C31" si="90">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
+        <f t="shared" ref="C31" si="116">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
         <v>0</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31" si="91">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
+        <f t="shared" ref="D31" si="117">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
         <v>0</v>
       </c>
       <c r="E31">
-        <f t="shared" ref="E31" si="92">SUM(IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
+        <f t="shared" ref="E31" si="118">SUM(IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
         <v>0</v>
       </c>
       <c r="F31">
-        <f t="shared" ref="F31" si="93">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31)</f>
+        <f t="shared" ref="F31" si="119">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31)</f>
         <v>0</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="94">SUM(H31:I31)</f>
+        <f t="shared" ref="G31" si="120">SUM(H31:I31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" ref="H31" si="95">COUNTIF(AI31:PR31,"T")</f>
+        <f t="shared" ref="H31" si="121">COUNTIF(AI31:PR31,"T")</f>
         <v>0</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" ref="I31" si="96">COUNTIF(AI31:PR31,"R")</f>
+        <f t="shared" ref="I31" si="122">COUNTIF(AI31:PR31,"R")</f>
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" ref="J31" si="97">COUNTIF(AI31:PR31,"NR")</f>
+        <f t="shared" ref="J31" si="123">COUNTIF(AI31:PR31,"NR")</f>
         <v>0</v>
       </c>
       <c r="K31">
-        <f t="shared" ref="K31" si="98">SUM(L31:M31)</f>
+        <f t="shared" ref="K31" si="124">SUM(L31:M31)</f>
         <v>0</v>
       </c>
       <c r="L31" s="3">
-        <f t="shared" ref="L31" si="99">COUNTIF(CY31:GX31,"T")</f>
+        <f t="shared" ref="L31" si="125">COUNTIF(CY31:GX31,"T")</f>
         <v>0</v>
       </c>
       <c r="M31" s="3">
-        <f t="shared" ref="M31" si="100">COUNTIF(CY31:GX31,"R")</f>
+        <f t="shared" ref="M31" si="126">COUNTIF(CY31:GX31,"R")</f>
         <v>0</v>
       </c>
       <c r="N31" s="3">
-        <f t="shared" ref="N31" si="101">COUNTIF(CY31:GX31,"NR")</f>
+        <f t="shared" ref="N31" si="127">COUNTIF(CY31:GX31,"NR")</f>
         <v>0</v>
       </c>
       <c r="O31">
-        <f t="shared" ref="O31" si="102">SUM(P31:Q31)</f>
+        <f t="shared" ref="O31" si="128">SUM(P31:Q31)</f>
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f t="shared" ref="P31" si="103">COUNTIF(GY31:IT31,"T")</f>
+        <f t="shared" ref="P31" si="129">COUNTIF(GY31:IT31,"T")</f>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <f t="shared" ref="Q31" si="104">COUNTIF(GY31:IT31,"R")</f>
+        <f t="shared" ref="Q31" si="130">COUNTIF(GY31:IT31,"R")</f>
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <f t="shared" ref="R31" si="105">COUNTIF(GY31:IT31,"NR")</f>
+        <f t="shared" ref="R31" si="131">COUNTIF(GY31:IT31,"NR")</f>
         <v>0</v>
       </c>
       <c r="S31">
-        <f t="shared" ref="S31" si="106">SUM(T31:U31)</f>
+        <f t="shared" ref="S31" si="132">SUM(T31:U31)</f>
         <v>0</v>
       </c>
       <c r="T31" s="3">
-        <f t="shared" ref="T31" si="107">COUNTIF(IU31:PR31,"T")</f>
+        <f t="shared" ref="T31" si="133">COUNTIF(IU31:PR31,"T")</f>
         <v>0</v>
       </c>
       <c r="U31" s="3">
-        <f t="shared" ref="U31" si="108">COUNTIF(IU31:PR31,"R")</f>
+        <f t="shared" ref="U31" si="134">COUNTIF(IU31:PR31,"R")</f>
         <v>0</v>
       </c>
       <c r="V31" s="3">
-        <f t="shared" ref="V31" si="109">COUNTIF(IU:PR,"NR")</f>
+        <f>COUNTIF(IU:PR,"NR")</f>
         <v>0</v>
       </c>
       <c r="W31" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="4">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y31" s="4" t="e">
@@ -6995,31 +7229,31 @@
         <v>#REF!</v>
       </c>
       <c r="AA31">
-        <f t="shared" ref="AA31" si="110">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
+        <f t="shared" ref="AA31" si="135">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
         <v>0</v>
       </c>
       <c r="AB31">
-        <f t="shared" ref="AB31" si="111">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
+        <f t="shared" ref="AB31" si="136">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
         <v>0</v>
       </c>
       <c r="AC31">
-        <f t="shared" ref="AC31" si="112">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
+        <f t="shared" ref="AC31" si="137">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
         <v>0</v>
       </c>
       <c r="AD31">
-        <f t="shared" ref="AD31" si="113">SUM(HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31)</f>
+        <f t="shared" ref="AD31" si="138">SUM(HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31)</f>
         <v>0</v>
       </c>
       <c r="AE31">
-        <f t="shared" ref="AE31" si="114">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31)</f>
+        <f t="shared" ref="AE31" si="139">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31)</f>
         <v>0</v>
       </c>
       <c r="AF31">
-        <f t="shared" ref="AF31" si="115">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31)</f>
+        <f t="shared" ref="AF31" si="140">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31)</f>
         <v>0</v>
       </c>
       <c r="AG31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AH31" t="e">
@@ -7027,177 +7261,23 @@
         <v>#REF!</v>
       </c>
       <c r="PS31" s="3">
-        <f t="shared" ref="PS31" si="116">COUNTIF(AI31:PR31,"HG")</f>
+        <f t="shared" ref="PS31" si="141">COUNTIF(AI31:PR31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT31" s="3">
-        <f t="shared" ref="PT31" si="117">COUNTIF(CY31:GX31,"HG")</f>
+        <f t="shared" ref="PT31" si="142">COUNTIF(CY31:GX31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU31" s="3">
-        <f t="shared" ref="PU31" si="118">COUNTIF(GY31:IT31,"HG")</f>
+        <f t="shared" ref="PU31" si="143">COUNTIF(GY31:IT31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV31">
-        <f t="shared" ref="PV31" si="119">COUNTIF(IU:PR,"HG")</f>
+        <f>COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW31">
-        <f t="shared" ref="PW31" si="120">G31-(K31+O31+S31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:439" x14ac:dyDescent="0.2">
-      <c r="B32">
-        <f t="shared" ref="B32" si="121">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>0</v>
-      </c>
-      <c r="C32">
-        <f t="shared" ref="C32" si="122">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <f t="shared" ref="D32" si="123">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <f t="shared" ref="E32" si="124">SUM(IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <f t="shared" ref="F32" si="125">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32)</f>
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <f t="shared" ref="G32" si="126">SUM(H32:I32)</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <f t="shared" ref="H32" si="127">COUNTIF(AI32:PR32,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <f t="shared" ref="I32" si="128">COUNTIF(AI32:PR32,"R")</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <f t="shared" ref="J32" si="129">COUNTIF(AI32:PR32,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <f t="shared" ref="K32" si="130">SUM(L32:M32)</f>
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <f t="shared" ref="L32" si="131">COUNTIF(CY32:GX32,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <f t="shared" ref="M32" si="132">COUNTIF(CY32:GX32,"R")</f>
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <f t="shared" ref="N32" si="133">COUNTIF(CY32:GX32,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <f t="shared" ref="O32" si="134">SUM(P32:Q32)</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <f t="shared" ref="P32" si="135">COUNTIF(GY32:IT32,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <f t="shared" ref="Q32" si="136">COUNTIF(GY32:IT32,"R")</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <f t="shared" ref="R32" si="137">COUNTIF(GY32:IT32,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <f t="shared" ref="S32" si="138">SUM(T32:U32)</f>
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <f t="shared" ref="T32" si="139">COUNTIF(IU32:PR32,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <f t="shared" ref="U32" si="140">COUNTIF(IU32:PR32,"R")</f>
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <f t="shared" ref="V32" si="141">COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="4" t="e">
-        <f>SUM(AL32,AP32,AT32,AX32,BB32,BF32,BJ32,BN32,BR32,BV32,BZ32,CD32,CH32,CL32,CP32,CT32,CX32,DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32,HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32,IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,#REF!,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z32" s="4" t="e">
-        <f>SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32,HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32,IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,#REF!,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA32">
-        <f t="shared" ref="AA32" si="142">SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32)</f>
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <f t="shared" ref="AB32" si="143">SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32)</f>
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <f t="shared" ref="AC32" si="144">SUM(HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32)</f>
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <f t="shared" ref="AD32" si="145">SUM(HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32)</f>
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <f t="shared" ref="AE32" si="146">SUM(AK32,AO32,AS32,AW32,BA32,BE32,BI32,BM32,BQ32,BU32,BY32,CC32,CG32,CK32,CO32,CS32,CW32)</f>
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <f t="shared" ref="AF32" si="147">SUM(AL32,AP32,AT32,AX32,BB32,BF32,BJ32,BN32,BR32,BV32,BZ32,CD32,CH32,CL32,CP32,CT32,CX32)</f>
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH32" t="e">
-        <f>SUM(IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,#REF!,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="PS32" s="3">
-        <f t="shared" ref="PS32" si="148">COUNTIF(AI32:PR32,"HG")</f>
-        <v>0</v>
-      </c>
-      <c r="PT32" s="3">
-        <f t="shared" ref="PT32" si="149">COUNTIF(CY32:GX32,"HG")</f>
-        <v>0</v>
-      </c>
-      <c r="PU32" s="3">
-        <f t="shared" ref="PU32" si="150">COUNTIF(GY32:IT32,"HG")</f>
-        <v>0</v>
-      </c>
-      <c r="PV32">
-        <f t="shared" ref="PV32" si="151">COUNTIF(IU:PR,"HG")</f>
-        <v>0</v>
-      </c>
-      <c r="PW32">
-        <f t="shared" ref="PW32" si="152">G32-(K32+O32+S32)</f>
+        <f t="shared" ref="PW31" si="144">G31-(K31+O31+S31)</f>
         <v>0</v>
       </c>
     </row>

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA475DC-5E9E-8241-BC42-EFFE849C6D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BE5E4A-7F7C-794C-AAF1-F24D7680E5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -2275,24 +2275,24 @@
         <v>0</v>
       </c>
       <c r="V2" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" ref="V2:V31" si="0">COUNTIF(IU:PR,"NR")</f>
         <v>0</v>
       </c>
       <c r="W2" s="3">
-        <f t="shared" ref="W2:W31" si="0">SUM(AK2,AO2,AS2,AW2,BA2,BE2,BI2,BM2,BQ2,BU2,BY2,CC2,CG2,CK2,CO2,CS2,CW2,DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <f t="shared" ref="W2:W31" si="1">SUM(AK2,AO2,AS2,AW2,BA2,BE2,BI2,BM2,BQ2,BU2,BY2,CC2,CG2,CK2,CO2,CS2,CW2,DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
         <v>0</v>
       </c>
       <c r="X2" s="4">
-        <f t="shared" ref="X2:X31" si="1">SUM(DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
-        <v>0</v>
-      </c>
-      <c r="Y2" s="4" t="e">
-        <f>SUM(AL2,AP2,AT2,AX2,BB2,BF2,BJ2,BN2,BR2,BV2,BZ2,CD2,CH2,CL2,CP2,CT2,CX2,DB2,DF2,DJ2,DN2,DR2,DV2,DZ2,ED2,EH2,EL2,EP2,ET2,EX2,FB2,FF2,FJ2,FN2,FR2,FV2,FZ2,GD2,GH2,GL2,GP2,GT2,GX2,HB2,HF2,HJ2,HN2,HR2,HV2,HZ2,ID2,IH2,IL2,IP2,IT2,IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,#REF!,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z2" s="4" t="e">
-        <f>SUM(DB2,DF2,DJ2,DN2,DR2,DV2,DZ2,ED2,EH2,EL2,EP2,ET2,EX2,FB2,FF2,FJ2,FN2,FR2,FV2,FZ2,GD2,GH2,GL2,GP2,GT2,GX2,HB2,HF2,HJ2,HN2,HR2,HV2,HZ2,ID2,IH2,IL2,IP2,IT2,IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,#REF!,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
-        <v>#REF!</v>
+        <f t="shared" ref="X2:X31" si="2">SUM(DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2,HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2,IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <f>SUM(AL2,AP2,AT2,AX2,BB2,BF2,BJ2,BN2,BR2,BV2,BZ2,CD2,CH2,CL2,CP2,CT2,CX2,DB2,DF2,DJ2,DN2,DR2,DV2,DZ2,ED2,EH2,EL2,EP2,ET2,EX2,FB2,FF2,FJ2,FN2,FR2,FV2,FZ2,GD2,GH2,GL2,GP2,GT2,GX2,HB2,HF2,HJ2,HN2,HR2,HV2,HZ2,ID2,IH2,IL2,IP2,IT2,IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <f>SUM(DB2,DF2,DJ2,DN2,DR2,DV2,DZ2,ED2,EH2,EL2,EP2,ET2,EX2,FB2,FF2,FJ2,FN2,FR2,FV2,FZ2,GD2,GH2,GL2,GP2,GT2,GX2,HB2,HF2,HJ2,HN2,HR2,HV2,HZ2,ID2,IH2,IL2,IP2,IT2,IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
+        <v>0</v>
       </c>
       <c r="AA2">
         <f>SUM(DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2)</f>
@@ -2319,12 +2319,12 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <f t="shared" ref="AG2:AG31" si="2">SUM(IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
-        <v>0</v>
-      </c>
-      <c r="AH2" t="e">
-        <f>SUM(IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,#REF!,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
-        <v>#REF!</v>
+        <f t="shared" ref="AG2:AG31" si="3">SUM(IW2,JA2,JE2,JI2,JM2,JQ2,JU2,JY2,KC2,KG2,KK2,KO2,KS2,KW2,LA2,LE2,LI2,LM2,LQ2,LU2,LY2,MC2,MH2,MK2,MO2,MS2,MW2,NA2,NE2,NI2,NM2,NQ2,NU2,NY2,OC2,OG2,OK2,OO2,OS2,OW2,PA2,PE2,PI2,PM2,PQ2)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f>SUM(IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
+        <v>0</v>
       </c>
       <c r="AQ2">
         <v>60</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="PV2">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" ref="PV2:PV31" si="4">COUNTIF(IU:PR,"HG")</f>
         <v>0</v>
       </c>
       <c r="PW2">
@@ -2362,151 +2362,151 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C28" si="3">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
+        <f t="shared" ref="C3:C28" si="5">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D28" si="4">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
+        <f t="shared" ref="D3:D28" si="6">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E28" si="5">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
+        <f t="shared" ref="E3:E28" si="7">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F29" si="6">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
+        <f t="shared" ref="F3:F29" si="8">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G28" si="7">SUM(H3:I3)</f>
+        <f t="shared" ref="G3:G28" si="9">SUM(H3:I3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H28" si="8">COUNTIF(AI3:PR3,"T")</f>
+        <f t="shared" ref="H3:H28" si="10">COUNTIF(AI3:PR3,"T")</f>
         <v>0</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I28" si="9">COUNTIF(AI3:PR3,"R")</f>
+        <f t="shared" ref="I3:I28" si="11">COUNTIF(AI3:PR3,"R")</f>
         <v>0</v>
       </c>
       <c r="J3" s="3">
-        <f t="shared" ref="J3:J28" si="10">COUNTIF(AI3:PR3,"NR")</f>
+        <f t="shared" ref="J3:J28" si="12">COUNTIF(AI3:PR3,"NR")</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K28" si="11">SUM(L3:M3)</f>
+        <f t="shared" ref="K3:K28" si="13">SUM(L3:M3)</f>
         <v>0</v>
       </c>
       <c r="L3" s="3">
-        <f t="shared" ref="L3:L28" si="12">COUNTIF(CY3:GX3,"T")</f>
+        <f t="shared" ref="L3:L28" si="14">COUNTIF(CY3:GX3,"T")</f>
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <f t="shared" ref="M3:M28" si="13">COUNTIF(CY3:GX3,"R")</f>
+        <f t="shared" ref="M3:M28" si="15">COUNTIF(CY3:GX3,"R")</f>
         <v>0</v>
       </c>
       <c r="N3" s="3">
-        <f t="shared" ref="N3:N28" si="14">COUNTIF(CY3:GX3,"NR")</f>
+        <f t="shared" ref="N3:N28" si="16">COUNTIF(CY3:GX3,"NR")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O28" si="15">SUM(P3:Q3)</f>
+        <f t="shared" ref="O3:O28" si="17">SUM(P3:Q3)</f>
         <v>0</v>
       </c>
       <c r="P3" s="3">
-        <f t="shared" ref="P3:P28" si="16">COUNTIF(GY3:IT3,"T")</f>
+        <f t="shared" ref="P3:P28" si="18">COUNTIF(GY3:IT3,"T")</f>
         <v>0</v>
       </c>
       <c r="Q3" s="3">
-        <f t="shared" ref="Q3:Q28" si="17">COUNTIF(GY3:IT3,"R")</f>
+        <f t="shared" ref="Q3:Q28" si="19">COUNTIF(GY3:IT3,"R")</f>
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <f t="shared" ref="R3:R28" si="18">COUNTIF(GY3:IT3,"NR")</f>
+        <f t="shared" ref="R3:R28" si="20">COUNTIF(GY3:IT3,"NR")</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S28" si="19">SUM(T3:U3)</f>
+        <f t="shared" ref="S3:S28" si="21">SUM(T3:U3)</f>
         <v>0</v>
       </c>
       <c r="T3" s="3">
-        <f t="shared" ref="T3:T28" si="20">COUNTIF(IU3:PR3,"T")</f>
+        <f t="shared" ref="T3:T28" si="22">COUNTIF(IU3:PR3,"T")</f>
         <v>0</v>
       </c>
       <c r="U3" s="3">
-        <f t="shared" ref="U3:U28" si="21">COUNTIF(IU3:PR3,"R")</f>
+        <f t="shared" ref="U3:U28" si="23">COUNTIF(IU3:PR3,"R")</f>
         <v>0</v>
       </c>
       <c r="V3" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="4" t="e">
-        <f>SUM(AL3,AP3,AT3,AX3,BB3,BF3,BJ3,BN3,BR3,BV3,BZ3,CD3,CH3,CL3,CP3,CT3,CX3,DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3,HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3,IX3,JB3,JF3,JJ3,JN3,JR3,JV3,JZ3,KD3,KH3,KL3,KP3,KT3,KX3,LB3,LF3,LJ3,LN3,LR3,LV3,LZ3,MD3,#REF!,ML3,MP3,MT3,MX3,NB3,NF3,NJ3,NN3,NR3,NV3,NZ3,OD3,OH3,OL3,OP3,OT3,OX3,PB3,PF3,PJ3,PN3,PR3)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z3" s="4" t="e">
-        <f>SUM(DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3,HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3,IX3,JB3,JF3,JJ3,JN3,JR3,JV3,JZ3,KD3,KH3,KL3,KP3,KT3,KX3,LB3,LF3,LJ3,LN3,LR3,LV3,LZ3,MD3,#REF!,ML3,MP3,MT3,MX3,NB3,NF3,NJ3,NN3,NR3,NV3,NZ3,OD3,OH3,OL3,OP3,OT3,OX3,PB3,PF3,PJ3,PN3,PR3)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <f>SUM(AL3,AP3,AT3,AX3,BB3,BF3,BJ3,BN3,BR3,BV3,BZ3,CD3,CH3,CL3,CP3,CT3,CX3,DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3,HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3,IX3,JB3,JF3,JJ3,JN3,JR3,JV3,JZ3,KD3,KH3,KL3,KP3,KT3,KX3,LB3,LF3,LJ3,LN3,LR3,LV3,LZ3,MD3,ML3,MP3,MT3,MX3,NB3,NF3,NJ3,NN3,NR3,NV3,NZ3,OD3,OH3,OL3,OP3,OT3,OX3,PB3,PF3,PJ3,PN3,PR3)</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <f t="shared" ref="Z3:Z31" si="24">SUM(DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3,HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3,IX3,JB3,JF3,JJ3,JN3,JR3,JV3,JZ3,KD3,KH3,KL3,KP3,KT3,KX3,LB3,LF3,LJ3,LN3,LR3,LV3,LZ3,MD3,ML3,MP3,MT3,MX3,NB3,NF3,NJ3,NN3,NR3,NV3,NZ3,OD3,OH3,OL3,OP3,OT3,OX3,PB3,PF3,PJ3,PN3,PR3)</f>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <f t="shared" ref="AA3:AA28" si="22">SUM(DA3,DE3,DI3,DM3,DQ3,DU3,DY3,EC3,EG3,EK3,EO3,ES3,EW3,FA3,FE3,FI3,FM3,FQ3,FU3,FY3,GC3,GG3,GK3,GO3,GS3,GW3)</f>
+        <f t="shared" ref="AA3:AA28" si="25">SUM(DA3,DE3,DI3,DM3,DQ3,DU3,DY3,EC3,EG3,EK3,EO3,ES3,EW3,FA3,FE3,FI3,FM3,FQ3,FU3,FY3,GC3,GG3,GK3,GO3,GS3,GW3)</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f t="shared" ref="AB3:AB28" si="23">SUM(DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3)</f>
+        <f t="shared" ref="AB3:AB28" si="26">SUM(DB3,DF3,DJ3,DN3,DR3,DV3,DZ3,ED3,EH3,EL3,EP3,ET3,EX3,FB3,FF3,FJ3,FN3,FR3,FV3,FZ3,GD3,GH3,GL3,GP3,GT3,GX3)</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" ref="AC3:AC28" si="24">SUM(HA3,HE3,HI3,HM3,HQ3,HU3,HY3,IC3,IG3,IK3,IO3,IS3)</f>
+        <f t="shared" ref="AC3:AC28" si="27">SUM(HA3,HE3,HI3,HM3,HQ3,HU3,HY3,IC3,IG3,IK3,IO3,IS3)</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD28" si="25">SUM(HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3)</f>
+        <f t="shared" ref="AD3:AD28" si="28">SUM(HB3,HF3,HJ3,HN3,HR3,HV3,HZ3,ID3,IH3,IL3,IP3,IT3)</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" ref="AE3:AE28" si="26">SUM(AK3,AO3,AS3,AW3,BA3,BE3,BI3,BM3,BQ3,BU3,BY3,CC3,CG3,CK3,CO3,CS3,CW3)</f>
+        <f t="shared" ref="AE3:AE28" si="29">SUM(AK3,AO3,AS3,AW3,BA3,BE3,BI3,BM3,BQ3,BU3,BY3,CC3,CG3,CK3,CO3,CS3,CW3)</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" ref="AF3:AF28" si="27">SUM(AL3,AP3,AT3,AX3,BB3,BF3,BJ3,BN3,BR3,BV3,BZ3,CD3,CH3,CL3,CP3,CT3,CX3)</f>
+        <f t="shared" ref="AF3:AF28" si="30">SUM(AL3,AP3,AT3,AX3,BB3,BF3,BJ3,BN3,BR3,BV3,BZ3,CD3,CH3,CL3,CP3,CT3,CX3)</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH3" t="e">
-        <f>SUM(IX3,JB3,JF3,JJ3,JN3,JR3,JV3,JZ3,KD3,KH3,KL3,KP3,KT3,KX3,LB3,LF3,LJ3,LN3,LR3,LV3,LZ3,MD3,#REF!,ML3,MP3,MT3,MX3,NB3,NF3,NJ3,NN3,NR3,NV3,NZ3,OD3,OH3,OL3,OP3,OT3,OX3,PB3,PF3,PJ3,PN3,PR3)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" ref="AH3:AH31" si="31">SUM(IX3,JB3,JF3,JJ3,JN3,JR3,JV3,JZ3,KD3,KH3,KL3,KP3,KT3,KX3,LB3,LF3,LJ3,LN3,LR3,LV3,LZ3,MD3,ML3,MP3,MT3,MX3,NB3,NF3,NJ3,NN3,NR3,NV3,NZ3,OD3,OH3,OL3,OP3,OT3,OX3,PB3,PF3,PJ3,PN3,PR3)</f>
+        <v>0</v>
       </c>
       <c r="PS3" s="3">
-        <f t="shared" ref="PS3:PS28" si="28">COUNTIF(AI3:PR3,"HG")</f>
+        <f t="shared" ref="PS3:PS28" si="32">COUNTIF(AI3:PR3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT3" s="3">
-        <f t="shared" ref="PT3:PT28" si="29">COUNTIF(CY3:GX3,"HG")</f>
+        <f t="shared" ref="PT3:PT28" si="33">COUNTIF(CY3:GX3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU3" s="3">
-        <f t="shared" ref="PU3:PU28" si="30">COUNTIF(GY3:IT3,"HG")</f>
+        <f t="shared" ref="PU3:PU28" si="34">COUNTIF(GY3:IT3,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV3">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW3">
-        <f t="shared" ref="PW3:PW28" si="31">G3-(K3+O3+S3)</f>
+        <f t="shared" ref="PW3:PW28" si="35">G3-(K3+O3+S3)</f>
         <v>0</v>
       </c>
     </row>
@@ -2515,136 +2515,136 @@
         <v>128</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B28" si="32">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
+        <f t="shared" ref="B4:B28" si="36">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
         <v>120</v>
       </c>
       <c r="C4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4" si="37">SUM(H4:I4)</f>
+        <v>3</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" ref="H4" si="38">COUNTIF(AI4:PR4,"T")</f>
+        <v>2</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" ref="I4" si="39">COUNTIF(AI4:PR4,"R")</f>
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
+        <f t="shared" ref="J4" si="40">COUNTIF(AI4:PR4,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4" si="41">SUM(L4:M4)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <f t="shared" ref="L4" si="42">COUNTIF(CY4:GX4,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <f t="shared" ref="M4" si="43">COUNTIF(CY4:GX4,"R")</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="3">
+        <f t="shared" ref="N4" si="44">COUNTIF(CY4:GX4,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f t="shared" ref="O4" si="45">SUM(P4:Q4)</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
+        <f t="shared" ref="P4" si="46">COUNTIF(GY4:IT4,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3">
+        <f t="shared" ref="Q4" si="47">COUNTIF(GY4:IT4,"R")</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="3">
+        <f t="shared" ref="R4" si="48">COUNTIF(GY4:IT4,"NR")</f>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4" si="49">SUM(T4:U4)</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U4" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V4" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W4" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
+        <f t="shared" ref="Y4:Y31" si="50">SUM(AL4,AP4,AT4,AX4,BB4,BF4,BJ4,BN4,BR4,BV4,BZ4,CD4,CH4,CL4,CP4,CT4,CX4,DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4,HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4,IX4,JB4,JF4,JJ4,JN4,JR4,JV4,JZ4,KD4,KH4,KL4,KP4,KT4,KX4,LB4,LF4,LJ4,LN4,LR4,LV4,LZ4,MD4,ML4,MP4,MT4,MX4,NB4,NF4,NJ4,NN4,NR4,NV4,NZ4,OD4,OH4,OL4,OP4,OT4,OX4,PB4,PF4,PJ4,PN4,PR4)</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" ref="AA4" si="51">SUM(DA4,DE4,DI4,DM4,DQ4,DU4,DY4,EC4,EG4,EK4,EO4,ES4,EW4,FA4,FE4,FI4,FM4,FQ4,FU4,FY4,GC4,GG4,GK4,GO4,GS4,GW4)</f>
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" ref="AB4" si="52">SUM(DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" ref="AC4" si="53">SUM(HA4,HE4,HI4,HM4,HQ4,HU4,HY4,IC4,IG4,IK4,IO4,IS4)</f>
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" ref="AD4" si="54">SUM(HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4)</f>
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <f t="shared" ref="AE4" si="55">SUM(AK4,AO4,AS4,AW4,BA4,BE4,BI4,BM4,BQ4,BU4,BY4,CC4,CG4,CK4,CO4,CS4,CW4)</f>
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <f t="shared" ref="AF4" si="56">SUM(AL4,AP4,AT4,AX4,BB4,BF4,BJ4,BN4,BR4,BV4,BZ4,CD4,CH4,CL4,CP4,CT4,CX4)</f>
+        <v>0</v>
+      </c>
+      <c r="AG4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="6"/>
-        <v>120</v>
-      </c>
-      <c r="G4">
-        <f t="shared" ref="G4" si="33">SUM(H4:I4)</f>
-        <v>3</v>
-      </c>
-      <c r="H4" s="3">
-        <f t="shared" ref="H4" si="34">COUNTIF(AI4:PR4,"T")</f>
-        <v>2</v>
-      </c>
-      <c r="I4" s="3">
-        <f t="shared" ref="I4" si="35">COUNTIF(AI4:PR4,"R")</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="3">
-        <f t="shared" ref="J4" si="36">COUNTIF(AI4:PR4,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <f t="shared" ref="K4" si="37">SUM(L4:M4)</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="3">
-        <f t="shared" ref="L4" si="38">COUNTIF(CY4:GX4,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <f t="shared" ref="M4" si="39">COUNTIF(CY4:GX4,"R")</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="3">
-        <f t="shared" ref="N4" si="40">COUNTIF(CY4:GX4,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <f t="shared" ref="O4" si="41">SUM(P4:Q4)</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="3">
-        <f t="shared" ref="P4" si="42">COUNTIF(GY4:IT4,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3">
-        <f t="shared" ref="Q4" si="43">COUNTIF(GY4:IT4,"R")</f>
-        <v>0</v>
-      </c>
-      <c r="R4" s="3">
-        <f t="shared" ref="R4" si="44">COUNTIF(GY4:IT4,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <f t="shared" ref="S4" si="45">SUM(T4:U4)</f>
-        <v>0</v>
-      </c>
-      <c r="T4" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U4" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V4" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W4" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4" t="e">
-        <f>SUM(AL4,AP4,AT4,AX4,BB4,BF4,BJ4,BN4,BR4,BV4,BZ4,CD4,CH4,CL4,CP4,CT4,CX4,DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4,HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4,IX4,JB4,JF4,JJ4,JN4,JR4,JV4,JZ4,KD4,KH4,KL4,KP4,KT4,KX4,LB4,LF4,LJ4,LN4,LR4,LV4,LZ4,MD4,#REF!,ML4,MP4,MT4,MX4,NB4,NF4,NJ4,NN4,NR4,NV4,NZ4,OD4,OH4,OL4,OP4,OT4,OX4,PB4,PF4,PJ4,PN4,PR4)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z4" s="4" t="e">
-        <f>SUM(DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4,HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4,IX4,JB4,JF4,JJ4,JN4,JR4,JV4,JZ4,KD4,KH4,KL4,KP4,KT4,KX4,LB4,LF4,LJ4,LN4,LR4,LV4,LZ4,MD4,#REF!,ML4,MP4,MT4,MX4,NB4,NF4,NJ4,NN4,NR4,NV4,NZ4,OD4,OH4,OL4,OP4,OT4,OX4,PB4,PF4,PJ4,PN4,PR4)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA4">
-        <f t="shared" ref="AA4" si="46">SUM(DA4,DE4,DI4,DM4,DQ4,DU4,DY4,EC4,EG4,EK4,EO4,ES4,EW4,FA4,FE4,FI4,FM4,FQ4,FU4,FY4,GC4,GG4,GK4,GO4,GS4,GW4)</f>
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <f t="shared" ref="AB4" si="47">SUM(DB4,DF4,DJ4,DN4,DR4,DV4,DZ4,ED4,EH4,EL4,EP4,ET4,EX4,FB4,FF4,FJ4,FN4,FR4,FV4,FZ4,GD4,GH4,GL4,GP4,GT4,GX4)</f>
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <f t="shared" ref="AC4" si="48">SUM(HA4,HE4,HI4,HM4,HQ4,HU4,HY4,IC4,IG4,IK4,IO4,IS4)</f>
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <f t="shared" ref="AD4" si="49">SUM(HB4,HF4,HJ4,HN4,HR4,HV4,HZ4,ID4,IH4,IL4,IP4,IT4)</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f t="shared" ref="AE4" si="50">SUM(AK4,AO4,AS4,AW4,BA4,BE4,BI4,BM4,BQ4,BU4,BY4,CC4,CG4,CK4,CO4,CS4,CW4)</f>
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <f t="shared" ref="AF4" si="51">SUM(AL4,AP4,AT4,AX4,BB4,BF4,BJ4,BN4,BR4,BV4,BZ4,CD4,CH4,CL4,CP4,CT4,CX4)</f>
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH4" t="e">
-        <f>SUM(IX4,JB4,JF4,JJ4,JN4,JR4,JV4,JZ4,KD4,KH4,KL4,KP4,KT4,KX4,LB4,LF4,LJ4,LN4,LR4,LV4,LZ4,MD4,#REF!,ML4,MP4,MT4,MX4,NB4,NF4,NJ4,NN4,NR4,NV4,NZ4,OD4,OH4,OL4,OP4,OT4,OX4,PB4,PF4,PJ4,PN4,PR4)</f>
-        <v>#REF!</v>
+      <c r="AH4">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI4">
         <v>45</v>
@@ -2665,23 +2665,23 @@
         <v>146</v>
       </c>
       <c r="PS4" s="3">
-        <f t="shared" ref="PS4" si="52">COUNTIF(AI4:PR4,"HG")</f>
+        <f t="shared" ref="PS4" si="57">COUNTIF(AI4:PR4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT4" s="3">
-        <f t="shared" ref="PT4" si="53">COUNTIF(CY4:GX4,"HG")</f>
+        <f t="shared" ref="PT4" si="58">COUNTIF(CY4:GX4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU4" s="3">
-        <f t="shared" ref="PU4" si="54">COUNTIF(GY4:IT4,"HG")</f>
+        <f t="shared" ref="PU4" si="59">COUNTIF(GY4:IT4,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV4">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW4">
-        <f t="shared" ref="PW4" si="55">G4-(K4+O4+S4)</f>
+        <f t="shared" ref="PW4" si="60">G4-(K4+O4+S4)</f>
         <v>3</v>
       </c>
     </row>
@@ -2690,136 +2690,136 @@
         <v>112</v>
       </c>
       <c r="B5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>105</v>
       </c>
       <c r="C5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="8"/>
+        <v>105</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T5" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U5" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W5" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="6"/>
-        <v>105</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="H5" s="3">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="I5" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L5" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N5" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P5" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R5" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T5" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U5" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V5" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W5" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="4" t="e">
-        <f>SUM(AL5,AP5,AT5,AX5,BB5,BF5,BJ5,BN5,BR5,BV5,BZ5,CD5,CH5,CL5,CP5,CT5,CX5,DB5,DF5,DJ5,DN5,DR5,DV5,DZ5,ED5,EH5,EL5,EP5,ET5,EX5,FB5,FF5,FJ5,FN5,FR5,FV5,FZ5,GD5,GH5,GL5,GP5,GT5,GX5,HB5,HF5,HJ5,HN5,HR5,HV5,HZ5,ID5,IH5,IL5,IP5,IT5,IX5,JB5,JF5,JJ5,JN5,JR5,JV5,JZ5,KD5,KH5,KL5,KP5,KT5,KX5,LB5,LF5,LJ5,LN5,LR5,LV5,LZ5,MD5,#REF!,ML5,MP5,MT5,MX5,NB5,NF5,NJ5,NN5,NR5,NV5,NZ5,OD5,OH5,OL5,OP5,OT5,OX5,PB5,PF5,PJ5,PN5,PR5)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z5" s="4" t="e">
-        <f>SUM(DB5,DF5,DJ5,DN5,DR5,DV5,DZ5,ED5,EH5,EL5,EP5,ET5,EX5,FB5,FF5,FJ5,FN5,FR5,FV5,FZ5,GD5,GH5,GL5,GP5,GT5,GX5,HB5,HF5,HJ5,HN5,HR5,HV5,HZ5,ID5,IH5,IL5,IP5,IT5,IX5,JB5,JF5,JJ5,JN5,JR5,JV5,JZ5,KD5,KH5,KL5,KP5,KT5,KX5,LB5,LF5,LJ5,LN5,LR5,LV5,LZ5,MD5,#REF!,ML5,MP5,MT5,MX5,NB5,NF5,NJ5,NN5,NR5,NV5,NZ5,OD5,OH5,OL5,OP5,OT5,OX5,PB5,PF5,PJ5,PN5,PR5)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH5" t="e">
-        <f>SUM(IX5,JB5,JF5,JJ5,JN5,JR5,JV5,JZ5,KD5,KH5,KL5,KP5,KT5,KX5,LB5,LF5,LJ5,LN5,LR5,LV5,LZ5,MD5,#REF!,ML5,MP5,MT5,MX5,NB5,NF5,NJ5,NN5,NR5,NV5,NZ5,OD5,OH5,OL5,OP5,OT5,OX5,PB5,PF5,PJ5,PN5,PR5)</f>
-        <v>#REF!</v>
+      <c r="AH5">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AM5">
         <v>45</v>
@@ -2834,23 +2834,23 @@
         <v>145</v>
       </c>
       <c r="PS5" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT5" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU5" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV5">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
     </row>
@@ -2859,136 +2859,136 @@
         <v>129</v>
       </c>
       <c r="B6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>120</v>
       </c>
       <c r="C6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="6"/>
-        <v>120</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H6" s="3">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I6" s="3">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="J6" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P6" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U6" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V6" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W6" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="4" t="e">
-        <f>SUM(AL6,AP6,AT6,AX6,BB6,BF6,BJ6,BN6,BR6,BV6,BZ6,CD6,CH6,CL6,CP6,CT6,CX6,DB6,DF6,DJ6,DN6,DR6,DV6,DZ6,ED6,EH6,EL6,EP6,ET6,EX6,FB6,FF6,FJ6,FN6,FR6,FV6,FZ6,GD6,GH6,GL6,GP6,GT6,GX6,HB6,HF6,HJ6,HN6,HR6,HV6,HZ6,ID6,IH6,IL6,IP6,IT6,IX6,JB6,JF6,JJ6,JN6,JR6,JV6,JZ6,KD6,KH6,KL6,KP6,KT6,KX6,LB6,LF6,LJ6,LN6,LR6,LV6,LZ6,MD6,#REF!,ML6,MP6,MT6,MX6,NB6,NF6,NJ6,NN6,NR6,NV6,NZ6,OD6,OH6,OL6,OP6,OT6,OX6,PB6,PF6,PJ6,PN6,PR6)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z6" s="4" t="e">
-        <f>SUM(DB6,DF6,DJ6,DN6,DR6,DV6,DZ6,ED6,EH6,EL6,EP6,ET6,EX6,FB6,FF6,FJ6,FN6,FR6,FV6,FZ6,GD6,GH6,GL6,GP6,GT6,GX6,HB6,HF6,HJ6,HN6,HR6,HV6,HZ6,ID6,IH6,IL6,IP6,IT6,IX6,JB6,JF6,JJ6,JN6,JR6,JV6,JZ6,KD6,KH6,KL6,KP6,KT6,KX6,LB6,LF6,LJ6,LN6,LR6,LV6,LZ6,MD6,#REF!,ML6,MP6,MT6,MX6,NB6,NF6,NJ6,NN6,NR6,NV6,NZ6,OD6,OH6,OL6,OP6,OT6,OX6,PB6,PF6,PJ6,PN6,PR6)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA6">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH6" t="e">
-        <f>SUM(IX6,JB6,JF6,JJ6,JN6,JR6,JV6,JZ6,KD6,KH6,KL6,KP6,KT6,KX6,LB6,LF6,LJ6,LN6,LR6,LV6,LZ6,MD6,#REF!,ML6,MP6,MT6,MX6,NB6,NF6,NJ6,NN6,NR6,NV6,NZ6,OD6,OH6,OL6,OP6,OT6,OX6,PB6,PF6,PJ6,PN6,PR6)</f>
-        <v>#REF!</v>
+      <c r="AH6">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI6">
         <v>45</v>
@@ -3009,23 +3009,23 @@
         <v>146</v>
       </c>
       <c r="PS6" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT6" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU6" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV6">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -3034,155 +3034,155 @@
         <v>130</v>
       </c>
       <c r="B7">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U7" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="PS7" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="C7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D7">
+      <c r="PT7" s="3">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="PU7" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="PV7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N7" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P7" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T7" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U7" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V7" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="4" t="e">
-        <f>SUM(AL7,AP7,AT7,AX7,BB7,BF7,BJ7,BN7,BR7,BV7,BZ7,CD7,CH7,CL7,CP7,CT7,CX7,DB7,DF7,DJ7,DN7,DR7,DV7,DZ7,ED7,EH7,EL7,EP7,ET7,EX7,FB7,FF7,FJ7,FN7,FR7,FV7,FZ7,GD7,GH7,GL7,GP7,GT7,GX7,HB7,HF7,HJ7,HN7,HR7,HV7,HZ7,ID7,IH7,IL7,IP7,IT7,IX7,JB7,JF7,JJ7,JN7,JR7,JV7,JZ7,KD7,KH7,KL7,KP7,KT7,KX7,LB7,LF7,LJ7,LN7,LR7,LV7,LZ7,MD7,#REF!,ML7,MP7,MT7,MX7,NB7,NF7,NJ7,NN7,NR7,NV7,NZ7,OD7,OH7,OL7,OP7,OT7,OX7,PB7,PF7,PJ7,PN7,PR7)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z7" s="4" t="e">
-        <f>SUM(DB7,DF7,DJ7,DN7,DR7,DV7,DZ7,ED7,EH7,EL7,EP7,ET7,EX7,FB7,FF7,FJ7,FN7,FR7,FV7,FZ7,GD7,GH7,GL7,GP7,GT7,GX7,HB7,HF7,HJ7,HN7,HR7,HV7,HZ7,ID7,IH7,IL7,IP7,IT7,IX7,JB7,JF7,JJ7,JN7,JR7,JV7,JZ7,KD7,KH7,KL7,KP7,KT7,KX7,LB7,LF7,LJ7,LN7,LR7,LV7,LZ7,MD7,#REF!,ML7,MP7,MT7,MX7,NB7,NF7,NJ7,NN7,NR7,NV7,NZ7,OD7,OH7,OL7,OP7,OT7,OX7,PB7,PF7,PJ7,PN7,PR7)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA7">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH7" t="e">
-        <f>SUM(IX7,JB7,JF7,JJ7,JN7,JR7,JV7,JZ7,KD7,KH7,KL7,KP7,KT7,KX7,LB7,LF7,LJ7,LN7,LR7,LV7,LZ7,MD7,#REF!,ML7,MP7,MT7,MX7,NB7,NF7,NJ7,NN7,NR7,NV7,NZ7,OD7,OH7,OL7,OP7,OT7,OX7,PB7,PF7,PJ7,PN7,PR7)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="PS7" s="3">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="PT7" s="3">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="PU7" s="3">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="PV7">
-        <f>COUNTIF(IU:PR,"HG")</f>
-        <v>0</v>
-      </c>
       <c r="PW7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -3191,71 +3191,71 @@
         <v>131</v>
       </c>
       <c r="B8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>150</v>
       </c>
       <c r="C8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
       <c r="G8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M8" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N8" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S8">
@@ -3263,64 +3263,64 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4" t="e">
-        <f>SUM(AL8,AP8,AT8,AX8,BB8,BF8,BJ8,BN8,BR8,BV8,BZ8,CD8,CH8,CL8,CP8,CT8,CX8,DB8,DF8,DJ8,DN8,DR8,DV8,DZ8,ED8,EH8,EL8,EP8,ET8,EX8,FB8,FF8,FJ8,FN8,FR8,FV8,FZ8,GD8,GH8,GL8,GP8,GT8,GX8,HB8,HF8,HJ8,HN8,HR8,HV8,HZ8,ID8,IH8,IL8,IP8,IT8,IX8,JB8,JF8,JJ8,JN8,JR8,JV8,JZ8,KD8,KH8,KL8,KP8,KT8,KX8,LB8,LF8,LJ8,LN8,LR8,LV8,LZ8,MD8,#REF!,ML8,MP8,MT8,MX8,NB8,NF8,NJ8,NN8,NR8,NV8,NZ8,OD8,OH8,OL8,OP8,OT8,OX8,PB8,PF8,PJ8,PN8,PR8)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z8" s="4" t="e">
-        <f>SUM(DB8,DF8,DJ8,DN8,DR8,DV8,DZ8,ED8,EH8,EL8,EP8,ET8,EX8,FB8,FF8,FJ8,FN8,FR8,FV8,FZ8,GD8,GH8,GL8,GP8,GT8,GX8,HB8,HF8,HJ8,HN8,HR8,HV8,HZ8,ID8,IH8,IL8,IP8,IT8,IX8,JB8,JF8,JJ8,JN8,JR8,JV8,JZ8,KD8,KH8,KL8,KP8,KT8,KX8,LB8,LF8,LJ8,LN8,LR8,LV8,LZ8,MD8,#REF!,ML8,MP8,MT8,MX8,NB8,NF8,NJ8,NN8,NR8,NV8,NZ8,OD8,OH8,OL8,OP8,OT8,OX8,PB8,PF8,PJ8,PN8,PR8)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH8" t="e">
-        <f>SUM(IX8,JB8,JF8,JJ8,JN8,JR8,JV8,JZ8,KD8,KH8,KL8,KP8,KT8,KX8,LB8,LF8,LJ8,LN8,LR8,LV8,LZ8,MD8,#REF!,ML8,MP8,MT8,MX8,NB8,NF8,NJ8,NN8,NR8,NV8,NZ8,OD8,OH8,OL8,OP8,OT8,OX8,PB8,PF8,PJ8,PN8,PR8)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI8">
         <v>45</v>
@@ -3341,23 +3341,23 @@
         <v>145</v>
       </c>
       <c r="PS8" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT8" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU8" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV8">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -3366,136 +3366,136 @@
         <v>118</v>
       </c>
       <c r="B9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>30</v>
       </c>
       <c r="C9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="G9">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
+      <c r="H9" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
       <c r="J9" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M9" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N9" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U9" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W9" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="4" t="e">
-        <f>SUM(AL9,AP9,AT9,AX9,BB9,BF9,BJ9,BN9,BR9,BV9,BZ9,CD9,CH9,CL9,CP9,CT9,CX9,DB9,DF9,DJ9,DN9,DR9,DV9,DZ9,ED9,EH9,EL9,EP9,ET9,EX9,FB9,FF9,FJ9,FN9,FR9,FV9,FZ9,GD9,GH9,GL9,GP9,GT9,GX9,HB9,HF9,HJ9,HN9,HR9,HV9,HZ9,ID9,IH9,IL9,IP9,IT9,IX9,JB9,JF9,JJ9,JN9,JR9,JV9,JZ9,KD9,KH9,KL9,KP9,KT9,KX9,LB9,LF9,LJ9,LN9,LR9,LV9,LZ9,MD9,#REF!,ML9,MP9,MT9,MX9,NB9,NF9,NJ9,NN9,NR9,NV9,NZ9,OD9,OH9,OL9,OP9,OT9,OX9,PB9,PF9,PJ9,PN9,PR9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z9" s="4" t="e">
-        <f>SUM(DB9,DF9,DJ9,DN9,DR9,DV9,DZ9,ED9,EH9,EL9,EP9,ET9,EX9,FB9,FF9,FJ9,FN9,FR9,FV9,FZ9,GD9,GH9,GL9,GP9,GT9,GX9,HB9,HF9,HJ9,HN9,HR9,HV9,HZ9,ID9,IH9,IL9,IP9,IT9,IX9,JB9,JF9,JJ9,JN9,JR9,JV9,JZ9,KD9,KH9,KL9,KP9,KT9,KX9,LB9,LF9,LJ9,LN9,LR9,LV9,LZ9,MD9,#REF!,ML9,MP9,MT9,MX9,NB9,NF9,NJ9,NN9,NR9,NV9,NZ9,OD9,OH9,OL9,OP9,OT9,OX9,PB9,PF9,PJ9,PN9,PR9)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH9" t="e">
-        <f>SUM(IX9,JB9,JF9,JJ9,JN9,JR9,JV9,JZ9,KD9,KH9,KL9,KP9,KT9,KX9,LB9,LF9,LJ9,LN9,LR9,LV9,LZ9,MD9,#REF!,ML9,MP9,MT9,MX9,NB9,NF9,NJ9,NN9,NR9,NV9,NZ9,OD9,OH9,OL9,OP9,OT9,OX9,PB9,PF9,PJ9,PN9,PR9)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AQ9">
         <v>30</v>
@@ -3504,23 +3504,23 @@
         <v>146</v>
       </c>
       <c r="PS9" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT9" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU9" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV9">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
     </row>
@@ -3529,136 +3529,136 @@
         <v>132</v>
       </c>
       <c r="B10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>150</v>
       </c>
       <c r="C10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="8"/>
+        <v>150</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="6"/>
-        <v>150</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="I10" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="4" t="e">
-        <f>SUM(AL10,AP10,AT10,AX10,BB10,BF10,BJ10,BN10,BR10,BV10,BZ10,CD10,CH10,CL10,CP10,CT10,CX10,DB10,DF10,DJ10,DN10,DR10,DV10,DZ10,ED10,EH10,EL10,EP10,ET10,EX10,FB10,FF10,FJ10,FN10,FR10,FV10,FZ10,GD10,GH10,GL10,GP10,GT10,GX10,HB10,HF10,HJ10,HN10,HR10,HV10,HZ10,ID10,IH10,IL10,IP10,IT10,IX10,JB10,JF10,JJ10,JN10,JR10,JV10,JZ10,KD10,KH10,KL10,KP10,KT10,KX10,LB10,LF10,LJ10,LN10,LR10,LV10,LZ10,MD10,#REF!,ML10,MP10,MT10,MX10,NB10,NF10,NJ10,NN10,NR10,NV10,NZ10,OD10,OH10,OL10,OP10,OT10,OX10,PB10,PF10,PJ10,PN10,PR10)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z10" s="4" t="e">
-        <f>SUM(DB10,DF10,DJ10,DN10,DR10,DV10,DZ10,ED10,EH10,EL10,EP10,ET10,EX10,FB10,FF10,FJ10,FN10,FR10,FV10,FZ10,GD10,GH10,GL10,GP10,GT10,GX10,HB10,HF10,HJ10,HN10,HR10,HV10,HZ10,ID10,IH10,IL10,IP10,IT10,IX10,JB10,JF10,JJ10,JN10,JR10,JV10,JZ10,KD10,KH10,KL10,KP10,KT10,KX10,LB10,LF10,LJ10,LN10,LR10,LV10,LZ10,MD10,#REF!,ML10,MP10,MT10,MX10,NB10,NF10,NJ10,NN10,NR10,NV10,NZ10,OD10,OH10,OL10,OP10,OT10,OX10,PB10,PF10,PJ10,PN10,PR10)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA10">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH10" t="e">
-        <f>SUM(IX10,JB10,JF10,JJ10,JN10,JR10,JV10,JZ10,KD10,KH10,KL10,KP10,KT10,KX10,LB10,LF10,LJ10,LN10,LR10,LV10,LZ10,MD10,#REF!,ML10,MP10,MT10,MX10,NB10,NF10,NJ10,NN10,NR10,NV10,NZ10,OD10,OH10,OL10,OP10,OT10,OX10,PB10,PF10,PJ10,PN10,PR10)</f>
-        <v>#REF!</v>
+      <c r="AH10">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI10">
         <v>45</v>
@@ -3679,23 +3679,23 @@
         <v>145</v>
       </c>
       <c r="PS10" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT10" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU10" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV10">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -3704,136 +3704,136 @@
         <v>113</v>
       </c>
       <c r="B11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>150</v>
       </c>
       <c r="C11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="8"/>
+        <v>150</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="6"/>
-        <v>150</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="I11" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="4" t="e">
-        <f>SUM(AL11,AP11,AT11,AX11,BB11,BF11,BJ11,BN11,BR11,BV11,BZ11,CD11,CH11,CL11,CP11,CT11,CX11,DB11,DF11,DJ11,DN11,DR11,DV11,DZ11,ED11,EH11,EL11,EP11,ET11,EX11,FB11,FF11,FJ11,FN11,FR11,FV11,FZ11,GD11,GH11,GL11,GP11,GT11,GX11,HB11,HF11,HJ11,HN11,HR11,HV11,HZ11,ID11,IH11,IL11,IP11,IT11,IX11,JB11,JF11,JJ11,JN11,JR11,JV11,JZ11,KD11,KH11,KL11,KP11,KT11,KX11,LB11,LF11,LJ11,LN11,LR11,LV11,LZ11,MD11,#REF!,ML11,MP11,MT11,MX11,NB11,NF11,NJ11,NN11,NR11,NV11,NZ11,OD11,OH11,OL11,OP11,OT11,OX11,PB11,PF11,PJ11,PN11,PR11)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z11" s="4" t="e">
-        <f>SUM(DB11,DF11,DJ11,DN11,DR11,DV11,DZ11,ED11,EH11,EL11,EP11,ET11,EX11,FB11,FF11,FJ11,FN11,FR11,FV11,FZ11,GD11,GH11,GL11,GP11,GT11,GX11,HB11,HF11,HJ11,HN11,HR11,HV11,HZ11,ID11,IH11,IL11,IP11,IT11,IX11,JB11,JF11,JJ11,JN11,JR11,JV11,JZ11,KD11,KH11,KL11,KP11,KT11,KX11,LB11,LF11,LJ11,LN11,LR11,LV11,LZ11,MD11,#REF!,ML11,MP11,MT11,MX11,NB11,NF11,NJ11,NN11,NR11,NV11,NZ11,OD11,OH11,OL11,OP11,OT11,OX11,PB11,PF11,PJ11,PN11,PR11)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA11">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH11" t="e">
-        <f>SUM(IX11,JB11,JF11,JJ11,JN11,JR11,JV11,JZ11,KD11,KH11,KL11,KP11,KT11,KX11,LB11,LF11,LJ11,LN11,LR11,LV11,LZ11,MD11,#REF!,ML11,MP11,MT11,MX11,NB11,NF11,NJ11,NN11,NR11,NV11,NZ11,OD11,OH11,OL11,OP11,OT11,OX11,PB11,PF11,PJ11,PN11,PR11)</f>
-        <v>#REF!</v>
+      <c r="AH11">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI11">
         <v>45</v>
@@ -3854,23 +3854,23 @@
         <v>145</v>
       </c>
       <c r="PS11" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT11" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU11" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV11">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -3879,136 +3879,136 @@
         <v>114</v>
       </c>
       <c r="B12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>45</v>
       </c>
       <c r="C12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="3">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I12" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W12" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="4" t="e">
-        <f>SUM(AL12,AP12,AT12,AX12,BB12,BF12,BJ12,BN12,BR12,BV12,BZ12,CD12,CH12,CL12,CP12,CT12,CX12,DB12,DF12,DJ12,DN12,DR12,DV12,DZ12,ED12,EH12,EL12,EP12,ET12,EX12,FB12,FF12,FJ12,FN12,FR12,FV12,FZ12,GD12,GH12,GL12,GP12,GT12,GX12,HB12,HF12,HJ12,HN12,HR12,HV12,HZ12,ID12,IH12,IL12,IP12,IT12,IX12,JB12,JF12,JJ12,JN12,JR12,JV12,JZ12,KD12,KH12,KL12,KP12,KT12,KX12,LB12,LF12,LJ12,LN12,LR12,LV12,LZ12,MD12,#REF!,ML12,MP12,MT12,MX12,NB12,NF12,NJ12,NN12,NR12,NV12,NZ12,OD12,OH12,OL12,OP12,OT12,OX12,PB12,PF12,PJ12,PN12,PR12)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z12" s="4" t="e">
-        <f>SUM(DB12,DF12,DJ12,DN12,DR12,DV12,DZ12,ED12,EH12,EL12,EP12,ET12,EX12,FB12,FF12,FJ12,FN12,FR12,FV12,FZ12,GD12,GH12,GL12,GP12,GT12,GX12,HB12,HF12,HJ12,HN12,HR12,HV12,HZ12,ID12,IH12,IL12,IP12,IT12,IX12,JB12,JF12,JJ12,JN12,JR12,JV12,JZ12,KD12,KH12,KL12,KP12,KT12,KX12,LB12,LF12,LJ12,LN12,LR12,LV12,LZ12,MD12,#REF!,ML12,MP12,MT12,MX12,NB12,NF12,NJ12,NN12,NR12,NV12,NZ12,OD12,OH12,OL12,OP12,OT12,OX12,PB12,PF12,PJ12,PN12,PR12)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH12" t="e">
-        <f>SUM(IX12,JB12,JF12,JJ12,JN12,JR12,JV12,JZ12,KD12,KH12,KL12,KP12,KT12,KX12,LB12,LF12,LJ12,LN12,LR12,LV12,LZ12,MD12,#REF!,ML12,MP12,MT12,MX12,NB12,NF12,NJ12,NN12,NR12,NV12,NZ12,OD12,OH12,OL12,OP12,OT12,OX12,PB12,PF12,PJ12,PN12,PR12)</f>
-        <v>#REF!</v>
+      <c r="AH12">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI12">
         <v>45</v>
@@ -4017,23 +4017,23 @@
         <v>145</v>
       </c>
       <c r="PS12" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT12" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU12" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV12">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
     </row>
@@ -4042,136 +4042,136 @@
         <v>127</v>
       </c>
       <c r="B13">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>90</v>
       </c>
       <c r="C13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="G13">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="H13" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
+      <c r="H13" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
       <c r="J13" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L13" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M13" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N13" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P13" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q13" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T13" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U13" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V13" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W13" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="4" t="e">
-        <f>SUM(AL13,AP13,AT13,AX13,BB13,BF13,BJ13,BN13,BR13,BV13,BZ13,CD13,CH13,CL13,CP13,CT13,CX13,DB13,DF13,DJ13,DN13,DR13,DV13,DZ13,ED13,EH13,EL13,EP13,ET13,EX13,FB13,FF13,FJ13,FN13,FR13,FV13,FZ13,GD13,GH13,GL13,GP13,GT13,GX13,HB13,HF13,HJ13,HN13,HR13,HV13,HZ13,ID13,IH13,IL13,IP13,IT13,IX13,JB13,JF13,JJ13,JN13,JR13,JV13,JZ13,KD13,KH13,KL13,KP13,KT13,KX13,LB13,LF13,LJ13,LN13,LR13,LV13,LZ13,MD13,#REF!,ML13,MP13,MT13,MX13,NB13,NF13,NJ13,NN13,NR13,NV13,NZ13,OD13,OH13,OL13,OP13,OT13,OX13,PB13,PF13,PJ13,PN13,PR13)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z13" s="4" t="e">
-        <f>SUM(DB13,DF13,DJ13,DN13,DR13,DV13,DZ13,ED13,EH13,EL13,EP13,ET13,EX13,FB13,FF13,FJ13,FN13,FR13,FV13,FZ13,GD13,GH13,GL13,GP13,GT13,GX13,HB13,HF13,HJ13,HN13,HR13,HV13,HZ13,ID13,IH13,IL13,IP13,IT13,IX13,JB13,JF13,JJ13,JN13,JR13,JV13,JZ13,KD13,KH13,KL13,KP13,KT13,KX13,LB13,LF13,LJ13,LN13,LR13,LV13,LZ13,MD13,#REF!,ML13,MP13,MT13,MX13,NB13,NF13,NJ13,NN13,NR13,NV13,NZ13,OD13,OH13,OL13,OP13,OT13,OX13,PB13,PF13,PJ13,PN13,PR13)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH13" t="e">
-        <f>SUM(IX13,JB13,JF13,JJ13,JN13,JR13,JV13,JZ13,KD13,KH13,KL13,KP13,KT13,KX13,LB13,LF13,LJ13,LN13,LR13,LV13,LZ13,MD13,#REF!,ML13,MP13,MT13,MX13,NB13,NF13,NJ13,NN13,NR13,NV13,NZ13,OD13,OH13,OL13,OP13,OT13,OX13,PB13,PF13,PJ13,PN13,PR13)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI13">
         <v>45</v>
@@ -4186,23 +4186,23 @@
         <v>146</v>
       </c>
       <c r="PS13" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT13" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU13" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV13">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
     </row>
@@ -4211,136 +4211,136 @@
         <v>115</v>
       </c>
       <c r="B14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>150</v>
       </c>
       <c r="C14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="8"/>
+        <v>150</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="J14" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="6"/>
-        <v>150</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="I14" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J14" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="4" t="e">
-        <f>SUM(AL14,AP14,AT14,AX14,BB14,BF14,BJ14,BN14,BR14,BV14,BZ14,CD14,CH14,CL14,CP14,CT14,CX14,DB14,DF14,DJ14,DN14,DR14,DV14,DZ14,ED14,EH14,EL14,EP14,ET14,EX14,FB14,FF14,FJ14,FN14,FR14,FV14,FZ14,GD14,GH14,GL14,GP14,GT14,GX14,HB14,HF14,HJ14,HN14,HR14,HV14,HZ14,ID14,IH14,IL14,IP14,IT14,IX14,JB14,JF14,JJ14,JN14,JR14,JV14,JZ14,KD14,KH14,KL14,KP14,KT14,KX14,LB14,LF14,LJ14,LN14,LR14,LV14,LZ14,MD14,#REF!,ML14,MP14,MT14,MX14,NB14,NF14,NJ14,NN14,NR14,NV14,NZ14,OD14,OH14,OL14,OP14,OT14,OX14,PB14,PF14,PJ14,PN14,PR14)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z14" s="4" t="e">
-        <f>SUM(DB14,DF14,DJ14,DN14,DR14,DV14,DZ14,ED14,EH14,EL14,EP14,ET14,EX14,FB14,FF14,FJ14,FN14,FR14,FV14,FZ14,GD14,GH14,GL14,GP14,GT14,GX14,HB14,HF14,HJ14,HN14,HR14,HV14,HZ14,ID14,IH14,IL14,IP14,IT14,IX14,JB14,JF14,JJ14,JN14,JR14,JV14,JZ14,KD14,KH14,KL14,KP14,KT14,KX14,LB14,LF14,LJ14,LN14,LR14,LV14,LZ14,MD14,#REF!,ML14,MP14,MT14,MX14,NB14,NF14,NJ14,NN14,NR14,NV14,NZ14,OD14,OH14,OL14,OP14,OT14,OX14,PB14,PF14,PJ14,PN14,PR14)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA14">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH14" t="e">
-        <f>SUM(IX14,JB14,JF14,JJ14,JN14,JR14,JV14,JZ14,KD14,KH14,KL14,KP14,KT14,KX14,LB14,LF14,LJ14,LN14,LR14,LV14,LZ14,MD14,#REF!,ML14,MP14,MT14,MX14,NB14,NF14,NJ14,NN14,NR14,NV14,NZ14,OD14,OH14,OL14,OP14,OT14,OX14,PB14,PF14,PJ14,PN14,PR14)</f>
-        <v>#REF!</v>
+      <c r="AH14">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI14">
         <v>45</v>
@@ -4361,23 +4361,23 @@
         <v>145</v>
       </c>
       <c r="PS14" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT14" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU14" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV14">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -4386,136 +4386,136 @@
         <v>133</v>
       </c>
       <c r="B15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>120</v>
       </c>
       <c r="C15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="6"/>
-        <v>120</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H15" s="3">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I15" s="3">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="J15" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="4" t="e">
-        <f>SUM(AL15,AP15,AT15,AX15,BB15,BF15,BJ15,BN15,BR15,BV15,BZ15,CD15,CH15,CL15,CP15,CT15,CX15,DB15,DF15,DJ15,DN15,DR15,DV15,DZ15,ED15,EH15,EL15,EP15,ET15,EX15,FB15,FF15,FJ15,FN15,FR15,FV15,FZ15,GD15,GH15,GL15,GP15,GT15,GX15,HB15,HF15,HJ15,HN15,HR15,HV15,HZ15,ID15,IH15,IL15,IP15,IT15,IX15,JB15,JF15,JJ15,JN15,JR15,JV15,JZ15,KD15,KH15,KL15,KP15,KT15,KX15,LB15,LF15,LJ15,LN15,LR15,LV15,LZ15,MD15,#REF!,ML15,MP15,MT15,MX15,NB15,NF15,NJ15,NN15,NR15,NV15,NZ15,OD15,OH15,OL15,OP15,OT15,OX15,PB15,PF15,PJ15,PN15,PR15)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z15" s="4" t="e">
-        <f>SUM(DB15,DF15,DJ15,DN15,DR15,DV15,DZ15,ED15,EH15,EL15,EP15,ET15,EX15,FB15,FF15,FJ15,FN15,FR15,FV15,FZ15,GD15,GH15,GL15,GP15,GT15,GX15,HB15,HF15,HJ15,HN15,HR15,HV15,HZ15,ID15,IH15,IL15,IP15,IT15,IX15,JB15,JF15,JJ15,JN15,JR15,JV15,JZ15,KD15,KH15,KL15,KP15,KT15,KX15,LB15,LF15,LJ15,LN15,LR15,LV15,LZ15,MD15,#REF!,ML15,MP15,MT15,MX15,NB15,NF15,NJ15,NN15,NR15,NV15,NZ15,OD15,OH15,OL15,OP15,OT15,OX15,PB15,PF15,PJ15,PN15,PR15)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH15" t="e">
-        <f>SUM(IX15,JB15,JF15,JJ15,JN15,JR15,JV15,JZ15,KD15,KH15,KL15,KP15,KT15,KX15,LB15,LF15,LJ15,LN15,LR15,LV15,LZ15,MD15,#REF!,ML15,MP15,MT15,MX15,NB15,NF15,NJ15,NN15,NR15,NV15,NZ15,OD15,OH15,OL15,OP15,OT15,OX15,PB15,PF15,PJ15,PN15,PR15)</f>
-        <v>#REF!</v>
+      <c r="AH15">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI15">
         <v>45</v>
@@ -4536,23 +4536,23 @@
         <v>146</v>
       </c>
       <c r="PS15" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT15" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU15" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV15">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -4561,136 +4561,136 @@
         <v>134</v>
       </c>
       <c r="B16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>67</v>
       </c>
       <c r="C16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>67</v>
       </c>
       <c r="G16">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="H16" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
+      <c r="H16" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
       <c r="J16" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M16" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N16" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P16" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q16" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T16" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U16" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V16" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W16" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="4" t="e">
-        <f>SUM(AL16,AP16,AT16,AX16,BB16,BF16,BJ16,BN16,BR16,BV16,BZ16,CD16,CH16,CL16,CP16,CT16,CX16,DB16,DF16,DJ16,DN16,DR16,DV16,DZ16,ED16,EH16,EL16,EP16,ET16,EX16,FB16,FF16,FJ16,FN16,FR16,FV16,FZ16,GD16,GH16,GL16,GP16,GT16,GX16,HB16,HF16,HJ16,HN16,HR16,HV16,HZ16,ID16,IH16,IL16,IP16,IT16,IX16,JB16,JF16,JJ16,JN16,JR16,JV16,JZ16,KD16,KH16,KL16,KP16,KT16,KX16,LB16,LF16,LJ16,LN16,LR16,LV16,LZ16,MD16,#REF!,ML16,MP16,MT16,MX16,NB16,NF16,NJ16,NN16,NR16,NV16,NZ16,OD16,OH16,OL16,OP16,OT16,OX16,PB16,PF16,PJ16,PN16,PR16)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z16" s="4" t="e">
-        <f>SUM(DB16,DF16,DJ16,DN16,DR16,DV16,DZ16,ED16,EH16,EL16,EP16,ET16,EX16,FB16,FF16,FJ16,FN16,FR16,FV16,FZ16,GD16,GH16,GL16,GP16,GT16,GX16,HB16,HF16,HJ16,HN16,HR16,HV16,HZ16,ID16,IH16,IL16,IP16,IT16,IX16,JB16,JF16,JJ16,JN16,JR16,JV16,JZ16,KD16,KH16,KL16,KP16,KT16,KX16,LB16,LF16,LJ16,LN16,LR16,LV16,LZ16,MD16,#REF!,ML16,MP16,MT16,MX16,NB16,NF16,NJ16,NN16,NR16,NV16,NZ16,OD16,OH16,OL16,OP16,OT16,OX16,PB16,PF16,PJ16,PN16,PR16)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH16" t="e">
-        <f>SUM(IX16,JB16,JF16,JJ16,JN16,JR16,JV16,JZ16,KD16,KH16,KL16,KP16,KT16,KX16,LB16,LF16,LJ16,LN16,LR16,LV16,LZ16,MD16,#REF!,ML16,MP16,MT16,MX16,NB16,NF16,NJ16,NN16,NR16,NV16,NZ16,OD16,OH16,OL16,OP16,OT16,OX16,PB16,PF16,PJ16,PN16,PR16)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI16">
         <v>45</v>
@@ -4708,23 +4708,23 @@
         <v>146</v>
       </c>
       <c r="PS16" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT16" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU16" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV16">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
     </row>
@@ -4733,136 +4733,136 @@
         <v>135</v>
       </c>
       <c r="B17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>120</v>
       </c>
       <c r="C17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="J17" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D17">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="6"/>
-        <v>120</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H17" s="3">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="I17" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J17" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W17" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="4" t="e">
-        <f>SUM(AL17,AP17,AT17,AX17,BB17,BF17,BJ17,BN17,BR17,BV17,BZ17,CD17,CH17,CL17,CP17,CT17,CX17,DB17,DF17,DJ17,DN17,DR17,DV17,DZ17,ED17,EH17,EL17,EP17,ET17,EX17,FB17,FF17,FJ17,FN17,FR17,FV17,FZ17,GD17,GH17,GL17,GP17,GT17,GX17,HB17,HF17,HJ17,HN17,HR17,HV17,HZ17,ID17,IH17,IL17,IP17,IT17,IX17,JB17,JF17,JJ17,JN17,JR17,JV17,JZ17,KD17,KH17,KL17,KP17,KT17,KX17,LB17,LF17,LJ17,LN17,LR17,LV17,LZ17,MD17,#REF!,ML17,MP17,MT17,MX17,NB17,NF17,NJ17,NN17,NR17,NV17,NZ17,OD17,OH17,OL17,OP17,OT17,OX17,PB17,PF17,PJ17,PN17,PR17)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z17" s="4" t="e">
-        <f>SUM(DB17,DF17,DJ17,DN17,DR17,DV17,DZ17,ED17,EH17,EL17,EP17,ET17,EX17,FB17,FF17,FJ17,FN17,FR17,FV17,FZ17,GD17,GH17,GL17,GP17,GT17,GX17,HB17,HF17,HJ17,HN17,HR17,HV17,HZ17,ID17,IH17,IL17,IP17,IT17,IX17,JB17,JF17,JJ17,JN17,JR17,JV17,JZ17,KD17,KH17,KL17,KP17,KT17,KX17,LB17,LF17,LJ17,LN17,LR17,LV17,LZ17,MD17,#REF!,ML17,MP17,MT17,MX17,NB17,NF17,NJ17,NN17,NR17,NV17,NZ17,OD17,OH17,OL17,OP17,OT17,OX17,PB17,PF17,PJ17,PN17,PR17)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH17" t="e">
-        <f>SUM(IX17,JB17,JF17,JJ17,JN17,JR17,JV17,JZ17,KD17,KH17,KL17,KP17,KT17,KX17,LB17,LF17,LJ17,LN17,LR17,LV17,LZ17,MD17,#REF!,ML17,MP17,MT17,MX17,NB17,NF17,NJ17,NN17,NR17,NV17,NZ17,OD17,OH17,OL17,OP17,OT17,OX17,PB17,PF17,PJ17,PN17,PR17)</f>
-        <v>#REF!</v>
+      <c r="AH17">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI17">
         <v>45</v>
@@ -4883,23 +4883,23 @@
         <v>146</v>
       </c>
       <c r="PS17" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT17" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV17">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -4908,136 +4908,136 @@
         <v>119</v>
       </c>
       <c r="B18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>150</v>
       </c>
       <c r="C18">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="8"/>
+        <v>150</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="X18" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="6"/>
-        <v>150</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H18" s="3">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="I18" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J18" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="4" t="e">
-        <f>SUM(AL18,AP18,AT18,AX18,BB18,BF18,BJ18,BN18,BR18,BV18,BZ18,CD18,CH18,CL18,CP18,CT18,CX18,DB18,DF18,DJ18,DN18,DR18,DV18,DZ18,ED18,EH18,EL18,EP18,ET18,EX18,FB18,FF18,FJ18,FN18,FR18,FV18,FZ18,GD18,GH18,GL18,GP18,GT18,GX18,HB18,HF18,HJ18,HN18,HR18,HV18,HZ18,ID18,IH18,IL18,IP18,IT18,IX18,JB18,JF18,JJ18,JN18,JR18,JV18,JZ18,KD18,KH18,KL18,KP18,KT18,KX18,LB18,LF18,LJ18,LN18,LR18,LV18,LZ18,MD18,#REF!,ML18,MP18,MT18,MX18,NB18,NF18,NJ18,NN18,NR18,NV18,NZ18,OD18,OH18,OL18,OP18,OT18,OX18,PB18,PF18,PJ18,PN18,PR18)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z18" s="4" t="e">
-        <f>SUM(DB18,DF18,DJ18,DN18,DR18,DV18,DZ18,ED18,EH18,EL18,EP18,ET18,EX18,FB18,FF18,FJ18,FN18,FR18,FV18,FZ18,GD18,GH18,GL18,GP18,GT18,GX18,HB18,HF18,HJ18,HN18,HR18,HV18,HZ18,ID18,IH18,IL18,IP18,IT18,IX18,JB18,JF18,JJ18,JN18,JR18,JV18,JZ18,KD18,KH18,KL18,KP18,KT18,KX18,LB18,LF18,LJ18,LN18,LR18,LV18,LZ18,MD18,#REF!,ML18,MP18,MT18,MX18,NB18,NF18,NJ18,NN18,NR18,NV18,NZ18,OD18,OH18,OL18,OP18,OT18,OX18,PB18,PF18,PJ18,PN18,PR18)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA18">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="AF18">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH18" t="e">
-        <f>SUM(IX18,JB18,JF18,JJ18,JN18,JR18,JV18,JZ18,KD18,KH18,KL18,KP18,KT18,KX18,LB18,LF18,LJ18,LN18,LR18,LV18,LZ18,MD18,#REF!,ML18,MP18,MT18,MX18,NB18,NF18,NJ18,NN18,NR18,NV18,NZ18,OD18,OH18,OL18,OP18,OT18,OX18,PB18,PF18,PJ18,PN18,PR18)</f>
-        <v>#REF!</v>
+      <c r="AH18">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI18">
         <v>45</v>
@@ -5061,23 +5061,23 @@
         <v>145</v>
       </c>
       <c r="PS18" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT18" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU18" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV18">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -5086,71 +5086,71 @@
         <v>117</v>
       </c>
       <c r="B19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>150</v>
       </c>
       <c r="C19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
       <c r="G19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L19" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P19" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q19" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S19">
@@ -5158,64 +5158,64 @@
         <v>0</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U19" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V19" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="4" t="e">
-        <f>SUM(AL19,AP19,AT19,AX19,BB19,BF19,BJ19,BN19,BR19,BV19,BZ19,CD19,CH19,CL19,CP19,CT19,CX19,DB19,DF19,DJ19,DN19,DR19,DV19,DZ19,ED19,EH19,EL19,EP19,ET19,EX19,FB19,FF19,FJ19,FN19,FR19,FV19,FZ19,GD19,GH19,GL19,GP19,GT19,GX19,HB19,HF19,HJ19,HN19,HR19,HV19,HZ19,ID19,IH19,IL19,IP19,IT19,IX19,JB19,JF19,JJ19,JN19,JR19,JV19,JZ19,KD19,KH19,KL19,KP19,KT19,KX19,LB19,LF19,LJ19,LN19,LR19,LV19,LZ19,MD19,#REF!,ML19,MP19,MT19,MX19,NB19,NF19,NJ19,NN19,NR19,NV19,NZ19,OD19,OH19,OL19,OP19,OT19,OX19,PB19,PF19,PJ19,PN19,PR19)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z19" s="4" t="e">
-        <f>SUM(DB19,DF19,DJ19,DN19,DR19,DV19,DZ19,ED19,EH19,EL19,EP19,ET19,EX19,FB19,FF19,FJ19,FN19,FR19,FV19,FZ19,GD19,GH19,GL19,GP19,GT19,GX19,HB19,HF19,HJ19,HN19,HR19,HV19,HZ19,ID19,IH19,IL19,IP19,IT19,IX19,JB19,JF19,JJ19,JN19,JR19,JV19,JZ19,KD19,KH19,KL19,KP19,KT19,KX19,LB19,LF19,LJ19,LN19,LR19,LV19,LZ19,MD19,#REF!,ML19,MP19,MT19,MX19,NB19,NF19,NJ19,NN19,NR19,NV19,NZ19,OD19,OH19,OL19,OP19,OT19,OX19,PB19,PF19,PJ19,PN19,PR19)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AE19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG19">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH19" t="e">
-        <f>SUM(IX19,JB19,JF19,JJ19,JN19,JR19,JV19,JZ19,KD19,KH19,KL19,KP19,KT19,KX19,LB19,LF19,LJ19,LN19,LR19,LV19,LZ19,MD19,#REF!,ML19,MP19,MT19,MX19,NB19,NF19,NJ19,NN19,NR19,NV19,NZ19,OD19,OH19,OL19,OP19,OT19,OX19,PB19,PF19,PJ19,PN19,PR19)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI19">
         <v>45</v>
@@ -5236,23 +5236,23 @@
         <v>145</v>
       </c>
       <c r="PS19" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV19">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -5261,136 +5261,136 @@
         <v>141</v>
       </c>
       <c r="B20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>75</v>
       </c>
       <c r="C20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
       <c r="G20">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="H20" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
+      <c r="H20" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
       <c r="J20" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S20">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="4" t="e">
-        <f>SUM(AL20,AP20,AT20,AX20,BB20,BF20,BJ20,BN20,BR20,BV20,BZ20,CD20,CH20,CL20,CP20,CT20,CX20,DB20,DF20,DJ20,DN20,DR20,DV20,DZ20,ED20,EH20,EL20,EP20,ET20,EX20,FB20,FF20,FJ20,FN20,FR20,FV20,FZ20,GD20,GH20,GL20,GP20,GT20,GX20,HB20,HF20,HJ20,HN20,HR20,HV20,HZ20,ID20,IH20,IL20,IP20,IT20,IX20,JB20,JF20,JJ20,JN20,JR20,JV20,JZ20,KD20,KH20,KL20,KP20,KT20,KX20,LB20,LF20,LJ20,LN20,LR20,LV20,LZ20,MD20,#REF!,ML20,MP20,MT20,MX20,NB20,NF20,NJ20,NN20,NR20,NV20,NZ20,OD20,OH20,OL20,OP20,OT20,OX20,PB20,PF20,PJ20,PN20,PR20)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z20" s="4" t="e">
-        <f>SUM(DB20,DF20,DJ20,DN20,DR20,DV20,DZ20,ED20,EH20,EL20,EP20,ET20,EX20,FB20,FF20,FJ20,FN20,FR20,FV20,FZ20,GD20,GH20,GL20,GP20,GT20,GX20,HB20,HF20,HJ20,HN20,HR20,HV20,HZ20,ID20,IH20,IL20,IP20,IT20,IX20,JB20,JF20,JJ20,JN20,JR20,JV20,JZ20,KD20,KH20,KL20,KP20,KT20,KX20,LB20,LF20,LJ20,LN20,LR20,LV20,LZ20,MD20,#REF!,ML20,MP20,MT20,MX20,NB20,NF20,NJ20,NN20,NR20,NV20,NZ20,OD20,OH20,OL20,OP20,OT20,OX20,PB20,PF20,PJ20,PN20,PR20)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AC20">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AD20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AE20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH20" t="e">
-        <f>SUM(IX20,JB20,JF20,JJ20,JN20,JR20,JV20,JZ20,KD20,KH20,KL20,KP20,KT20,KX20,LB20,LF20,LJ20,LN20,LR20,LV20,LZ20,MD20,#REF!,ML20,MP20,MT20,MX20,NB20,NF20,NJ20,NN20,NR20,NV20,NZ20,OD20,OH20,OL20,OP20,OT20,OX20,PB20,PF20,PJ20,PN20,PR20)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI20">
         <v>45</v>
@@ -5405,23 +5405,23 @@
         <v>146</v>
       </c>
       <c r="PS20" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT20" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU20" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV20">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
     </row>
@@ -5430,136 +5430,136 @@
         <v>136</v>
       </c>
       <c r="B21">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>74</v>
       </c>
       <c r="C21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>74</v>
       </c>
       <c r="G21">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H21" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
+      <c r="H21" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
       <c r="J21" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L21" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N21" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R21" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T21" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U21" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V21" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="4" t="e">
-        <f>SUM(AL21,AP21,AT21,AX21,BB21,BF21,BJ21,BN21,BR21,BV21,BZ21,CD21,CH21,CL21,CP21,CT21,CX21,DB21,DF21,DJ21,DN21,DR21,DV21,DZ21,ED21,EH21,EL21,EP21,ET21,EX21,FB21,FF21,FJ21,FN21,FR21,FV21,FZ21,GD21,GH21,GL21,GP21,GT21,GX21,HB21,HF21,HJ21,HN21,HR21,HV21,HZ21,ID21,IH21,IL21,IP21,IT21,IX21,JB21,JF21,JJ21,JN21,JR21,JV21,JZ21,KD21,KH21,KL21,KP21,KT21,KX21,LB21,LF21,LJ21,LN21,LR21,LV21,LZ21,MD21,#REF!,ML21,MP21,MT21,MX21,NB21,NF21,NJ21,NN21,NR21,NV21,NZ21,OD21,OH21,OL21,OP21,OT21,OX21,PB21,PF21,PJ21,PN21,PR21)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z21" s="4" t="e">
-        <f>SUM(DB21,DF21,DJ21,DN21,DR21,DV21,DZ21,ED21,EH21,EL21,EP21,ET21,EX21,FB21,FF21,FJ21,FN21,FR21,FV21,FZ21,GD21,GH21,GL21,GP21,GT21,GX21,HB21,HF21,HJ21,HN21,HR21,HV21,HZ21,ID21,IH21,IL21,IP21,IT21,IX21,JB21,JF21,JJ21,JN21,JR21,JV21,JZ21,KD21,KH21,KL21,KP21,KT21,KX21,LB21,LF21,LJ21,LN21,LR21,LV21,LZ21,MD21,#REF!,ML21,MP21,MT21,MX21,NB21,NF21,NJ21,NN21,NR21,NV21,NZ21,OD21,OH21,OL21,OP21,OT21,OX21,PB21,PF21,PJ21,PN21,PR21)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AE21">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH21" t="e">
-        <f>SUM(IX21,JB21,JF21,JJ21,JN21,JR21,JV21,JZ21,KD21,KH21,KL21,KP21,KT21,KX21,LB21,LF21,LJ21,LN21,LR21,LV21,LZ21,MD21,#REF!,ML21,MP21,MT21,MX21,NB21,NF21,NJ21,NN21,NR21,NV21,NZ21,OD21,OH21,OL21,OP21,OT21,OX21,PB21,PF21,PJ21,PN21,PR21)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI21">
         <v>22</v>
@@ -5580,23 +5580,23 @@
         <v>146</v>
       </c>
       <c r="PS21" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT21" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU21" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV21">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW21">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -5605,136 +5605,136 @@
         <v>137</v>
       </c>
       <c r="B22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>82</v>
       </c>
       <c r="C22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="G22">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
+      <c r="H22" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
       <c r="J22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S22">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="T22" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="U22" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V22" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="4" t="e">
-        <f>SUM(AL22,AP22,AT22,AX22,BB22,BF22,BJ22,BN22,BR22,BV22,BZ22,CD22,CH22,CL22,CP22,CT22,CX22,DB22,DF22,DJ22,DN22,DR22,DV22,DZ22,ED22,EH22,EL22,EP22,ET22,EX22,FB22,FF22,FJ22,FN22,FR22,FV22,FZ22,GD22,GH22,GL22,GP22,GT22,GX22,HB22,HF22,HJ22,HN22,HR22,HV22,HZ22,ID22,IH22,IL22,IP22,IT22,IX22,JB22,JF22,JJ22,JN22,JR22,JV22,JZ22,KD22,KH22,KL22,KP22,KT22,KX22,LB22,LF22,LJ22,LN22,LR22,LV22,LZ22,MD22,#REF!,ML22,MP22,MT22,MX22,NB22,NF22,NJ22,NN22,NR22,NV22,NZ22,OD22,OH22,OL22,OP22,OT22,OX22,PB22,PF22,PJ22,PN22,PR22)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z22" s="4" t="e">
-        <f>SUM(DB22,DF22,DJ22,DN22,DR22,DV22,DZ22,ED22,EH22,EL22,EP22,ET22,EX22,FB22,FF22,FJ22,FN22,FR22,FV22,FZ22,GD22,GH22,GL22,GP22,GT22,GX22,HB22,HF22,HJ22,HN22,HR22,HV22,HZ22,ID22,IH22,IL22,IP22,IT22,IX22,JB22,JF22,JJ22,JN22,JR22,JV22,JZ22,KD22,KH22,KL22,KP22,KT22,KX22,LB22,LF22,LJ22,LN22,LR22,LV22,LZ22,MD22,#REF!,ML22,MP22,MT22,MX22,NB22,NF22,NJ22,NN22,NR22,NV22,NZ22,OD22,OH22,OL22,OP22,OT22,OX22,PB22,PF22,PJ22,PN22,PR22)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4">
+        <f t="shared" si="50"/>
+        <v>1</v>
+      </c>
+      <c r="Z22" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AE22">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF22">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AG22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH22" t="e">
-        <f>SUM(IX22,JB22,JF22,JJ22,JN22,JR22,JV22,JZ22,KD22,KH22,KL22,KP22,KT22,KX22,LB22,LF22,LJ22,LN22,LR22,LV22,LZ22,MD22,#REF!,ML22,MP22,MT22,MX22,NB22,NF22,NJ22,NN22,NR22,NV22,NZ22,OD22,OH22,OL22,OP22,OT22,OX22,PB22,PF22,PJ22,PN22,PR22)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI22">
         <v>22</v>
@@ -5758,23 +5758,23 @@
         <v>146</v>
       </c>
       <c r="PS22" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT22" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU22" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV22">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW22">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -5783,136 +5783,136 @@
         <v>138</v>
       </c>
       <c r="B23">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="C23">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="J23" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="X23" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="AF23">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D23">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="6"/>
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="H23" s="3">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I23" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J23" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W23" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="4" t="e">
-        <f>SUM(AL23,AP23,AT23,AX23,BB23,BF23,BJ23,BN23,BR23,BV23,BZ23,CD23,CH23,CL23,CP23,CT23,CX23,DB23,DF23,DJ23,DN23,DR23,DV23,DZ23,ED23,EH23,EL23,EP23,ET23,EX23,FB23,FF23,FJ23,FN23,FR23,FV23,FZ23,GD23,GH23,GL23,GP23,GT23,GX23,HB23,HF23,HJ23,HN23,HR23,HV23,HZ23,ID23,IH23,IL23,IP23,IT23,IX23,JB23,JF23,JJ23,JN23,JR23,JV23,JZ23,KD23,KH23,KL23,KP23,KT23,KX23,LB23,LF23,LJ23,LN23,LR23,LV23,LZ23,MD23,#REF!,ML23,MP23,MT23,MX23,NB23,NF23,NJ23,NN23,NR23,NV23,NZ23,OD23,OH23,OL23,OP23,OT23,OX23,PB23,PF23,PJ23,PN23,PR23)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z23" s="4" t="e">
-        <f>SUM(DB23,DF23,DJ23,DN23,DR23,DV23,DZ23,ED23,EH23,EL23,EP23,ET23,EX23,FB23,FF23,FJ23,FN23,FR23,FV23,FZ23,GD23,GH23,GL23,GP23,GT23,GX23,HB23,HF23,HJ23,HN23,HR23,HV23,HZ23,ID23,IH23,IL23,IP23,IT23,IX23,JB23,JF23,JJ23,JN23,JR23,JV23,JZ23,KD23,KH23,KL23,KP23,KT23,KX23,LB23,LF23,LJ23,LN23,LR23,LV23,LZ23,MD23,#REF!,ML23,MP23,MT23,MX23,NB23,NF23,NJ23,NN23,NR23,NV23,NZ23,OD23,OH23,OL23,OP23,OT23,OX23,PB23,PF23,PJ23,PN23,PR23)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA23">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="AF23">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH23" t="e">
-        <f>SUM(IX23,JB23,JF23,JJ23,JN23,JR23,JV23,JZ23,KD23,KH23,KL23,KP23,KT23,KX23,LB23,LF23,LJ23,LN23,LR23,LV23,LZ23,MD23,#REF!,ML23,MP23,MT23,MX23,NB23,NF23,NJ23,NN23,NR23,NV23,NZ23,OD23,OH23,OL23,OP23,OT23,OX23,PB23,PF23,PJ23,PN23,PR23)</f>
-        <v>#REF!</v>
+      <c r="AH23">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI23">
         <v>45</v>
@@ -5930,23 +5930,23 @@
         <v>1</v>
       </c>
       <c r="PS23" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT23" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU23" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV23">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
     </row>
@@ -5955,136 +5955,136 @@
         <v>140</v>
       </c>
       <c r="B24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>90</v>
       </c>
       <c r="C24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="8"/>
+        <v>90</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D24">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="6"/>
-        <v>90</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="H24" s="3">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I24" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J24" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="4" t="e">
-        <f>SUM(AL24,AP24,AT24,AX24,BB24,BF24,BJ24,BN24,BR24,BV24,BZ24,CD24,CH24,CL24,CP24,CT24,CX24,DB24,DF24,DJ24,DN24,DR24,DV24,DZ24,ED24,EH24,EL24,EP24,ET24,EX24,FB24,FF24,FJ24,FN24,FR24,FV24,FZ24,GD24,GH24,GL24,GP24,GT24,GX24,HB24,HF24,HJ24,HN24,HR24,HV24,HZ24,ID24,IH24,IL24,IP24,IT24,IX24,JB24,JF24,JJ24,JN24,JR24,JV24,JZ24,KD24,KH24,KL24,KP24,KT24,KX24,LB24,LF24,LJ24,LN24,LR24,LV24,LZ24,MD24,#REF!,ML24,MP24,MT24,MX24,NB24,NF24,NJ24,NN24,NR24,NV24,NZ24,OD24,OH24,OL24,OP24,OT24,OX24,PB24,PF24,PJ24,PN24,PR24)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z24" s="4" t="e">
-        <f>SUM(DB24,DF24,DJ24,DN24,DR24,DV24,DZ24,ED24,EH24,EL24,EP24,ET24,EX24,FB24,FF24,FJ24,FN24,FR24,FV24,FZ24,GD24,GH24,GL24,GP24,GT24,GX24,HB24,HF24,HJ24,HN24,HR24,HV24,HZ24,ID24,IH24,IL24,IP24,IT24,IX24,JB24,JF24,JJ24,JN24,JR24,JV24,JZ24,KD24,KH24,KL24,KP24,KT24,KX24,LB24,LF24,LJ24,LN24,LR24,LV24,LZ24,MD24,#REF!,ML24,MP24,MT24,MX24,NB24,NF24,NJ24,NN24,NR24,NV24,NZ24,OD24,OH24,OL24,OP24,OT24,OX24,PB24,PF24,PJ24,PN24,PR24)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA24">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH24" t="e">
-        <f>SUM(IX24,JB24,JF24,JJ24,JN24,JR24,JV24,JZ24,KD24,KH24,KL24,KP24,KT24,KX24,LB24,LF24,LJ24,LN24,LR24,LV24,LZ24,MD24,#REF!,ML24,MP24,MT24,MX24,NB24,NF24,NJ24,NN24,NR24,NV24,NZ24,OD24,OH24,OL24,OP24,OT24,OX24,PB24,PF24,PJ24,PN24,PR24)</f>
-        <v>#REF!</v>
+      <c r="AH24">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI24">
         <v>45</v>
@@ -6099,23 +6099,23 @@
         <v>146</v>
       </c>
       <c r="PS24" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT24" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU24" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV24">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
     </row>
@@ -6124,136 +6124,136 @@
         <v>139</v>
       </c>
       <c r="B25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>120</v>
       </c>
       <c r="C25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="J25" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="X25" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D25">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="6"/>
-        <v>120</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H25" s="3">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I25" s="3">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="J25" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W25" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="4" t="e">
-        <f>SUM(AL25,AP25,AT25,AX25,BB25,BF25,BJ25,BN25,BR25,BV25,BZ25,CD25,CH25,CL25,CP25,CT25,CX25,DB25,DF25,DJ25,DN25,DR25,DV25,DZ25,ED25,EH25,EL25,EP25,ET25,EX25,FB25,FF25,FJ25,FN25,FR25,FV25,FZ25,GD25,GH25,GL25,GP25,GT25,GX25,HB25,HF25,HJ25,HN25,HR25,HV25,HZ25,ID25,IH25,IL25,IP25,IT25,IX25,JB25,JF25,JJ25,JN25,JR25,JV25,JZ25,KD25,KH25,KL25,KP25,KT25,KX25,LB25,LF25,LJ25,LN25,LR25,LV25,LZ25,MD25,#REF!,ML25,MP25,MT25,MX25,NB25,NF25,NJ25,NN25,NR25,NV25,NZ25,OD25,OH25,OL25,OP25,OT25,OX25,PB25,PF25,PJ25,PN25,PR25)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z25" s="4" t="e">
-        <f>SUM(DB25,DF25,DJ25,DN25,DR25,DV25,DZ25,ED25,EH25,EL25,EP25,ET25,EX25,FB25,FF25,FJ25,FN25,FR25,FV25,FZ25,GD25,GH25,GL25,GP25,GT25,GX25,HB25,HF25,HJ25,HN25,HR25,HV25,HZ25,ID25,IH25,IL25,IP25,IT25,IX25,JB25,JF25,JJ25,JN25,JR25,JV25,JZ25,KD25,KH25,KL25,KP25,KT25,KX25,LB25,LF25,LJ25,LN25,LR25,LV25,LZ25,MD25,#REF!,ML25,MP25,MT25,MX25,NB25,NF25,NJ25,NN25,NR25,NV25,NZ25,OD25,OH25,OL25,OP25,OT25,OX25,PB25,PF25,PJ25,PN25,PR25)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA25">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="AF25">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH25" t="e">
-        <f>SUM(IX25,JB25,JF25,JJ25,JN25,JR25,JV25,JZ25,KD25,KH25,KL25,KP25,KT25,KX25,LB25,LF25,LJ25,LN25,LR25,LV25,LZ25,MD25,#REF!,ML25,MP25,MT25,MX25,NB25,NF25,NJ25,NN25,NR25,NV25,NZ25,OD25,OH25,OL25,OP25,OT25,OX25,PB25,PF25,PJ25,PN25,PR25)</f>
-        <v>#REF!</v>
+      <c r="AH25">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI25">
         <v>45</v>
@@ -6277,23 +6277,23 @@
         <v>1</v>
       </c>
       <c r="PS25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT25" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV25">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -6302,155 +6302,155 @@
         <v>116</v>
       </c>
       <c r="B26">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="PS26" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="C26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D26">
+      <c r="PT26" s="3">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="PU26" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="PV26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E26">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W26" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="4" t="e">
-        <f>SUM(AL26,AP26,AT26,AX26,BB26,BF26,BJ26,BN26,BR26,BV26,BZ26,CD26,CH26,CL26,CP26,CT26,CX26,DB26,DF26,DJ26,DN26,DR26,DV26,DZ26,ED26,EH26,EL26,EP26,ET26,EX26,FB26,FF26,FJ26,FN26,FR26,FV26,FZ26,GD26,GH26,GL26,GP26,GT26,GX26,HB26,HF26,HJ26,HN26,HR26,HV26,HZ26,ID26,IH26,IL26,IP26,IT26,IX26,JB26,JF26,JJ26,JN26,JR26,JV26,JZ26,KD26,KH26,KL26,KP26,KT26,KX26,LB26,LF26,LJ26,LN26,LR26,LV26,LZ26,MD26,#REF!,ML26,MP26,MT26,MX26,NB26,NF26,NJ26,NN26,NR26,NV26,NZ26,OD26,OH26,OL26,OP26,OT26,OX26,PB26,PF26,PJ26,PN26,PR26)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z26" s="4" t="e">
-        <f>SUM(DB26,DF26,DJ26,DN26,DR26,DV26,DZ26,ED26,EH26,EL26,EP26,ET26,EX26,FB26,FF26,FJ26,FN26,FR26,FV26,FZ26,GD26,GH26,GL26,GP26,GT26,GX26,HB26,HF26,HJ26,HN26,HR26,HV26,HZ26,ID26,IH26,IL26,IP26,IT26,IX26,JB26,JF26,JJ26,JN26,JR26,JV26,JZ26,KD26,KH26,KL26,KP26,KT26,KX26,LB26,LF26,LJ26,LN26,LR26,LV26,LZ26,MD26,#REF!,ML26,MP26,MT26,MX26,NB26,NF26,NJ26,NN26,NR26,NV26,NZ26,OD26,OH26,OL26,OP26,OT26,OX26,PB26,PF26,PJ26,PN26,PR26)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA26">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH26" t="e">
-        <f>SUM(IX26,JB26,JF26,JJ26,JN26,JR26,JV26,JZ26,KD26,KH26,KL26,KP26,KT26,KX26,LB26,LF26,LJ26,LN26,LR26,LV26,LZ26,MD26,#REF!,ML26,MP26,MT26,MX26,NB26,NF26,NJ26,NN26,NR26,NV26,NZ26,OD26,OH26,OL26,OP26,OT26,OX26,PB26,PF26,PJ26,PN26,PR26)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="PS26" s="3">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="PT26" s="3">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="PU26" s="3">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="PV26">
-        <f>COUNTIF(IU:PR,"HG")</f>
-        <v>0</v>
-      </c>
       <c r="PW26">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -6459,136 +6459,136 @@
         <v>142</v>
       </c>
       <c r="B27">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>90</v>
       </c>
       <c r="C27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="8"/>
+        <v>90</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D27">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="6"/>
-        <v>90</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="H27" s="3">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I27" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J27" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W27" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="4" t="e">
-        <f>SUM(AL27,AP27,AT27,AX27,BB27,BF27,BJ27,BN27,BR27,BV27,BZ27,CD27,CH27,CL27,CP27,CT27,CX27,DB27,DF27,DJ27,DN27,DR27,DV27,DZ27,ED27,EH27,EL27,EP27,ET27,EX27,FB27,FF27,FJ27,FN27,FR27,FV27,FZ27,GD27,GH27,GL27,GP27,GT27,GX27,HB27,HF27,HJ27,HN27,HR27,HV27,HZ27,ID27,IH27,IL27,IP27,IT27,IX27,JB27,JF27,JJ27,JN27,JR27,JV27,JZ27,KD27,KH27,KL27,KP27,KT27,KX27,LB27,LF27,LJ27,LN27,LR27,LV27,LZ27,MD27,#REF!,ML27,MP27,MT27,MX27,NB27,NF27,NJ27,NN27,NR27,NV27,NZ27,OD27,OH27,OL27,OP27,OT27,OX27,PB27,PF27,PJ27,PN27,PR27)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z27" s="4" t="e">
-        <f>SUM(DB27,DF27,DJ27,DN27,DR27,DV27,DZ27,ED27,EH27,EL27,EP27,ET27,EX27,FB27,FF27,FJ27,FN27,FR27,FV27,FZ27,GD27,GH27,GL27,GP27,GT27,GX27,HB27,HF27,HJ27,HN27,HR27,HV27,HZ27,ID27,IH27,IL27,IP27,IT27,IX27,JB27,JF27,JJ27,JN27,JR27,JV27,JZ27,KD27,KH27,KL27,KP27,KT27,KX27,LB27,LF27,LJ27,LN27,LR27,LV27,LZ27,MD27,#REF!,ML27,MP27,MT27,MX27,NB27,NF27,NJ27,NN27,NR27,NV27,NZ27,OD27,OH27,OL27,OP27,OT27,OX27,PB27,PF27,PJ27,PN27,PR27)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA27">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH27" t="e">
-        <f>SUM(IX27,JB27,JF27,JJ27,JN27,JR27,JV27,JZ27,KD27,KH27,KL27,KP27,KT27,KX27,LB27,LF27,LJ27,LN27,LR27,LV27,LZ27,MD27,#REF!,ML27,MP27,MT27,MX27,NB27,NF27,NJ27,NN27,NR27,NV27,NZ27,OD27,OH27,OL27,OP27,OT27,OX27,PB27,PF27,PJ27,PN27,PR27)</f>
-        <v>#REF!</v>
+      <c r="AH27">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI27">
         <v>45</v>
@@ -6603,23 +6603,23 @@
         <v>146</v>
       </c>
       <c r="PS27" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU27" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV27">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW27">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
     </row>
@@ -6628,136 +6628,136 @@
         <v>143</v>
       </c>
       <c r="B28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>120</v>
       </c>
       <c r="C28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="3">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AG28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D28">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="6"/>
-        <v>120</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="H28" s="3">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I28" s="3">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="J28" s="3">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="3">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
-        <v>0</v>
-      </c>
-      <c r="W28" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="4" t="e">
-        <f>SUM(AL28,AP28,AT28,AX28,BB28,BF28,BJ28,BN28,BR28,BV28,BZ28,CD28,CH28,CL28,CP28,CT28,CX28,DB28,DF28,DJ28,DN28,DR28,DV28,DZ28,ED28,EH28,EL28,EP28,ET28,EX28,FB28,FF28,FJ28,FN28,FR28,FV28,FZ28,GD28,GH28,GL28,GP28,GT28,GX28,HB28,HF28,HJ28,HN28,HR28,HV28,HZ28,ID28,IH28,IL28,IP28,IT28,IX28,JB28,JF28,JJ28,JN28,JR28,JV28,JZ28,KD28,KH28,KL28,KP28,KT28,KX28,LB28,LF28,LJ28,LN28,LR28,LV28,LZ28,MD28,#REF!,ML28,MP28,MT28,MX28,NB28,NF28,NJ28,NN28,NR28,NV28,NZ28,OD28,OH28,OL28,OP28,OT28,OX28,PB28,PF28,PJ28,PN28,PR28)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z28" s="4" t="e">
-        <f>SUM(DB28,DF28,DJ28,DN28,DR28,DV28,DZ28,ED28,EH28,EL28,EP28,ET28,EX28,FB28,FF28,FJ28,FN28,FR28,FV28,FZ28,GD28,GH28,GL28,GP28,GT28,GX28,HB28,HF28,HJ28,HN28,HR28,HV28,HZ28,ID28,IH28,IL28,IP28,IT28,IX28,JB28,JF28,JJ28,JN28,JR28,JV28,JZ28,KD28,KH28,KL28,KP28,KT28,KX28,LB28,LF28,LJ28,LN28,LR28,LV28,LZ28,MD28,#REF!,ML28,MP28,MT28,MX28,NB28,NF28,NJ28,NN28,NR28,NV28,NZ28,OD28,OH28,OL28,OP28,OT28,OX28,PB28,PF28,PJ28,PN28,PR28)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA28">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH28" t="e">
-        <f>SUM(IX28,JB28,JF28,JJ28,JN28,JR28,JV28,JZ28,KD28,KH28,KL28,KP28,KT28,KX28,LB28,LF28,LJ28,LN28,LR28,LV28,LZ28,MD28,#REF!,ML28,MP28,MT28,MX28,NB28,NF28,NJ28,NN28,NR28,NV28,NZ28,OD28,OH28,OL28,OP28,OT28,OX28,PB28,PF28,PJ28,PN28,PR28)</f>
-        <v>#REF!</v>
+      <c r="AH28">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI28">
         <v>45</v>
@@ -6778,23 +6778,23 @@
         <v>146</v>
       </c>
       <c r="PS28" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="PT28" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="PU28" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="PV28">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW28">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
     </row>
@@ -6803,136 +6803,136 @@
         <v>144</v>
       </c>
       <c r="B29">
-        <f t="shared" ref="B29" si="56">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
+        <f t="shared" ref="B29" si="61">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
         <v>120</v>
       </c>
       <c r="C29">
-        <f t="shared" ref="C29" si="57">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
+        <f t="shared" ref="C29" si="62">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
         <v>0</v>
       </c>
       <c r="D29">
-        <f t="shared" ref="D29" si="58">SUM(GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29)</f>
+        <f t="shared" ref="D29" si="63">SUM(GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29)</f>
         <v>0</v>
       </c>
       <c r="E29">
-        <f t="shared" ref="E29" si="59">SUM(IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
+        <f t="shared" ref="E29" si="64">SUM(IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
         <v>0</v>
       </c>
       <c r="F29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>120</v>
       </c>
       <c r="G29">
-        <f t="shared" ref="G29" si="60">SUM(H29:I29)</f>
+        <f t="shared" ref="G29" si="65">SUM(H29:I29)</f>
         <v>3</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" ref="H29" si="61">COUNTIF(AI29:PR29,"T")</f>
+        <f t="shared" ref="H29" si="66">COUNTIF(AI29:PR29,"T")</f>
         <v>1</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" ref="I29" si="62">COUNTIF(AI29:PR29,"R")</f>
+        <f t="shared" ref="I29" si="67">COUNTIF(AI29:PR29,"R")</f>
         <v>2</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" ref="J29" si="63">COUNTIF(AI29:PR29,"NR")</f>
+        <f t="shared" ref="J29" si="68">COUNTIF(AI29:PR29,"NR")</f>
         <v>0</v>
       </c>
       <c r="K29">
-        <f t="shared" ref="K29" si="64">SUM(L29:M29)</f>
+        <f t="shared" ref="K29" si="69">SUM(L29:M29)</f>
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <f t="shared" ref="L29" si="65">COUNTIF(CY29:GX29,"T")</f>
+        <f t="shared" ref="L29" si="70">COUNTIF(CY29:GX29,"T")</f>
         <v>0</v>
       </c>
       <c r="M29" s="3">
-        <f t="shared" ref="M29" si="66">COUNTIF(CY29:GX29,"R")</f>
+        <f t="shared" ref="M29" si="71">COUNTIF(CY29:GX29,"R")</f>
         <v>0</v>
       </c>
       <c r="N29" s="3">
-        <f t="shared" ref="N29" si="67">COUNTIF(CY29:GX29,"NR")</f>
+        <f t="shared" ref="N29" si="72">COUNTIF(CY29:GX29,"NR")</f>
         <v>0</v>
       </c>
       <c r="O29">
-        <f t="shared" ref="O29" si="68">SUM(P29:Q29)</f>
+        <f t="shared" ref="O29" si="73">SUM(P29:Q29)</f>
         <v>0</v>
       </c>
       <c r="P29" s="3">
-        <f t="shared" ref="P29" si="69">COUNTIF(GY29:IT29,"T")</f>
+        <f t="shared" ref="P29" si="74">COUNTIF(GY29:IT29,"T")</f>
         <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <f t="shared" ref="Q29" si="70">COUNTIF(GY29:IT29,"R")</f>
+        <f t="shared" ref="Q29" si="75">COUNTIF(GY29:IT29,"R")</f>
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <f t="shared" ref="R29" si="71">COUNTIF(GY29:IT29,"NR")</f>
+        <f t="shared" ref="R29" si="76">COUNTIF(GY29:IT29,"NR")</f>
         <v>0</v>
       </c>
       <c r="S29">
-        <f t="shared" ref="S29" si="72">SUM(T29:U29)</f>
+        <f t="shared" ref="S29" si="77">SUM(T29:U29)</f>
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <f t="shared" ref="T29" si="73">COUNTIF(IU29:PR29,"T")</f>
+        <f t="shared" ref="T29" si="78">COUNTIF(IU29:PR29,"T")</f>
         <v>0</v>
       </c>
       <c r="U29" s="3">
-        <f t="shared" ref="U29" si="74">COUNTIF(IU29:PR29,"R")</f>
+        <f t="shared" ref="U29" si="79">COUNTIF(IU29:PR29,"R")</f>
         <v>0</v>
       </c>
       <c r="V29" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W29" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X29" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="4" t="e">
-        <f>SUM(AL29,AP29,AT29,AX29,BB29,BF29,BJ29,BN29,BR29,BV29,BZ29,CD29,CH29,CL29,CP29,CT29,CX29,DB29,DF29,DJ29,DN29,DR29,DV29,DZ29,ED29,EH29,EL29,EP29,ET29,EX29,FB29,FF29,FJ29,FN29,FR29,FV29,FZ29,GD29,GH29,GL29,GP29,GT29,GX29,HB29,HF29,HJ29,HN29,HR29,HV29,HZ29,ID29,IH29,IL29,IP29,IT29,IX29,JB29,JF29,JJ29,JN29,JR29,JV29,JZ29,KD29,KH29,KL29,KP29,KT29,KX29,LB29,LF29,LJ29,LN29,LR29,LV29,LZ29,MD29,#REF!,ML29,MP29,MT29,MX29,NB29,NF29,NJ29,NN29,NR29,NV29,NZ29,OD29,OH29,OL29,OP29,OT29,OX29,PB29,PF29,PJ29,PN29,PR29)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z29" s="4" t="e">
-        <f>SUM(DB29,DF29,DJ29,DN29,DR29,DV29,DZ29,ED29,EH29,EL29,EP29,ET29,EX29,FB29,FF29,FJ29,FN29,FR29,FV29,FZ29,GD29,GH29,GL29,GP29,GT29,GX29,HB29,HF29,HJ29,HN29,HR29,HV29,HZ29,ID29,IH29,IL29,IP29,IT29,IX29,JB29,JF29,JJ29,JN29,JR29,JV29,JZ29,KD29,KH29,KL29,KP29,KT29,KX29,LB29,LF29,LJ29,LN29,LR29,LV29,LZ29,MD29,#REF!,ML29,MP29,MT29,MX29,NB29,NF29,NJ29,NN29,NR29,NV29,NZ29,OD29,OH29,OL29,OP29,OT29,OX29,PB29,PF29,PJ29,PN29,PR29)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <f t="shared" ref="AA29" si="75">SUM(DA29,DE29,DI29,DM29,DQ29,DU29,DY29,EC29,EG29,EK29,EO29,ES29,EW29,FA29,FE29,FI29,FM29,FQ29,FU29,FY29,GC29,GG29,GK29,GO29,GS29,GW29)</f>
+        <f t="shared" ref="AA29" si="80">SUM(DA29,DE29,DI29,DM29,DQ29,DU29,DY29,EC29,EG29,EK29,EO29,ES29,EW29,FA29,FE29,FI29,FM29,FQ29,FU29,FY29,GC29,GG29,GK29,GO29,GS29,GW29)</f>
         <v>0</v>
       </c>
       <c r="AB29">
-        <f t="shared" ref="AB29" si="76">SUM(DB29,DF29,DJ29,DN29,DR29,DV29,DZ29,ED29,EH29,EL29,EP29,ET29,EX29,FB29,FF29,FJ29,FN29,FR29,FV29,FZ29,GD29,GH29,GL29,GP29,GT29,GX29)</f>
+        <f t="shared" ref="AB29" si="81">SUM(DB29,DF29,DJ29,DN29,DR29,DV29,DZ29,ED29,EH29,EL29,EP29,ET29,EX29,FB29,FF29,FJ29,FN29,FR29,FV29,FZ29,GD29,GH29,GL29,GP29,GT29,GX29)</f>
         <v>0</v>
       </c>
       <c r="AC29">
-        <f t="shared" ref="AC29" si="77">SUM(HA29,HE29,HI29,HM29,HQ29,HU29,HY29,IC29,IG29,IK29,IO29,IS29)</f>
+        <f t="shared" ref="AC29" si="82">SUM(HA29,HE29,HI29,HM29,HQ29,HU29,HY29,IC29,IG29,IK29,IO29,IS29)</f>
         <v>0</v>
       </c>
       <c r="AD29">
-        <f t="shared" ref="AD29" si="78">SUM(HB29,HF29,HJ29,HN29,HR29,HV29,HZ29,ID29,IH29,IL29,IP29,IT29)</f>
+        <f t="shared" ref="AD29" si="83">SUM(HB29,HF29,HJ29,HN29,HR29,HV29,HZ29,ID29,IH29,IL29,IP29,IT29)</f>
         <v>0</v>
       </c>
       <c r="AE29">
-        <f t="shared" ref="AE29" si="79">SUM(AK29,AO29,AS29,AW29,BA29,BE29,BI29,BM29,BQ29,BU29,BY29,CC29,CG29,CK29,CO29,CS29,CW29)</f>
+        <f t="shared" ref="AE29" si="84">SUM(AK29,AO29,AS29,AW29,BA29,BE29,BI29,BM29,BQ29,BU29,BY29,CC29,CG29,CK29,CO29,CS29,CW29)</f>
         <v>0</v>
       </c>
       <c r="AF29">
-        <f t="shared" ref="AF29" si="80">SUM(AL29,AP29,AT29,AX29,BB29,BF29,BJ29,BN29,BR29,BV29,BZ29,CD29,CH29,CL29,CP29,CT29,CX29)</f>
+        <f t="shared" ref="AF29" si="85">SUM(AL29,AP29,AT29,AX29,BB29,BF29,BJ29,BN29,BR29,BV29,BZ29,CD29,CH29,CL29,CP29,CT29,CX29)</f>
         <v>0</v>
       </c>
       <c r="AG29">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH29" t="e">
-        <f>SUM(IX29,JB29,JF29,JJ29,JN29,JR29,JV29,JZ29,KD29,KH29,KL29,KP29,KT29,KX29,LB29,LF29,LJ29,LN29,LR29,LV29,LZ29,MD29,#REF!,ML29,MP29,MT29,MX29,NB29,NF29,NJ29,NN29,NR29,NV29,NZ29,OD29,OH29,OL29,OP29,OT29,OX29,PB29,PF29,PJ29,PN29,PR29)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="AI29">
         <v>45</v>
@@ -6953,331 +6953,331 @@
         <v>146</v>
       </c>
       <c r="PS29" s="3">
-        <f t="shared" ref="PS29" si="81">COUNTIF(AI29:PR29,"HG")</f>
+        <f t="shared" ref="PS29" si="86">COUNTIF(AI29:PR29,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT29" s="3">
-        <f t="shared" ref="PT29" si="82">COUNTIF(CY29:GX29,"HG")</f>
+        <f t="shared" ref="PT29" si="87">COUNTIF(CY29:GX29,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU29" s="3">
-        <f t="shared" ref="PU29" si="83">COUNTIF(GY29:IT29,"HG")</f>
+        <f t="shared" ref="PU29" si="88">COUNTIF(GY29:IT29,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV29">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW29">
-        <f t="shared" ref="PW29" si="84">G29-(K29+O29+S29)</f>
+        <f t="shared" ref="PW29" si="89">G29-(K29+O29+S29)</f>
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B30">
-        <f t="shared" ref="B30" si="85">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
+        <f t="shared" ref="B30" si="90">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
         <v>0</v>
       </c>
       <c r="C30">
-        <f t="shared" ref="C30" si="86">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
+        <f t="shared" ref="C30" si="91">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
         <v>0</v>
       </c>
       <c r="D30">
-        <f t="shared" ref="D30" si="87">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
+        <f t="shared" ref="D30" si="92">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
         <v>0</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30" si="88">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
+        <f t="shared" ref="E30" si="93">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
         <v>0</v>
       </c>
       <c r="F30">
-        <f t="shared" ref="F30" si="89">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30)</f>
+        <f t="shared" ref="F30" si="94">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30)</f>
         <v>0</v>
       </c>
       <c r="G30">
-        <f t="shared" ref="G30" si="90">SUM(H30:I30)</f>
+        <f t="shared" ref="G30" si="95">SUM(H30:I30)</f>
         <v>0</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" ref="H30" si="91">COUNTIF(AI30:PR30,"T")</f>
+        <f t="shared" ref="H30" si="96">COUNTIF(AI30:PR30,"T")</f>
         <v>0</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" ref="I30" si="92">COUNTIF(AI30:PR30,"R")</f>
+        <f t="shared" ref="I30" si="97">COUNTIF(AI30:PR30,"R")</f>
         <v>0</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" ref="J30" si="93">COUNTIF(AI30:PR30,"NR")</f>
+        <f t="shared" ref="J30" si="98">COUNTIF(AI30:PR30,"NR")</f>
         <v>0</v>
       </c>
       <c r="K30">
-        <f t="shared" ref="K30" si="94">SUM(L30:M30)</f>
+        <f t="shared" ref="K30" si="99">SUM(L30:M30)</f>
         <v>0</v>
       </c>
       <c r="L30" s="3">
-        <f t="shared" ref="L30" si="95">COUNTIF(CY30:GX30,"T")</f>
+        <f t="shared" ref="L30" si="100">COUNTIF(CY30:GX30,"T")</f>
         <v>0</v>
       </c>
       <c r="M30" s="3">
-        <f t="shared" ref="M30" si="96">COUNTIF(CY30:GX30,"R")</f>
+        <f t="shared" ref="M30" si="101">COUNTIF(CY30:GX30,"R")</f>
         <v>0</v>
       </c>
       <c r="N30" s="3">
-        <f t="shared" ref="N30" si="97">COUNTIF(CY30:GX30,"NR")</f>
+        <f t="shared" ref="N30" si="102">COUNTIF(CY30:GX30,"NR")</f>
         <v>0</v>
       </c>
       <c r="O30">
-        <f t="shared" ref="O30" si="98">SUM(P30:Q30)</f>
+        <f t="shared" ref="O30" si="103">SUM(P30:Q30)</f>
         <v>0</v>
       </c>
       <c r="P30" s="3">
-        <f t="shared" ref="P30" si="99">COUNTIF(GY30:IT30,"T")</f>
+        <f t="shared" ref="P30" si="104">COUNTIF(GY30:IT30,"T")</f>
         <v>0</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" ref="Q30" si="100">COUNTIF(GY30:IT30,"R")</f>
+        <f t="shared" ref="Q30" si="105">COUNTIF(GY30:IT30,"R")</f>
         <v>0</v>
       </c>
       <c r="R30" s="3">
-        <f t="shared" ref="R30" si="101">COUNTIF(GY30:IT30,"NR")</f>
+        <f t="shared" ref="R30" si="106">COUNTIF(GY30:IT30,"NR")</f>
         <v>0</v>
       </c>
       <c r="S30">
-        <f t="shared" ref="S30" si="102">SUM(T30:U30)</f>
+        <f t="shared" ref="S30" si="107">SUM(T30:U30)</f>
         <v>0</v>
       </c>
       <c r="T30" s="3">
-        <f t="shared" ref="T30" si="103">COUNTIF(IU30:PR30,"T")</f>
+        <f t="shared" ref="T30" si="108">COUNTIF(IU30:PR30,"T")</f>
         <v>0</v>
       </c>
       <c r="U30" s="3">
-        <f t="shared" ref="U30" si="104">COUNTIF(IU30:PR30,"R")</f>
+        <f t="shared" ref="U30" si="109">COUNTIF(IU30:PR30,"R")</f>
         <v>0</v>
       </c>
       <c r="V30" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W30" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X30" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="4" t="e">
-        <f>SUM(AL30,AP30,AT30,AX30,BB30,BF30,BJ30,BN30,BR30,BV30,BZ30,CD30,CH30,CL30,CP30,CT30,CX30,DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30,HB30,HF30,HJ30,HN30,HR30,HV30,HZ30,ID30,IH30,IL30,IP30,IT30,IX30,JB30,JF30,JJ30,JN30,JR30,JV30,JZ30,KD30,KH30,KL30,KP30,KT30,KX30,LB30,LF30,LJ30,LN30,LR30,LV30,LZ30,MD30,#REF!,ML30,MP30,MT30,MX30,NB30,NF30,NJ30,NN30,NR30,NV30,NZ30,OD30,OH30,OL30,OP30,OT30,OX30,PB30,PF30,PJ30,PN30,PR30)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z30" s="4" t="e">
-        <f>SUM(DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30,HB30,HF30,HJ30,HN30,HR30,HV30,HZ30,ID30,IH30,IL30,IP30,IT30,IX30,JB30,JF30,JJ30,JN30,JR30,JV30,JZ30,KD30,KH30,KL30,KP30,KT30,KX30,LB30,LF30,LJ30,LN30,LR30,LV30,LZ30,MD30,#REF!,ML30,MP30,MT30,MX30,NB30,NF30,NJ30,NN30,NR30,NV30,NZ30,OD30,OH30,OL30,OP30,OT30,OX30,PB30,PF30,PJ30,PN30,PR30)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <f t="shared" ref="AA30" si="105">SUM(DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30)</f>
+        <f t="shared" ref="AA30" si="110">SUM(DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30)</f>
         <v>0</v>
       </c>
       <c r="AB30">
-        <f t="shared" ref="AB30" si="106">SUM(DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30)</f>
+        <f t="shared" ref="AB30" si="111">SUM(DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30)</f>
         <v>0</v>
       </c>
       <c r="AC30">
-        <f t="shared" ref="AC30" si="107">SUM(HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30)</f>
+        <f t="shared" ref="AC30" si="112">SUM(HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30)</f>
         <v>0</v>
       </c>
       <c r="AD30">
-        <f t="shared" ref="AD30" si="108">SUM(HB30,HF30,HJ30,HN30,HR30,HV30,HZ30,ID30,IH30,IL30,IP30,IT30)</f>
+        <f t="shared" ref="AD30" si="113">SUM(HB30,HF30,HJ30,HN30,HR30,HV30,HZ30,ID30,IH30,IL30,IP30,IT30)</f>
         <v>0</v>
       </c>
       <c r="AE30">
-        <f t="shared" ref="AE30" si="109">SUM(AK30,AO30,AS30,AW30,BA30,BE30,BI30,BM30,BQ30,BU30,BY30,CC30,CG30,CK30,CO30,CS30,CW30)</f>
+        <f t="shared" ref="AE30" si="114">SUM(AK30,AO30,AS30,AW30,BA30,BE30,BI30,BM30,BQ30,BU30,BY30,CC30,CG30,CK30,CO30,CS30,CW30)</f>
         <v>0</v>
       </c>
       <c r="AF30">
-        <f t="shared" ref="AF30" si="110">SUM(AL30,AP30,AT30,AX30,BB30,BF30,BJ30,BN30,BR30,BV30,BZ30,CD30,CH30,CL30,CP30,CT30,CX30)</f>
+        <f t="shared" ref="AF30" si="115">SUM(AL30,AP30,AT30,AX30,BB30,BF30,BJ30,BN30,BR30,BV30,BZ30,CD30,CH30,CL30,CP30,CT30,CX30)</f>
         <v>0</v>
       </c>
       <c r="AG30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH30" t="e">
-        <f>SUM(IX30,JB30,JF30,JJ30,JN30,JR30,JV30,JZ30,KD30,KH30,KL30,KP30,KT30,KX30,LB30,LF30,LJ30,LN30,LR30,LV30,LZ30,MD30,#REF!,ML30,MP30,MT30,MX30,NB30,NF30,NJ30,NN30,NR30,NV30,NZ30,OD30,OH30,OL30,OP30,OT30,OX30,PB30,PF30,PJ30,PN30,PR30)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="PS30" s="3">
-        <f t="shared" ref="PS30" si="111">COUNTIF(AI30:PR30,"HG")</f>
+        <f t="shared" ref="PS30" si="116">COUNTIF(AI30:PR30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT30" s="3">
-        <f t="shared" ref="PT30" si="112">COUNTIF(CY30:GX30,"HG")</f>
+        <f t="shared" ref="PT30" si="117">COUNTIF(CY30:GX30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU30" s="3">
-        <f t="shared" ref="PU30" si="113">COUNTIF(GY30:IT30,"HG")</f>
+        <f t="shared" ref="PU30" si="118">COUNTIF(GY30:IT30,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV30">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW30">
-        <f t="shared" ref="PW30" si="114">G30-(K30+O30+S30)</f>
+        <f t="shared" ref="PW30" si="119">G30-(K30+O30+S30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:439" x14ac:dyDescent="0.2">
       <c r="B31">
-        <f t="shared" ref="B31" si="115">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
+        <f t="shared" ref="B31" si="120">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
         <v>0</v>
       </c>
       <c r="C31">
-        <f t="shared" ref="C31" si="116">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
+        <f t="shared" ref="C31" si="121">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
         <v>0</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31" si="117">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
+        <f t="shared" ref="D31" si="122">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
         <v>0</v>
       </c>
       <c r="E31">
-        <f t="shared" ref="E31" si="118">SUM(IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
+        <f t="shared" ref="E31" si="123">SUM(IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
         <v>0</v>
       </c>
       <c r="F31">
-        <f t="shared" ref="F31" si="119">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31)</f>
+        <f t="shared" ref="F31" si="124">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31)</f>
         <v>0</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="120">SUM(H31:I31)</f>
+        <f t="shared" ref="G31" si="125">SUM(H31:I31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" ref="H31" si="121">COUNTIF(AI31:PR31,"T")</f>
+        <f t="shared" ref="H31" si="126">COUNTIF(AI31:PR31,"T")</f>
         <v>0</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" ref="I31" si="122">COUNTIF(AI31:PR31,"R")</f>
+        <f t="shared" ref="I31" si="127">COUNTIF(AI31:PR31,"R")</f>
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" ref="J31" si="123">COUNTIF(AI31:PR31,"NR")</f>
+        <f t="shared" ref="J31" si="128">COUNTIF(AI31:PR31,"NR")</f>
         <v>0</v>
       </c>
       <c r="K31">
-        <f t="shared" ref="K31" si="124">SUM(L31:M31)</f>
+        <f t="shared" ref="K31" si="129">SUM(L31:M31)</f>
         <v>0</v>
       </c>
       <c r="L31" s="3">
-        <f t="shared" ref="L31" si="125">COUNTIF(CY31:GX31,"T")</f>
+        <f t="shared" ref="L31" si="130">COUNTIF(CY31:GX31,"T")</f>
         <v>0</v>
       </c>
       <c r="M31" s="3">
-        <f t="shared" ref="M31" si="126">COUNTIF(CY31:GX31,"R")</f>
+        <f t="shared" ref="M31" si="131">COUNTIF(CY31:GX31,"R")</f>
         <v>0</v>
       </c>
       <c r="N31" s="3">
-        <f t="shared" ref="N31" si="127">COUNTIF(CY31:GX31,"NR")</f>
+        <f t="shared" ref="N31" si="132">COUNTIF(CY31:GX31,"NR")</f>
         <v>0</v>
       </c>
       <c r="O31">
-        <f t="shared" ref="O31" si="128">SUM(P31:Q31)</f>
+        <f t="shared" ref="O31" si="133">SUM(P31:Q31)</f>
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f t="shared" ref="P31" si="129">COUNTIF(GY31:IT31,"T")</f>
+        <f t="shared" ref="P31" si="134">COUNTIF(GY31:IT31,"T")</f>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <f t="shared" ref="Q31" si="130">COUNTIF(GY31:IT31,"R")</f>
+        <f t="shared" ref="Q31" si="135">COUNTIF(GY31:IT31,"R")</f>
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <f t="shared" ref="R31" si="131">COUNTIF(GY31:IT31,"NR")</f>
+        <f t="shared" ref="R31" si="136">COUNTIF(GY31:IT31,"NR")</f>
         <v>0</v>
       </c>
       <c r="S31">
-        <f t="shared" ref="S31" si="132">SUM(T31:U31)</f>
+        <f t="shared" ref="S31" si="137">SUM(T31:U31)</f>
         <v>0</v>
       </c>
       <c r="T31" s="3">
-        <f t="shared" ref="T31" si="133">COUNTIF(IU31:PR31,"T")</f>
+        <f t="shared" ref="T31" si="138">COUNTIF(IU31:PR31,"T")</f>
         <v>0</v>
       </c>
       <c r="U31" s="3">
-        <f t="shared" ref="U31" si="134">COUNTIF(IU31:PR31,"R")</f>
+        <f t="shared" ref="U31" si="139">COUNTIF(IU31:PR31,"R")</f>
         <v>0</v>
       </c>
       <c r="V31" s="3">
-        <f>COUNTIF(IU:PR,"NR")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W31" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X31" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="4" t="e">
-        <f>SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31,DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,#REF!,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z31" s="4" t="e">
-        <f>SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,#REF!,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="4">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <f t="shared" ref="AA31" si="135">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
+        <f t="shared" ref="AA31" si="140">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
         <v>0</v>
       </c>
       <c r="AB31">
-        <f t="shared" ref="AB31" si="136">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
+        <f t="shared" ref="AB31" si="141">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
         <v>0</v>
       </c>
       <c r="AC31">
-        <f t="shared" ref="AC31" si="137">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
+        <f t="shared" ref="AC31" si="142">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
         <v>0</v>
       </c>
       <c r="AD31">
-        <f t="shared" ref="AD31" si="138">SUM(HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31)</f>
+        <f t="shared" ref="AD31" si="143">SUM(HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31)</f>
         <v>0</v>
       </c>
       <c r="AE31">
-        <f t="shared" ref="AE31" si="139">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31)</f>
+        <f t="shared" ref="AE31" si="144">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31)</f>
         <v>0</v>
       </c>
       <c r="AF31">
-        <f t="shared" ref="AF31" si="140">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31)</f>
+        <f t="shared" ref="AF31" si="145">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31)</f>
         <v>0</v>
       </c>
       <c r="AG31">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH31" t="e">
-        <f>SUM(IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,#REF!,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>#REF!</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="PS31" s="3">
-        <f t="shared" ref="PS31" si="141">COUNTIF(AI31:PR31,"HG")</f>
+        <f t="shared" ref="PS31" si="146">COUNTIF(AI31:PR31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PT31" s="3">
-        <f t="shared" ref="PT31" si="142">COUNTIF(CY31:GX31,"HG")</f>
+        <f t="shared" ref="PT31" si="147">COUNTIF(CY31:GX31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PU31" s="3">
-        <f t="shared" ref="PU31" si="143">COUNTIF(GY31:IT31,"HG")</f>
+        <f t="shared" ref="PU31" si="148">COUNTIF(GY31:IT31,"HG")</f>
         <v>0</v>
       </c>
       <c r="PV31">
-        <f>COUNTIF(IU:PR,"HG")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="PW31">
-        <f t="shared" ref="PW31" si="144">G31-(K31+O31+S31)</f>
+        <f t="shared" ref="PW31" si="149">G31-(K31+O31+S31)</f>
         <v>0</v>
       </c>
     </row>

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BE5E4A-7F7C-794C-AAF1-F24D7680E5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8C9C0D-C1C7-2145-B2D1-4F905D7F26DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="147">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
@@ -2212,15 +2212,15 @@
       </c>
       <c r="F2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2)</f>
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2332,6 +2332,12 @@
       <c r="AR2" t="s">
         <v>145</v>
       </c>
+      <c r="AU2">
+        <v>90</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>145</v>
+      </c>
       <c r="PS2" s="3">
         <f>COUNTIF(AI2:PR2,"HG")</f>
         <v>0</v>
@@ -2350,7 +2356,7 @@
       </c>
       <c r="PW2">
         <f>G2-(K2+O2+S2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:439" x14ac:dyDescent="0.2">
@@ -2691,7 +2697,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="36"/>
-        <v>105</v>
+        <v>180</v>
       </c>
       <c r="C5">
         <f t="shared" si="5"/>
@@ -2707,15 +2713,15 @@
       </c>
       <c r="F5">
         <f t="shared" si="8"/>
-        <v>105</v>
+        <v>180</v>
       </c>
       <c r="G5">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="11"/>
@@ -2833,6 +2839,12 @@
       <c r="AR5" t="s">
         <v>145</v>
       </c>
+      <c r="AU5">
+        <v>75</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>145</v>
+      </c>
       <c r="PS5" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -2851,7 +2863,7 @@
       </c>
       <c r="PW5">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:439" x14ac:dyDescent="0.2">
@@ -2860,7 +2872,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="36"/>
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
@@ -2876,11 +2888,11 @@
       </c>
       <c r="F6">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
@@ -2888,7 +2900,7 @@
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="12"/>
@@ -3008,6 +3020,12 @@
       <c r="AR6" t="s">
         <v>146</v>
       </c>
+      <c r="AU6">
+        <v>15</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>146</v>
+      </c>
       <c r="PS6" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3026,7 +3044,7 @@
       </c>
       <c r="PW6">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:439" x14ac:dyDescent="0.2">
@@ -3192,7 +3210,7 @@
       </c>
       <c r="B8">
         <f t="shared" si="36"/>
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C8">
         <f t="shared" si="5"/>
@@ -3208,15 +3226,15 @@
       </c>
       <c r="F8">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="G8">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="11"/>
@@ -3340,6 +3358,12 @@
       <c r="AR8" t="s">
         <v>145</v>
       </c>
+      <c r="AU8">
+        <v>60</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>145</v>
+      </c>
       <c r="PS8" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3358,7 +3382,7 @@
       </c>
       <c r="PW8">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:439" x14ac:dyDescent="0.2">
@@ -3367,7 +3391,7 @@
       </c>
       <c r="B9">
         <f t="shared" si="36"/>
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="C9">
         <f t="shared" si="5"/>
@@ -3383,15 +3407,15 @@
       </c>
       <c r="F9">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="G9">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="11"/>
@@ -3503,6 +3527,12 @@
       <c r="AR9" t="s">
         <v>146</v>
       </c>
+      <c r="AU9">
+        <v>75</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>145</v>
+      </c>
       <c r="PS9" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3521,7 +3551,7 @@
       </c>
       <c r="PW9">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:439" x14ac:dyDescent="0.2">
@@ -3530,7 +3560,7 @@
       </c>
       <c r="B10">
         <f t="shared" si="36"/>
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
@@ -3546,15 +3576,15 @@
       </c>
       <c r="F10">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
@@ -3678,6 +3708,12 @@
       <c r="AR10" t="s">
         <v>145</v>
       </c>
+      <c r="AU10">
+        <v>60</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>145</v>
+      </c>
       <c r="PS10" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3696,7 +3732,7 @@
       </c>
       <c r="PW10">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:439" x14ac:dyDescent="0.2">
@@ -3705,7 +3741,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="36"/>
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C11">
         <f t="shared" si="5"/>
@@ -3721,15 +3757,15 @@
       </c>
       <c r="F11">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="11"/>
@@ -3853,6 +3889,12 @@
       <c r="AR11" t="s">
         <v>145</v>
       </c>
+      <c r="AU11">
+        <v>60</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>145</v>
+      </c>
       <c r="PS11" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3871,7 +3913,7 @@
       </c>
       <c r="PW11">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:439" x14ac:dyDescent="0.2">
@@ -3880,7 +3922,7 @@
       </c>
       <c r="B12">
         <f t="shared" si="36"/>
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <f t="shared" si="5"/>
@@ -3896,11 +3938,11 @@
       </c>
       <c r="F12">
         <f t="shared" si="8"/>
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="10"/>
@@ -3908,7 +3950,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="12"/>
@@ -4016,6 +4058,12 @@
       <c r="AJ12" t="s">
         <v>145</v>
       </c>
+      <c r="AU12">
+        <v>30</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>146</v>
+      </c>
       <c r="PS12" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4034,7 +4082,7 @@
       </c>
       <c r="PW12">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:439" x14ac:dyDescent="0.2">
@@ -4043,7 +4091,7 @@
       </c>
       <c r="B13">
         <f t="shared" si="36"/>
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C13">
         <f t="shared" si="5"/>
@@ -4059,11 +4107,11 @@
       </c>
       <c r="F13">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G13">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="10"/>
@@ -4071,7 +4119,7 @@
       </c>
       <c r="I13" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="12"/>
@@ -4185,6 +4233,12 @@
       <c r="AN13" t="s">
         <v>146</v>
       </c>
+      <c r="AU13">
+        <v>30</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>146</v>
+      </c>
       <c r="PS13" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4203,7 +4257,7 @@
       </c>
       <c r="PW13">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:439" x14ac:dyDescent="0.2">
@@ -4212,7 +4266,7 @@
       </c>
       <c r="B14">
         <f t="shared" si="36"/>
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
@@ -4228,11 +4282,11 @@
       </c>
       <c r="F14">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
@@ -4240,7 +4294,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="12"/>
@@ -4360,6 +4414,12 @@
       <c r="AR14" t="s">
         <v>145</v>
       </c>
+      <c r="AU14">
+        <v>30</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>146</v>
+      </c>
       <c r="PS14" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4378,7 +4438,7 @@
       </c>
       <c r="PW14">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:439" x14ac:dyDescent="0.2">
@@ -4387,7 +4447,7 @@
       </c>
       <c r="B15">
         <f t="shared" si="36"/>
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="C15">
         <f t="shared" si="5"/>
@@ -4403,11 +4463,11 @@
       </c>
       <c r="F15">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G15">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="10"/>
@@ -4415,7 +4475,7 @@
       </c>
       <c r="I15" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="12"/>
@@ -4535,6 +4595,12 @@
       <c r="AR15" t="s">
         <v>146</v>
       </c>
+      <c r="AU15">
+        <v>30</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>146</v>
+      </c>
       <c r="PS15" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4553,7 +4619,7 @@
       </c>
       <c r="PW15">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:439" x14ac:dyDescent="0.2">
@@ -4734,7 +4800,7 @@
       </c>
       <c r="B17">
         <f t="shared" si="36"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="C17">
         <f t="shared" si="5"/>
@@ -4750,11 +4816,11 @@
       </c>
       <c r="F17">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G17">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="10"/>
@@ -4762,7 +4828,7 @@
       </c>
       <c r="I17" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="3">
         <f t="shared" si="12"/>
@@ -4882,6 +4948,12 @@
       <c r="AR17" t="s">
         <v>146</v>
       </c>
+      <c r="AU17">
+        <v>40</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>146</v>
+      </c>
       <c r="PS17" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4900,7 +4972,7 @@
       </c>
       <c r="PW17">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:439" x14ac:dyDescent="0.2">
@@ -5087,7 +5159,7 @@
       </c>
       <c r="B19">
         <f t="shared" si="36"/>
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
@@ -5103,11 +5175,11 @@
       </c>
       <c r="F19">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G19">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="10"/>
@@ -5115,7 +5187,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="12"/>
@@ -5235,6 +5307,12 @@
       <c r="AR19" t="s">
         <v>145</v>
       </c>
+      <c r="AU19">
+        <v>30</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>146</v>
+      </c>
       <c r="PS19" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -5253,7 +5331,7 @@
       </c>
       <c r="PW19">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:439" x14ac:dyDescent="0.2">
@@ -5262,7 +5340,7 @@
       </c>
       <c r="B20">
         <f t="shared" si="36"/>
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C20">
         <f t="shared" si="5"/>
@@ -5278,11 +5356,11 @@
       </c>
       <c r="F20">
         <f t="shared" si="8"/>
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G20">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="10"/>
@@ -5290,7 +5368,7 @@
       </c>
       <c r="I20" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="3">
         <f t="shared" si="12"/>
@@ -5404,6 +5482,12 @@
       <c r="AR20" t="s">
         <v>146</v>
       </c>
+      <c r="AU20">
+        <v>30</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>146</v>
+      </c>
       <c r="PS20" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -5422,7 +5506,7 @@
       </c>
       <c r="PW20">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:439" x14ac:dyDescent="0.2">
@@ -5606,7 +5690,7 @@
       </c>
       <c r="B22">
         <f t="shared" si="36"/>
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C22">
         <f t="shared" si="5"/>
@@ -5622,11 +5706,11 @@
       </c>
       <c r="F22">
         <f t="shared" si="8"/>
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="G22">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="10"/>
@@ -5634,7 +5718,7 @@
       </c>
       <c r="I22" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <f t="shared" si="12"/>
@@ -5757,6 +5841,12 @@
       <c r="AR22" t="s">
         <v>146</v>
       </c>
+      <c r="AU22">
+        <v>15</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>146</v>
+      </c>
       <c r="PS22" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -5775,7 +5865,7 @@
       </c>
       <c r="PW22">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:439" x14ac:dyDescent="0.2">
@@ -5784,7 +5874,7 @@
       </c>
       <c r="B23">
         <f t="shared" si="36"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C23">
         <f t="shared" si="5"/>
@@ -5800,11 +5890,11 @@
       </c>
       <c r="F23">
         <f t="shared" si="8"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G23">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="10"/>
@@ -5812,7 +5902,7 @@
       </c>
       <c r="I23" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="3">
         <f t="shared" si="12"/>
@@ -5929,6 +6019,12 @@
       <c r="AO23">
         <v>1</v>
       </c>
+      <c r="AU23">
+        <v>15</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>146</v>
+      </c>
       <c r="PS23" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -5947,7 +6043,7 @@
       </c>
       <c r="PW23">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:439" x14ac:dyDescent="0.2">
@@ -5956,7 +6052,7 @@
       </c>
       <c r="B24">
         <f t="shared" si="36"/>
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C24">
         <f t="shared" si="5"/>
@@ -5972,11 +6068,11 @@
       </c>
       <c r="F24">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G24">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="10"/>
@@ -5984,7 +6080,7 @@
       </c>
       <c r="I24" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" si="12"/>
@@ -6098,6 +6194,12 @@
       <c r="AN24" t="s">
         <v>146</v>
       </c>
+      <c r="AU24">
+        <v>30</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>146</v>
+      </c>
       <c r="PS24" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6116,7 +6218,7 @@
       </c>
       <c r="PW24">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:439" x14ac:dyDescent="0.2">
@@ -6125,7 +6227,7 @@
       </c>
       <c r="B25">
         <f t="shared" si="36"/>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C25">
         <f t="shared" si="5"/>
@@ -6141,15 +6243,15 @@
       </c>
       <c r="F25">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G25">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="11"/>
@@ -6276,6 +6378,12 @@
       <c r="AS25">
         <v>1</v>
       </c>
+      <c r="AU25">
+        <v>60</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>145</v>
+      </c>
       <c r="PS25" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6294,7 +6402,7 @@
       </c>
       <c r="PW25">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:439" x14ac:dyDescent="0.2">
@@ -6629,7 +6737,7 @@
       </c>
       <c r="B28">
         <f t="shared" si="36"/>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
@@ -6645,15 +6753,15 @@
       </c>
       <c r="F28">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
@@ -6777,6 +6885,12 @@
       <c r="AR28" t="s">
         <v>146</v>
       </c>
+      <c r="AU28">
+        <v>60</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>145</v>
+      </c>
       <c r="PS28" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6795,7 +6909,7 @@
       </c>
       <c r="PW28">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:439" x14ac:dyDescent="0.2">
@@ -6804,7 +6918,7 @@
       </c>
       <c r="B29">
         <f t="shared" ref="B29" si="61">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C29">
         <f t="shared" ref="C29" si="62">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
@@ -6820,15 +6934,15 @@
       </c>
       <c r="F29">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G29">
         <f t="shared" ref="G29" si="65">SUM(H29:I29)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" ref="H29" si="66">COUNTIF(AI29:PR29,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" ref="I29" si="67">COUNTIF(AI29:PR29,"R")</f>
@@ -6952,6 +7066,12 @@
       <c r="AR29" t="s">
         <v>146</v>
       </c>
+      <c r="AU29">
+        <v>60</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>145</v>
+      </c>
       <c r="PS29" s="3">
         <f t="shared" ref="PS29" si="86">COUNTIF(AI29:PR29,"HG")</f>
         <v>0</v>
@@ -6970,7 +7090,7 @@
       </c>
       <c r="PW29">
         <f t="shared" ref="PW29" si="89">G29-(K29+O29+S29)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:439" x14ac:dyDescent="0.2">

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8C9C0D-C1C7-2145-B2D1-4F905D7F26DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD834D72-39FD-6E44-A685-CB01EB7B9C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="147">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
@@ -2212,15 +2212,15 @@
       </c>
       <c r="F2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2)</f>
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2338,6 +2338,12 @@
       <c r="AV2" t="s">
         <v>145</v>
       </c>
+      <c r="AY2">
+        <v>90</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>145</v>
+      </c>
       <c r="PS2" s="3">
         <f>COUNTIF(AI2:PR2,"HG")</f>
         <v>0</v>
@@ -2356,7 +2362,7 @@
       </c>
       <c r="PW2">
         <f>G2-(K2+O2+S2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:439" x14ac:dyDescent="0.2">
@@ -2522,7 +2528,7 @@
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B28" si="36">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="C4">
         <f t="shared" si="5"/>
@@ -2538,15 +2544,15 @@
       </c>
       <c r="F4">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G4">
         <f t="shared" ref="G4" si="37">SUM(H4:I4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4" si="38">COUNTIF(AI4:PR4,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" ref="I4" si="39">COUNTIF(AI4:PR4,"R")</f>
@@ -2670,6 +2676,12 @@
       <c r="AR4" t="s">
         <v>146</v>
       </c>
+      <c r="BC4">
+        <v>70</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>145</v>
+      </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="57">COUNTIF(AI4:PR4,"HG")</f>
         <v>0</v>
@@ -2688,7 +2700,7 @@
       </c>
       <c r="PW4">
         <f t="shared" ref="PW4" si="60">G4-(K4+O4+S4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:439" x14ac:dyDescent="0.2">
@@ -2697,7 +2709,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="36"/>
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="C5">
         <f t="shared" si="5"/>
@@ -2713,15 +2725,15 @@
       </c>
       <c r="F5">
         <f t="shared" si="8"/>
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G5">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="11"/>
@@ -2845,6 +2857,12 @@
       <c r="AV5" t="s">
         <v>145</v>
       </c>
+      <c r="AY5">
+        <v>90</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>145</v>
+      </c>
       <c r="PS5" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -2863,7 +2881,7 @@
       </c>
       <c r="PW5">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:439" x14ac:dyDescent="0.2">
@@ -2872,7 +2890,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="36"/>
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
@@ -2888,19 +2906,19 @@
       </c>
       <c r="F6">
         <f t="shared" si="8"/>
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="12"/>
@@ -3026,6 +3044,18 @@
       <c r="AV6" t="s">
         <v>146</v>
       </c>
+      <c r="AY6">
+        <v>60</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>145</v>
+      </c>
+      <c r="BC6">
+        <v>35</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>146</v>
+      </c>
       <c r="PS6" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3044,7 +3074,7 @@
       </c>
       <c r="PW6">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:439" x14ac:dyDescent="0.2">
@@ -3053,7 +3083,7 @@
       </c>
       <c r="B7">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <f t="shared" si="5"/>
@@ -3069,15 +3099,15 @@
       </c>
       <c r="F7">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="11"/>
@@ -3183,6 +3213,12 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="BC7">
+        <v>55</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>145</v>
+      </c>
       <c r="PS7" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3201,7 +3237,7 @@
       </c>
       <c r="PW7">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:439" x14ac:dyDescent="0.2">
@@ -3391,7 +3427,7 @@
       </c>
       <c r="B9">
         <f t="shared" si="36"/>
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="C9">
         <f t="shared" si="5"/>
@@ -3407,19 +3443,19 @@
       </c>
       <c r="F9">
         <f t="shared" si="8"/>
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="G9">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="12"/>
@@ -3533,6 +3569,18 @@
       <c r="AV9" t="s">
         <v>145</v>
       </c>
+      <c r="AY9">
+        <v>90</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>145</v>
+      </c>
+      <c r="BC9">
+        <v>50</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>146</v>
+      </c>
       <c r="PS9" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3551,7 +3599,7 @@
       </c>
       <c r="PW9">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:439" x14ac:dyDescent="0.2">
@@ -3560,7 +3608,7 @@
       </c>
       <c r="B10">
         <f t="shared" si="36"/>
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
@@ -3576,19 +3624,19 @@
       </c>
       <c r="F10">
         <f t="shared" si="8"/>
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="12"/>
@@ -3714,6 +3762,18 @@
       <c r="AV10" t="s">
         <v>145</v>
       </c>
+      <c r="AY10">
+        <v>80</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>145</v>
+      </c>
+      <c r="BC10">
+        <v>20</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>146</v>
+      </c>
       <c r="PS10" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3732,7 +3792,7 @@
       </c>
       <c r="PW10">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:439" x14ac:dyDescent="0.2">
@@ -3741,7 +3801,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="36"/>
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="C11">
         <f t="shared" si="5"/>
@@ -3757,19 +3817,19 @@
       </c>
       <c r="F11">
         <f t="shared" si="8"/>
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="12"/>
@@ -3895,6 +3955,18 @@
       <c r="AV11" t="s">
         <v>145</v>
       </c>
+      <c r="AY11">
+        <v>80</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>145</v>
+      </c>
+      <c r="BC11">
+        <v>20</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>146</v>
+      </c>
       <c r="PS11" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -3913,7 +3985,7 @@
       </c>
       <c r="PW11">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:439" x14ac:dyDescent="0.2">
@@ -4091,7 +4163,7 @@
       </c>
       <c r="B13">
         <f t="shared" si="36"/>
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="C13">
         <f t="shared" si="5"/>
@@ -4107,19 +4179,19 @@
       </c>
       <c r="F13">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="G13">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="12"/>
@@ -4239,6 +4311,18 @@
       <c r="AV13" t="s">
         <v>146</v>
       </c>
+      <c r="AY13">
+        <v>25</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>146</v>
+      </c>
+      <c r="BC13">
+        <v>65</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>145</v>
+      </c>
       <c r="PS13" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4257,7 +4341,7 @@
       </c>
       <c r="PW13">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:439" x14ac:dyDescent="0.2">
@@ -4266,7 +4350,7 @@
       </c>
       <c r="B14">
         <f t="shared" si="36"/>
-        <v>180</v>
+        <v>245</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
@@ -4282,15 +4366,15 @@
       </c>
       <c r="F14">
         <f t="shared" si="8"/>
-        <v>180</v>
+        <v>245</v>
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
@@ -4420,6 +4504,12 @@
       <c r="AV14" t="s">
         <v>146</v>
       </c>
+      <c r="AY14">
+        <v>65</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>145</v>
+      </c>
       <c r="PS14" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4438,7 +4528,7 @@
       </c>
       <c r="PW14">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:439" x14ac:dyDescent="0.2">
@@ -4447,7 +4537,7 @@
       </c>
       <c r="B15">
         <f t="shared" si="36"/>
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C15">
         <f t="shared" si="5"/>
@@ -4463,11 +4553,11 @@
       </c>
       <c r="F15">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="G15">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="10"/>
@@ -4475,7 +4565,7 @@
       </c>
       <c r="I15" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="12"/>
@@ -4601,6 +4691,18 @@
       <c r="AV15" t="s">
         <v>146</v>
       </c>
+      <c r="AY15">
+        <v>5</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>146</v>
+      </c>
+      <c r="BC15">
+        <v>10</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>146</v>
+      </c>
       <c r="PS15" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4619,7 +4721,7 @@
       </c>
       <c r="PW15">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:439" x14ac:dyDescent="0.2">
@@ -4800,7 +4902,7 @@
       </c>
       <c r="B17">
         <f t="shared" si="36"/>
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="C17">
         <f t="shared" si="5"/>
@@ -4816,19 +4918,19 @@
       </c>
       <c r="F17">
         <f t="shared" si="8"/>
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="G17">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="3">
         <f t="shared" si="12"/>
@@ -4954,6 +5056,18 @@
       <c r="AV17" t="s">
         <v>146</v>
       </c>
+      <c r="AY17">
+        <v>20</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>146</v>
+      </c>
+      <c r="BC17">
+        <v>70</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>145</v>
+      </c>
       <c r="PS17" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -4972,7 +5086,7 @@
       </c>
       <c r="PW17">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:439" x14ac:dyDescent="0.2">
@@ -5159,7 +5273,7 @@
       </c>
       <c r="B19">
         <f t="shared" si="36"/>
-        <v>180</v>
+        <v>295</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
@@ -5175,19 +5289,19 @@
       </c>
       <c r="F19">
         <f t="shared" si="8"/>
-        <v>180</v>
+        <v>295</v>
       </c>
       <c r="G19">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="12"/>
@@ -5313,6 +5427,18 @@
       <c r="AV19" t="s">
         <v>146</v>
       </c>
+      <c r="AY19">
+        <v>45</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>146</v>
+      </c>
+      <c r="BC19">
+        <v>70</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>145</v>
+      </c>
       <c r="PS19" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -5331,7 +5457,7 @@
       </c>
       <c r="PW19">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:439" x14ac:dyDescent="0.2">
@@ -5340,7 +5466,7 @@
       </c>
       <c r="B20">
         <f t="shared" si="36"/>
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="C20">
         <f t="shared" si="5"/>
@@ -5356,19 +5482,19 @@
       </c>
       <c r="F20">
         <f t="shared" si="8"/>
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="G20">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="3">
         <f t="shared" si="12"/>
@@ -5488,6 +5614,18 @@
       <c r="AV20" t="s">
         <v>146</v>
       </c>
+      <c r="AY20">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="s">
+        <v>146</v>
+      </c>
+      <c r="BC20">
+        <v>80</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>145</v>
+      </c>
       <c r="PS20" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -5506,7 +5644,7 @@
       </c>
       <c r="PW20">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:439" x14ac:dyDescent="0.2">
@@ -5515,7 +5653,7 @@
       </c>
       <c r="B21">
         <f t="shared" si="36"/>
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="C21">
         <f t="shared" si="5"/>
@@ -5531,19 +5669,19 @@
       </c>
       <c r="F21">
         <f t="shared" si="8"/>
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="G21">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="3">
         <f t="shared" si="12"/>
@@ -5663,6 +5801,18 @@
       <c r="AR21" t="s">
         <v>146</v>
       </c>
+      <c r="AY21">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="s">
+        <v>146</v>
+      </c>
+      <c r="BC21">
+        <v>70</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>145</v>
+      </c>
       <c r="PS21" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -5681,7 +5831,7 @@
       </c>
       <c r="PW21">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:439" x14ac:dyDescent="0.2">
@@ -5690,7 +5840,7 @@
       </c>
       <c r="B22">
         <f t="shared" si="36"/>
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C22">
         <f t="shared" si="5"/>
@@ -5706,11 +5856,11 @@
       </c>
       <c r="F22">
         <f t="shared" si="8"/>
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="G22">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="10"/>
@@ -5718,7 +5868,7 @@
       </c>
       <c r="I22" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22" s="3">
         <f t="shared" si="12"/>
@@ -5847,6 +5997,18 @@
       <c r="AV22" t="s">
         <v>146</v>
       </c>
+      <c r="AY22">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="s">
+        <v>146</v>
+      </c>
+      <c r="BC22">
+        <v>20</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>146</v>
+      </c>
       <c r="PS22" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -5865,7 +6027,7 @@
       </c>
       <c r="PW22">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:439" x14ac:dyDescent="0.2">
@@ -5874,7 +6036,7 @@
       </c>
       <c r="B23">
         <f t="shared" si="36"/>
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C23">
         <f t="shared" si="5"/>
@@ -5890,11 +6052,11 @@
       </c>
       <c r="F23">
         <f t="shared" si="8"/>
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G23">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="10"/>
@@ -5902,7 +6064,7 @@
       </c>
       <c r="I23" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" s="3">
         <f t="shared" si="12"/>
@@ -6025,6 +6187,18 @@
       <c r="AV23" t="s">
         <v>146</v>
       </c>
+      <c r="AY23">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="s">
+        <v>146</v>
+      </c>
+      <c r="BC23">
+        <v>20</v>
+      </c>
+      <c r="BD23" t="s">
+        <v>146</v>
+      </c>
       <c r="PS23" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6043,7 +6217,7 @@
       </c>
       <c r="PW23">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:439" x14ac:dyDescent="0.2">
@@ -6052,7 +6226,7 @@
       </c>
       <c r="B24">
         <f t="shared" si="36"/>
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="C24">
         <f t="shared" si="5"/>
@@ -6068,15 +6242,15 @@
       </c>
       <c r="F24">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="G24">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="11"/>
@@ -6200,6 +6374,18 @@
       <c r="AV24" t="s">
         <v>146</v>
       </c>
+      <c r="AY24">
+        <v>60</v>
+      </c>
+      <c r="AZ24" t="s">
+        <v>145</v>
+      </c>
+      <c r="BC24">
+        <v>50</v>
+      </c>
+      <c r="BD24" t="s">
+        <v>145</v>
+      </c>
       <c r="PS24" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6218,7 +6404,7 @@
       </c>
       <c r="PW24">
         <f t="shared" si="35"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:439" x14ac:dyDescent="0.2">
@@ -6227,7 +6413,7 @@
       </c>
       <c r="B25">
         <f t="shared" si="36"/>
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C25">
         <f t="shared" si="5"/>
@@ -6243,15 +6429,15 @@
       </c>
       <c r="F25">
         <f t="shared" si="8"/>
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G25">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="11"/>
@@ -6384,6 +6570,12 @@
       <c r="AV25" t="s">
         <v>145</v>
       </c>
+      <c r="AY25">
+        <v>70</v>
+      </c>
+      <c r="AZ25" t="s">
+        <v>145</v>
+      </c>
       <c r="PS25" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6402,7 +6594,7 @@
       </c>
       <c r="PW25">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:439" x14ac:dyDescent="0.2">
@@ -6411,7 +6603,7 @@
       </c>
       <c r="B26">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C26">
         <f t="shared" si="5"/>
@@ -6427,11 +6619,11 @@
       </c>
       <c r="F26">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G26">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="10"/>
@@ -6439,7 +6631,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="12"/>
@@ -6495,7 +6687,7 @@
       </c>
       <c r="W26" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" s="4">
         <f t="shared" si="2"/>
@@ -6527,7 +6719,7 @@
       </c>
       <c r="AE26">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26">
         <f t="shared" si="30"/>
@@ -6541,6 +6733,15 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="BC26">
+        <v>40</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>146</v>
+      </c>
+      <c r="BE26">
+        <v>1</v>
+      </c>
       <c r="PS26" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6559,7 +6760,7 @@
       </c>
       <c r="PW26">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:439" x14ac:dyDescent="0.2">
@@ -6568,7 +6769,7 @@
       </c>
       <c r="B27">
         <f t="shared" si="36"/>
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C27">
         <f t="shared" si="5"/>
@@ -6584,11 +6785,11 @@
       </c>
       <c r="F27">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G27">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="10"/>
@@ -6596,7 +6797,7 @@
       </c>
       <c r="I27" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="3">
         <f t="shared" si="12"/>
@@ -6710,6 +6911,12 @@
       <c r="AN27" t="s">
         <v>146</v>
       </c>
+      <c r="BC27">
+        <v>20</v>
+      </c>
+      <c r="BD27" t="s">
+        <v>146</v>
+      </c>
       <c r="PS27" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6728,7 +6935,7 @@
       </c>
       <c r="PW27">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:439" x14ac:dyDescent="0.2">
@@ -6737,7 +6944,7 @@
       </c>
       <c r="B28">
         <f t="shared" si="36"/>
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
@@ -6753,15 +6960,15 @@
       </c>
       <c r="F28">
         <f t="shared" si="8"/>
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
@@ -6891,6 +7098,12 @@
       <c r="AV28" t="s">
         <v>145</v>
       </c>
+      <c r="BC28">
+        <v>80</v>
+      </c>
+      <c r="BD28" t="s">
+        <v>145</v>
+      </c>
       <c r="PS28" s="3">
         <f t="shared" si="32"/>
         <v>0</v>
@@ -6909,7 +7122,7 @@
       </c>
       <c r="PW28">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:439" x14ac:dyDescent="0.2">
@@ -6918,7 +7131,7 @@
       </c>
       <c r="B29">
         <f t="shared" ref="B29" si="61">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="C29">
         <f t="shared" ref="C29" si="62">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
@@ -6934,19 +7147,19 @@
       </c>
       <c r="F29">
         <f t="shared" si="8"/>
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="G29">
         <f t="shared" ref="G29" si="65">SUM(H29:I29)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" ref="H29" si="66">COUNTIF(AI29:PR29,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" ref="I29" si="67">COUNTIF(AI29:PR29,"R")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="3">
         <f t="shared" ref="J29" si="68">COUNTIF(AI29:PR29,"NR")</f>
@@ -7072,6 +7285,18 @@
       <c r="AV29" t="s">
         <v>145</v>
       </c>
+      <c r="AY29">
+        <v>85</v>
+      </c>
+      <c r="AZ29" t="s">
+        <v>145</v>
+      </c>
+      <c r="BC29">
+        <v>20</v>
+      </c>
+      <c r="BD29" t="s">
+        <v>146</v>
+      </c>
       <c r="PS29" s="3">
         <f t="shared" ref="PS29" si="86">COUNTIF(AI29:PR29,"HG")</f>
         <v>0</v>
@@ -7090,7 +7315,7 @@
       </c>
       <c r="PW29">
         <f t="shared" ref="PW29" si="89">G29-(K29+O29+S29)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:439" x14ac:dyDescent="0.2">

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD834D72-39FD-6E44-A685-CB01EB7B9C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F8DD8B-058E-5243-AD7F-93951C825092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="150">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -59,18 +59,6 @@
     <t>Match Amical 7</t>
   </si>
   <si>
-    <t>N3J1</t>
-  </si>
-  <si>
-    <t>N3J2</t>
-  </si>
-  <si>
-    <t>N3J3</t>
-  </si>
-  <si>
-    <t>N3J4</t>
-  </si>
-  <si>
     <t>N3J5</t>
   </si>
   <si>
@@ -477,6 +465,27 @@
   </si>
   <si>
     <t>R</t>
+  </si>
+  <si>
+    <t>N1J1</t>
+  </si>
+  <si>
+    <t>N1J2</t>
+  </si>
+  <si>
+    <t>N1J3</t>
+  </si>
+  <si>
+    <t>N1J4</t>
+  </si>
+  <si>
+    <t>Brian Chevreuil</t>
+  </si>
+  <si>
+    <t>Marc Thomas</t>
+  </si>
+  <si>
+    <t>HG</t>
   </si>
 </sst>
 </file>
@@ -873,1326 +882,1326 @@
   <sheetData>
     <row r="1" spans="1:439" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="AI1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="AY1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="BC1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="BG1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="BK1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="CA1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BL1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BO1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="CE1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="BP1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BS1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="CI1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="BT1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BW1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="CM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BX1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="CB1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="CU1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="CF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CW1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="CY1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="DA1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="DB1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="DC1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="DD1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="DE1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="DH1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="DI1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="DJ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="DK1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="DL1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="DM1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="DN1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="DO1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DP1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="DQ1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="DR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="DS1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="DT1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="DU1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="DV1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="DW1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="DX1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="DY1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="DZ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="EA1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="EB1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="EC1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="ED1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="EE1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="EF1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="EG1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="EH1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="EI1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="EJ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="EK1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="EL1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="EM1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="EN1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="EO1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="EP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="EQ1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="ER1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="ES1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="ET1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="EU1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="EV1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="EW1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="EX1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="EY1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="EZ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="FA1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="FB1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="FC1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="FD1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="FE1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="FF1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="FG1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="FH1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="FI1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="FJ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="FK1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="FL1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="FM1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="FN1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="FO1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="FP1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="FQ1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="FR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="FS1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="FT1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="FU1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="FV1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="FW1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="FX1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="FY1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="FZ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="GA1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="GB1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="GC1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="GD1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="GE1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="GF1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="GG1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="GH1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="GI1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="GJ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="GK1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="GL1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="GM1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="GN1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="GO1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="GP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="GQ1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="GR1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="GS1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="GT1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="GU1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="GV1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="GW1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="GX1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="GY1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="GZ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="HA1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="HB1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="HC1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="HD1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="HE1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="HF1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="HG1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="HH1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="HI1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="HJ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="HK1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="HL1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="HM1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="HN1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="HO1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="HP1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="HQ1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="HR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="HS1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="HT1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="HU1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="HV1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="HW1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="HX1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="HY1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="HZ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="IA1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="IB1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="IC1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="ID1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="IE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="IF1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="IG1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="IH1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="II1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="IJ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="IK1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="IL1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="IM1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="IN1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="IO1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="IP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="IQ1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="IR1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="IS1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="IT1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="IU1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="CJ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="CM1" s="1" t="s">
+      <c r="IV1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="IW1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="IX1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="IY1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="CN1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="IZ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="JA1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="JB1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="JC1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="CR1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="CU1" s="1" t="s">
+      <c r="JD1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="JE1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="JF1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="JG1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="CV1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CW1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CX1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="DA1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="DB1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="DC1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="DD1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="DE1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="DF1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="DG1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="DH1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="DI1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="DJ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="DK1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="DL1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="DM1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="DN1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="DO1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="DP1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="DQ1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="DR1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="DS1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="DT1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="DU1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="DV1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="DW1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="DX1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="DY1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="DZ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="EA1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="EB1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="EC1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="ED1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="EE1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="EF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="EG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="EH1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="EI1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="EJ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="EK1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="EL1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="EM1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="EN1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="EO1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="EP1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="EQ1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="ER1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="ES1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="ET1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="EU1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="EV1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="EW1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="EX1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="EY1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="EZ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="FA1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="FB1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="FC1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="FD1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="FE1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="FF1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="FG1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="FH1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="FI1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="FJ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="FK1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="FL1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="FM1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="FN1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="FO1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="FP1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="FQ1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="FR1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="FS1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="FT1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="FU1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="FV1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="FW1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="FX1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="FY1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="FZ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="GA1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="GB1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="GC1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="GD1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="GE1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="GF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="GG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="GH1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="GI1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="GJ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="GK1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="GL1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="GM1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="GN1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="GO1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="GP1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="GQ1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="GR1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="GS1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="GT1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="GU1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="GV1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="GW1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="GX1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="GY1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="GZ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="HA1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="HB1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="HC1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="HD1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="HE1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="HF1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="HG1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="HH1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="HI1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="HJ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="HK1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="HL1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="HM1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="HN1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="HO1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="HP1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="HQ1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="HR1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="HS1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="HT1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="HU1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="HV1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="HW1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="HX1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="HY1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="HZ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="IA1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="IB1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="IC1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="ID1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="IE1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="IF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="IG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="IH1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="II1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="IJ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="IK1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="IL1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="IM1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="IN1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="IO1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="IP1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="IQ1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="IR1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="IS1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="IT1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="IU1" s="2" t="s">
+      <c r="JH1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="JI1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="JJ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="JK1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="IV1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="IW1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="IX1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="IY1" s="1" t="s">
+      <c r="JL1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="JM1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="JN1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="JO1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="IZ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="JA1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="JB1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="JC1" s="2" t="s">
+      <c r="JP1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="JQ1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="JR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="JS1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="JD1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="JE1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="JF1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="JG1" s="1" t="s">
+      <c r="JT1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="JU1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="JV1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="JW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="JH1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="JI1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="JJ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="JK1" s="2" t="s">
+      <c r="JX1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="JY1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="JZ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="KA1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="JL1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="JM1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="JN1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="JO1" s="1" t="s">
+      <c r="KB1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="KC1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="KD1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="KE1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="JP1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="JQ1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="JR1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="JS1" s="2" t="s">
+      <c r="KF1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="KG1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="KH1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="KI1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="JT1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="JU1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="JV1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="JW1" s="1" t="s">
+      <c r="KJ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="KK1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="KL1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="KM1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="JX1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="JY1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="JZ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="KA1" s="2" t="s">
+      <c r="KN1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="KO1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="KP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="KQ1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="KB1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="KC1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="KD1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="KE1" s="1" t="s">
+      <c r="KR1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="KS1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="KT1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="KU1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="KF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="KG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="KH1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="KI1" s="2" t="s">
+      <c r="KV1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="KW1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="KX1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="KY1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="KJ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="KK1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="KL1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="KM1" s="1" t="s">
+      <c r="KZ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="LA1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="LB1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="LC1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="KN1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="KO1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="KP1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="KQ1" s="2" t="s">
+      <c r="LD1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="LE1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="LF1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="LG1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="KR1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="KS1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="KT1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="KU1" s="1" t="s">
+      <c r="LH1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="LI1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="LJ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="LK1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="KV1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="KW1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="KX1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="KY1" s="2" t="s">
+      <c r="LL1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="LM1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="LN1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="LO1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="KZ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="LA1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="LB1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="LC1" s="1" t="s">
+      <c r="LP1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="LQ1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="LR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="LS1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="LD1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="LE1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="LF1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="LG1" s="2" t="s">
+      <c r="LT1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="LU1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="LV1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="LW1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="LH1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="LI1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="LJ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="LK1" s="1" t="s">
+      <c r="LX1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="LY1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="LZ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="MA1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="LL1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="LM1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="LN1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="LO1" s="2" t="s">
+      <c r="MB1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="MC1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="MD1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="ME1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="LP1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="LQ1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="LR1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="LS1" s="1" t="s">
+      <c r="MF1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="MG1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="MH1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="MI1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="MJ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="MK1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="ML1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="MM1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="MN1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="MO1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="MP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="MQ1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="MR1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="MS1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="MT1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="MU1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="MV1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="MW1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="MX1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="MY1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="MZ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="NA1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="NB1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="NC1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="ND1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="NE1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="NF1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="NG1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="NH1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="NI1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="NJ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="NK1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="NL1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="NM1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="NN1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="NO1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="NP1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="NQ1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="NR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="NS1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="NT1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="NU1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="NV1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="NW1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="LT1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="LU1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="LV1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="LW1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="LX1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="LY1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="LZ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="MA1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="MB1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="MC1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="MD1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="ME1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="MF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="MG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="MH1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="MI1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="MJ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="MK1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="ML1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="MM1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="MN1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="MO1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="MP1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="MQ1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="MR1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="MS1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="MT1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="MU1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="MV1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="MW1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="MX1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="MY1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="MZ1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="NA1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="NB1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="NC1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="ND1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="NE1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="NF1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="NG1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="NH1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="NI1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="NJ1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="NK1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="NL1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="NM1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="NN1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="NO1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="NP1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="NQ1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="NR1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="NS1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="NT1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="NU1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="NV1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="NW1" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="NX1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="NY1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="NZ1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="OA1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="OB1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="OC1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="OD1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="OE1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="OF1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="OG1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="OH1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="OI1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="OJ1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="OK1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="OL1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="OM1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="ON1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="OO1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="OP1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="OQ1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="OR1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="OS1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="OT1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="OU1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="OV1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="OW1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="OX1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="OY1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="OZ1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="PA1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="PB1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="PC1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="PD1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="PE1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="PF1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="PG1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="PH1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="PI1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="PJ1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="PK1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="PL1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="PM1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="PN1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="PO1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="PP1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="PQ1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="PR1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="PS1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="PT1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="PU1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="PV1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="PW1" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="PT1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="PU1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="PV1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="PW1" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:439" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
@@ -2330,27 +2339,30 @@
         <v>60</v>
       </c>
       <c r="AR2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AU2">
         <v>90</v>
       </c>
       <c r="AV2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AY2">
         <v>90</v>
       </c>
       <c r="AZ2" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>149</v>
       </c>
       <c r="PS2" s="3">
         <f>COUNTIF(AI2:PR2,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT2" s="3">
         <f>COUNTIF(CY2:GX2,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU2" s="3">
         <f>COUNTIF(GY2:IT2,"HG")</f>
@@ -2367,15 +2379,15 @@
     </row>
     <row r="3" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B3">
         <f>SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3,CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3,GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3,IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C28" si="5">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D28" si="6">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
@@ -2391,11 +2403,11 @@
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G28" si="9">SUM(H3:I3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H28" si="10">COUNTIF(AI3:PR3,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" ref="I3:I28" si="11">COUNTIF(AI3:PR3,"R")</f>
@@ -2407,11 +2419,11 @@
       </c>
       <c r="K3">
         <f t="shared" ref="K3:K28" si="13">SUM(L3:M3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3">
         <f t="shared" ref="L3:L28" si="14">COUNTIF(CY3:GX3,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="3">
         <f t="shared" ref="M3:M28" si="15">COUNTIF(CY3:GX3,"R")</f>
@@ -2500,6 +2512,12 @@
       <c r="AH3">
         <f t="shared" ref="AH3:AH31" si="31">SUM(IX3,JB3,JF3,JJ3,JN3,JR3,JV3,JZ3,KD3,KH3,KL3,KP3,KT3,KX3,LB3,LF3,LJ3,LN3,LR3,LV3,LZ3,MD3,ML3,MP3,MT3,MX3,NB3,NF3,NJ3,NN3,NR3,NV3,NZ3,OD3,OH3,OL3,OP3,OT3,OX3,PB3,PF3,PJ3,PN3,PR3)</f>
         <v>0</v>
+      </c>
+      <c r="CY3">
+        <v>90</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>141</v>
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS28" si="32">COUNTIF(AI3:PR3,"HG")</f>
@@ -2524,7 +2542,7 @@
     </row>
     <row r="4" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B28" si="36">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
@@ -2662,33 +2680,36 @@
         <v>45</v>
       </c>
       <c r="AJ4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM4">
         <v>45</v>
       </c>
       <c r="AN4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ4">
         <v>30</v>
       </c>
       <c r="AR4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC4">
         <v>70</v>
       </c>
       <c r="BD4" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>149</v>
       </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="57">COUNTIF(AI4:PR4,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="58">COUNTIF(CY4:GX4,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="59">COUNTIF(GY4:IT4,"HG")</f>
@@ -2705,15 +2726,15 @@
     </row>
     <row r="5" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B5">
         <f t="shared" si="36"/>
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="C5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D5">
         <f t="shared" si="6"/>
@@ -2729,11 +2750,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="11"/>
@@ -2745,11 +2766,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="15"/>
@@ -2843,25 +2864,31 @@
         <v>45</v>
       </c>
       <c r="AN5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ5">
         <v>60</v>
       </c>
       <c r="AR5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AU5">
         <v>75</v>
       </c>
       <c r="AV5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AY5">
         <v>90</v>
       </c>
       <c r="AZ5" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CY5">
+        <v>90</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>141</v>
       </c>
       <c r="PS5" s="3">
         <f t="shared" si="32"/>
@@ -2886,15 +2913,15 @@
     </row>
     <row r="6" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B6">
         <f t="shared" si="36"/>
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <f t="shared" si="6"/>
@@ -2910,7 +2937,7 @@
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
@@ -2918,7 +2945,7 @@
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="12"/>
@@ -2926,7 +2953,7 @@
       </c>
       <c r="K6">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="14"/>
@@ -2934,7 +2961,7 @@
       </c>
       <c r="M6" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="3">
         <f t="shared" si="16"/>
@@ -3024,37 +3051,43 @@
         <v>45</v>
       </c>
       <c r="AJ6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AM6">
         <v>45</v>
       </c>
       <c r="AN6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ6">
         <v>30</v>
       </c>
       <c r="AR6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU6">
         <v>15</v>
       </c>
       <c r="AV6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY6">
         <v>60</v>
       </c>
       <c r="AZ6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="BC6">
         <v>35</v>
       </c>
       <c r="BD6" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CY6">
+        <v>12</v>
+      </c>
+      <c r="CZ6" t="s">
+        <v>142</v>
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="32"/>
@@ -3079,7 +3112,7 @@
     </row>
     <row r="7" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B7">
         <f t="shared" si="36"/>
@@ -3217,15 +3250,18 @@
         <v>55</v>
       </c>
       <c r="BD7" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CZ7" t="s">
+        <v>149</v>
       </c>
       <c r="PS7" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT7" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU7" s="3">
         <f t="shared" si="34"/>
@@ -3242,15 +3278,15 @@
     </row>
     <row r="8" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B8">
         <f t="shared" si="36"/>
-        <v>210</v>
+        <v>272</v>
       </c>
       <c r="C8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D8">
         <f t="shared" si="6"/>
@@ -3266,11 +3302,11 @@
       </c>
       <c r="G8">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="11"/>
@@ -3282,11 +3318,11 @@
       </c>
       <c r="K8">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="15"/>
@@ -3380,25 +3416,31 @@
         <v>45</v>
       </c>
       <c r="AJ8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AM8">
         <v>45</v>
       </c>
       <c r="AN8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ8">
         <v>60</v>
       </c>
       <c r="AR8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AU8">
         <v>60</v>
       </c>
       <c r="AV8" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CY8">
+        <v>62</v>
+      </c>
+      <c r="CZ8" t="s">
+        <v>141</v>
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="32"/>
@@ -3423,15 +3465,15 @@
     </row>
     <row r="9" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B9">
         <f t="shared" si="36"/>
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="C9">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D9">
         <f t="shared" si="6"/>
@@ -3447,11 +3489,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="11"/>
@@ -3463,11 +3505,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="15"/>
@@ -3561,25 +3603,31 @@
         <v>30</v>
       </c>
       <c r="AR9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU9">
         <v>75</v>
       </c>
       <c r="AV9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AY9">
         <v>90</v>
       </c>
       <c r="AZ9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="BC9">
         <v>50</v>
       </c>
       <c r="BD9" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CY9">
+        <v>78</v>
+      </c>
+      <c r="CZ9" t="s">
+        <v>141</v>
       </c>
       <c r="PS9" s="3">
         <f t="shared" si="32"/>
@@ -3604,15 +3652,15 @@
     </row>
     <row r="10" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B10">
         <f t="shared" si="36"/>
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D10">
         <f t="shared" si="6"/>
@@ -3628,11 +3676,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
@@ -3644,11 +3692,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="15"/>
@@ -3742,37 +3790,43 @@
         <v>45</v>
       </c>
       <c r="AJ10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AM10">
         <v>45</v>
       </c>
       <c r="AN10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ10">
         <v>60</v>
       </c>
       <c r="AR10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AU10">
         <v>60</v>
       </c>
       <c r="AV10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AY10">
         <v>80</v>
       </c>
       <c r="AZ10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="BC10">
         <v>20</v>
       </c>
       <c r="BD10" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CY10">
+        <v>90</v>
+      </c>
+      <c r="CZ10" t="s">
+        <v>141</v>
       </c>
       <c r="PS10" s="3">
         <f t="shared" si="32"/>
@@ -3797,7 +3851,7 @@
     </row>
     <row r="11" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B11">
         <f t="shared" si="36"/>
@@ -3935,45 +3989,48 @@
         <v>45</v>
       </c>
       <c r="AJ11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM11">
         <v>45</v>
       </c>
       <c r="AN11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ11">
         <v>60</v>
       </c>
       <c r="AR11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AU11">
         <v>60</v>
       </c>
       <c r="AV11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AY11">
         <v>80</v>
       </c>
       <c r="AZ11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="BC11">
         <v>20</v>
       </c>
       <c r="BD11" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CZ11" t="s">
+        <v>149</v>
       </c>
       <c r="PS11" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT11" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU11" s="3">
         <f t="shared" si="34"/>
@@ -3990,15 +4047,15 @@
     </row>
     <row r="12" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B12">
         <f t="shared" si="36"/>
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="C12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <f t="shared" si="6"/>
@@ -4014,7 +4071,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="10"/>
@@ -4022,7 +4079,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="12"/>
@@ -4030,7 +4087,7 @@
       </c>
       <c r="K12">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3">
         <f t="shared" si="14"/>
@@ -4038,7 +4095,7 @@
       </c>
       <c r="M12" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="3">
         <f t="shared" si="16"/>
@@ -4128,13 +4185,19 @@
         <v>45</v>
       </c>
       <c r="AJ12" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AU12">
         <v>30</v>
       </c>
       <c r="AV12" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CY12">
+        <v>28</v>
+      </c>
+      <c r="CZ12" t="s">
+        <v>142</v>
       </c>
       <c r="PS12" s="3">
         <f t="shared" si="32"/>
@@ -4159,7 +4222,7 @@
     </row>
     <row r="13" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B13">
         <f t="shared" si="36"/>
@@ -4297,39 +4360,42 @@
         <v>45</v>
       </c>
       <c r="AJ13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AM13">
         <v>45</v>
       </c>
       <c r="AN13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU13">
         <v>30</v>
       </c>
       <c r="AV13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY13">
         <v>25</v>
       </c>
       <c r="AZ13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC13">
         <v>65</v>
       </c>
       <c r="BD13" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CZ13" t="s">
+        <v>149</v>
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="34"/>
@@ -4346,15 +4412,15 @@
     </row>
     <row r="14" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B14">
         <f t="shared" si="36"/>
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D14">
         <f t="shared" si="6"/>
@@ -4370,7 +4436,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
@@ -4378,7 +4444,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="12"/>
@@ -4386,7 +4452,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="14"/>
@@ -4394,7 +4460,7 @@
       </c>
       <c r="M14" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="16"/>
@@ -4484,31 +4550,37 @@
         <v>45</v>
       </c>
       <c r="AJ14" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AM14">
         <v>45</v>
       </c>
       <c r="AN14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ14">
         <v>60</v>
       </c>
       <c r="AR14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AU14">
         <v>30</v>
       </c>
       <c r="AV14" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY14">
         <v>65</v>
       </c>
       <c r="AZ14" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CY14">
+        <v>12</v>
+      </c>
+      <c r="CZ14" t="s">
+        <v>142</v>
       </c>
       <c r="PS14" s="3">
         <f t="shared" si="32"/>
@@ -4533,7 +4605,7 @@
     </row>
     <row r="15" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B15">
         <f t="shared" si="36"/>
@@ -4671,45 +4743,48 @@
         <v>45</v>
       </c>
       <c r="AJ15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM15">
         <v>45</v>
       </c>
       <c r="AN15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ15">
         <v>30</v>
       </c>
       <c r="AR15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU15">
         <v>30</v>
       </c>
       <c r="AV15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY15">
         <v>5</v>
       </c>
       <c r="AZ15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC15">
         <v>10</v>
       </c>
       <c r="BD15" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CZ15" t="s">
+        <v>149</v>
       </c>
       <c r="PS15" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT15" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU15" s="3">
         <f t="shared" si="34"/>
@@ -4726,7 +4801,7 @@
     </row>
     <row r="16" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B16">
         <f t="shared" si="36"/>
@@ -4864,7 +4939,7 @@
         <v>45</v>
       </c>
       <c r="AJ16" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AK16">
         <v>1</v>
@@ -4873,15 +4948,18 @@
         <v>22</v>
       </c>
       <c r="AN16" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CZ16" t="s">
+        <v>149</v>
       </c>
       <c r="PS16" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT16" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU16" s="3">
         <f t="shared" si="34"/>
@@ -4898,15 +4976,15 @@
     </row>
     <row r="17" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B17">
         <f t="shared" si="36"/>
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="C17">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D17">
         <f t="shared" si="6"/>
@@ -4922,11 +5000,11 @@
       </c>
       <c r="G17">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="3">
         <f t="shared" si="11"/>
@@ -4938,11 +5016,11 @@
       </c>
       <c r="K17">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="3">
         <f t="shared" si="15"/>
@@ -4986,11 +5064,11 @@
       </c>
       <c r="W17" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="50"/>
@@ -5002,7 +5080,7 @@
       </c>
       <c r="AA17">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17">
         <f t="shared" si="26"/>
@@ -5036,37 +5114,46 @@
         <v>45</v>
       </c>
       <c r="AJ17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM17">
         <v>45</v>
       </c>
       <c r="AN17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ17">
         <v>30</v>
       </c>
       <c r="AR17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU17">
         <v>40</v>
       </c>
       <c r="AV17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY17">
         <v>20</v>
       </c>
       <c r="AZ17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC17">
         <v>70</v>
       </c>
       <c r="BD17" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CY17">
+        <v>90</v>
+      </c>
+      <c r="CZ17" t="s">
+        <v>141</v>
+      </c>
+      <c r="DA17">
+        <v>1</v>
       </c>
       <c r="PS17" s="3">
         <f t="shared" si="32"/>
@@ -5091,15 +5178,15 @@
     </row>
     <row r="18" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B18">
         <f t="shared" si="36"/>
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C18">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <f t="shared" si="6"/>
@@ -5115,7 +5202,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="10"/>
@@ -5123,7 +5210,7 @@
       </c>
       <c r="I18" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="12"/>
@@ -5131,7 +5218,7 @@
       </c>
       <c r="K18">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="14"/>
@@ -5139,7 +5226,7 @@
       </c>
       <c r="M18" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="16"/>
@@ -5229,7 +5316,7 @@
         <v>45</v>
       </c>
       <c r="AJ18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AK18">
         <v>1</v>
@@ -5238,13 +5325,19 @@
         <v>45</v>
       </c>
       <c r="AN18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ18">
         <v>60</v>
       </c>
       <c r="AR18" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CY18">
+        <v>28</v>
+      </c>
+      <c r="CZ18" t="s">
+        <v>142</v>
       </c>
       <c r="PS18" s="3">
         <f t="shared" si="32"/>
@@ -5269,15 +5362,15 @@
     </row>
     <row r="19" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B19">
         <f t="shared" si="36"/>
-        <v>295</v>
+        <v>373</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D19">
         <f t="shared" si="6"/>
@@ -5293,11 +5386,11 @@
       </c>
       <c r="G19">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="11"/>
@@ -5309,11 +5402,11 @@
       </c>
       <c r="K19">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="3">
         <f t="shared" si="15"/>
@@ -5407,37 +5500,43 @@
         <v>45</v>
       </c>
       <c r="AJ19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AM19">
         <v>45</v>
       </c>
       <c r="AN19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ19">
         <v>60</v>
       </c>
       <c r="AR19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AU19">
         <v>30</v>
       </c>
       <c r="AV19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY19">
         <v>45</v>
       </c>
       <c r="AZ19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC19">
         <v>70</v>
       </c>
       <c r="BD19" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CY19">
+        <v>78</v>
+      </c>
+      <c r="CZ19" t="s">
+        <v>141</v>
       </c>
       <c r="PS19" s="3">
         <f t="shared" si="32"/>
@@ -5462,7 +5561,7 @@
     </row>
     <row r="20" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B20">
         <f t="shared" si="36"/>
@@ -5600,39 +5699,42 @@
         <v>45</v>
       </c>
       <c r="AJ20" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ20">
         <v>30</v>
       </c>
       <c r="AR20" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU20">
         <v>30</v>
       </c>
       <c r="AV20" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY20">
         <v>10</v>
       </c>
       <c r="AZ20" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC20">
         <v>80</v>
       </c>
       <c r="BD20" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CZ20" t="s">
+        <v>149</v>
       </c>
       <c r="PS20" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="34"/>
@@ -5649,7 +5751,7 @@
     </row>
     <row r="21" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B21">
         <f t="shared" si="36"/>
@@ -5787,39 +5889,42 @@
         <v>22</v>
       </c>
       <c r="AJ21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AM21">
         <v>22</v>
       </c>
       <c r="AN21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ21">
         <v>30</v>
       </c>
       <c r="AR21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY21">
         <v>10</v>
       </c>
       <c r="AZ21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC21">
         <v>70</v>
       </c>
       <c r="BD21" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CZ21" t="s">
+        <v>149</v>
       </c>
       <c r="PS21" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT21" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU21" s="3">
         <f t="shared" si="34"/>
@@ -5836,7 +5941,7 @@
     </row>
     <row r="22" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B22">
         <f t="shared" si="36"/>
@@ -5974,7 +6079,7 @@
         <v>22</v>
       </c>
       <c r="AJ22" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AL22">
         <v>1</v>
@@ -5983,39 +6088,42 @@
         <v>30</v>
       </c>
       <c r="AN22" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ22">
         <v>30</v>
       </c>
       <c r="AR22" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU22">
         <v>15</v>
       </c>
       <c r="AV22" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY22">
         <v>10</v>
       </c>
       <c r="AZ22" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC22">
         <v>20</v>
       </c>
       <c r="BD22" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CZ22" t="s">
+        <v>149</v>
       </c>
       <c r="PS22" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="34"/>
@@ -6032,7 +6140,7 @@
     </row>
     <row r="23" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B23">
         <f t="shared" si="36"/>
@@ -6170,13 +6278,13 @@
         <v>45</v>
       </c>
       <c r="AJ23" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM23">
         <v>15</v>
       </c>
       <c r="AN23" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AO23">
         <v>1</v>
@@ -6185,27 +6293,30 @@
         <v>15</v>
       </c>
       <c r="AV23" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY23">
         <v>10</v>
       </c>
       <c r="AZ23" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC23">
         <v>20</v>
       </c>
       <c r="BD23" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CZ23" t="s">
+        <v>149</v>
       </c>
       <c r="PS23" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT23" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU23" s="3">
         <f t="shared" si="34"/>
@@ -6222,15 +6333,15 @@
     </row>
     <row r="24" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B24">
         <f t="shared" si="36"/>
-        <v>230</v>
+        <v>292</v>
       </c>
       <c r="C24">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D24">
         <f t="shared" si="6"/>
@@ -6246,11 +6357,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="11"/>
@@ -6262,11 +6373,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="15"/>
@@ -6318,11 +6429,11 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24">
         <f t="shared" si="25"/>
@@ -6330,7 +6441,7 @@
       </c>
       <c r="AB24">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24">
         <f t="shared" si="27"/>
@@ -6360,31 +6471,40 @@
         <v>45</v>
       </c>
       <c r="AJ24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM24">
         <v>45</v>
       </c>
       <c r="AN24" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU24">
         <v>30</v>
       </c>
       <c r="AV24" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AY24">
         <v>60</v>
       </c>
       <c r="AZ24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="BC24">
         <v>50</v>
       </c>
       <c r="BD24" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CY24">
+        <v>62</v>
+      </c>
+      <c r="CZ24" t="s">
+        <v>141</v>
+      </c>
+      <c r="DB24">
+        <v>1</v>
       </c>
       <c r="PS24" s="3">
         <f t="shared" si="32"/>
@@ -6409,7 +6529,7 @@
     </row>
     <row r="25" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B25">
         <f t="shared" si="36"/>
@@ -6547,19 +6667,19 @@
         <v>45</v>
       </c>
       <c r="AJ25" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM25">
         <v>45</v>
       </c>
       <c r="AN25" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ25">
         <v>30</v>
       </c>
       <c r="AR25" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AS25">
         <v>1</v>
@@ -6568,21 +6688,24 @@
         <v>60</v>
       </c>
       <c r="AV25" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AY25">
         <v>70</v>
       </c>
       <c r="AZ25" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CZ25" t="s">
+        <v>149</v>
       </c>
       <c r="PS25" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT25" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU25" s="3">
         <f t="shared" si="34"/>
@@ -6599,15 +6722,15 @@
     </row>
     <row r="26" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B26">
         <f t="shared" si="36"/>
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C26">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <f t="shared" si="6"/>
@@ -6623,7 +6746,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="10"/>
@@ -6631,7 +6754,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="12"/>
@@ -6639,7 +6762,7 @@
       </c>
       <c r="K26">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="14"/>
@@ -6647,7 +6770,7 @@
       </c>
       <c r="M26" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="16"/>
@@ -6737,10 +6860,16 @@
         <v>40</v>
       </c>
       <c r="BD26" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BE26">
         <v>1</v>
+      </c>
+      <c r="CY26">
+        <v>15</v>
+      </c>
+      <c r="CZ26" t="s">
+        <v>142</v>
       </c>
       <c r="PS26" s="3">
         <f t="shared" si="32"/>
@@ -6765,7 +6894,7 @@
     </row>
     <row r="27" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B27">
         <f t="shared" si="36"/>
@@ -6903,27 +7032,30 @@
         <v>45</v>
       </c>
       <c r="AJ27" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM27">
         <v>45</v>
       </c>
       <c r="AN27" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="BC27">
         <v>20</v>
       </c>
       <c r="BD27" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CZ27" t="s">
+        <v>149</v>
       </c>
       <c r="PS27" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT27" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU27" s="3">
         <f t="shared" si="34"/>
@@ -6940,15 +7072,15 @@
     </row>
     <row r="28" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B28">
         <f t="shared" si="36"/>
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D28">
         <f t="shared" si="6"/>
@@ -6964,11 +7096,11 @@
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
@@ -6980,11 +7112,11 @@
       </c>
       <c r="K28">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="3">
         <f t="shared" si="15"/>
@@ -7078,31 +7210,37 @@
         <v>45</v>
       </c>
       <c r="AJ28" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM28">
         <v>45</v>
       </c>
       <c r="AN28" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ28">
         <v>30</v>
       </c>
       <c r="AR28" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU28">
         <v>60</v>
       </c>
       <c r="AV28" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="BC28">
         <v>80</v>
       </c>
       <c r="BD28" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="CY28">
+        <v>90</v>
+      </c>
+      <c r="CZ28" t="s">
+        <v>141</v>
       </c>
       <c r="PS28" s="3">
         <f t="shared" si="32"/>
@@ -7127,15 +7265,15 @@
     </row>
     <row r="29" spans="1:439" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B29">
         <f t="shared" ref="B29" si="61">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
-        <v>285</v>
+        <v>375</v>
       </c>
       <c r="C29">
         <f t="shared" ref="C29" si="62">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D29">
         <f t="shared" ref="D29" si="63">SUM(GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29)</f>
@@ -7151,11 +7289,11 @@
       </c>
       <c r="G29">
         <f t="shared" ref="G29" si="65">SUM(H29:I29)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" ref="H29" si="66">COUNTIF(AI29:PR29,"T")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" ref="I29" si="67">COUNTIF(AI29:PR29,"R")</f>
@@ -7167,11 +7305,11 @@
       </c>
       <c r="K29">
         <f t="shared" ref="K29" si="69">SUM(L29:M29)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" ref="L29" si="70">COUNTIF(CY29:GX29,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" ref="M29" si="71">COUNTIF(CY29:GX29,"R")</f>
@@ -7265,37 +7403,43 @@
         <v>45</v>
       </c>
       <c r="AJ29" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AM29">
         <v>45</v>
       </c>
       <c r="AN29" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AQ29">
         <v>30</v>
       </c>
       <c r="AR29" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AU29">
         <v>60</v>
       </c>
       <c r="AV29" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AY29">
         <v>85</v>
       </c>
       <c r="AZ29" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="BC29">
         <v>20</v>
       </c>
       <c r="BD29" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="CY29">
+        <v>90</v>
+      </c>
+      <c r="CZ29" t="s">
+        <v>141</v>
       </c>
       <c r="PS29" s="3">
         <f t="shared" ref="PS29" si="86">COUNTIF(AI29:PR29,"HG")</f>
@@ -7319,13 +7463,16 @@
       </c>
     </row>
     <row r="30" spans="1:439" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>147</v>
+      </c>
       <c r="B30">
         <f t="shared" ref="B30" si="90">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="91">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="92">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
@@ -7341,11 +7488,11 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="95">SUM(H30:I30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="96">COUNTIF(AI30:PR30,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="97">COUNTIF(AI30:PR30,"R")</f>
@@ -7357,11 +7504,11 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="99">SUM(L30:M30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="100">COUNTIF(CY30:GX30,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="101">COUNTIF(CY30:GX30,"R")</f>
@@ -7451,6 +7598,12 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="CY30">
+        <v>75</v>
+      </c>
+      <c r="CZ30" t="s">
+        <v>141</v>
+      </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="116">COUNTIF(AI30:PR30,"HG")</f>
         <v>0</v>
@@ -7473,6 +7626,9 @@
       </c>
     </row>
     <row r="31" spans="1:439" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>148</v>
+      </c>
       <c r="B31">
         <f t="shared" ref="B31" si="120">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
         <v>0</v>
@@ -7605,13 +7761,16 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="CZ31" t="s">
+        <v>149</v>
+      </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="146">COUNTIF(AI31:PR31,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT31" s="3">
         <f t="shared" ref="PT31" si="147">COUNTIF(CY31:GX31,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU31" s="3">
         <f t="shared" ref="PU31" si="148">COUNTIF(GY31:IT31,"HG")</f>
